--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IVV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AAPL_back" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AMZN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AMZN_back" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GE_back" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IVV" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IVV_back" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="M" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="M_back" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 10864</t>
+          <t>Day 1 — Active seconds: 13013</t>
         </is>
       </c>
     </row>
@@ -456,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1066</v>
+        <v>1788</v>
       </c>
       <c r="C3" t="n">
-        <v>1764</v>
+        <v>2104</v>
       </c>
       <c r="D3" t="n">
-        <v>8034</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>371</v>
+        <v>1199</v>
       </c>
       <c r="C4" t="n">
-        <v>956</v>
+        <v>1531</v>
       </c>
       <c r="D4" t="n">
-        <v>2386</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +515,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.800000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="C7" t="n">
         <v>16.2</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +531,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 14235</t>
+          <t>Day 2 — Active seconds: 15868</t>
         </is>
       </c>
     </row>
@@ -571,13 +576,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1042</v>
+        <v>1508</v>
       </c>
       <c r="C13" t="n">
-        <v>2566</v>
+        <v>2900</v>
       </c>
       <c r="D13" t="n">
-        <v>10627</v>
+        <v>11460</v>
       </c>
     </row>
     <row r="14">
@@ -587,13 +592,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>515</v>
+        <v>1205</v>
       </c>
       <c r="C14" t="n">
-        <v>1853</v>
+        <v>2473</v>
       </c>
       <c r="D14" t="n">
-        <v>4852</v>
+        <v>7061</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +630,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="D17" t="n">
-        <v>74.7</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="18">
@@ -641,19 +646,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>15.6</v>
       </c>
       <c r="D18" t="n">
-        <v>34.1</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 13239</t>
+          <t>Day 3 — Active seconds: 15422</t>
         </is>
       </c>
     </row>
@@ -686,13 +691,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1178</v>
+        <v>1864</v>
       </c>
       <c r="C23" t="n">
-        <v>1691</v>
+        <v>1932</v>
       </c>
       <c r="D23" t="n">
-        <v>10370</v>
+        <v>11626</v>
       </c>
     </row>
     <row r="24">
@@ -702,13 +707,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>564</v>
+        <v>1352</v>
       </c>
       <c r="C24" t="n">
-        <v>1020</v>
+        <v>1479</v>
       </c>
       <c r="D24" t="n">
-        <v>4976</v>
+        <v>7149</v>
       </c>
     </row>
     <row r="26">
@@ -740,13 +745,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.9</v>
+        <v>12.1</v>
       </c>
       <c r="C27" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="D27" t="n">
-        <v>78.3</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -756,19 +761,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="D28" t="n">
-        <v>37.6</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 14184</t>
+          <t>Day 4 — Active seconds: 15957</t>
         </is>
       </c>
     </row>
@@ -801,13 +806,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>803</v>
+        <v>1366</v>
       </c>
       <c r="C33" t="n">
-        <v>2159</v>
+        <v>2581</v>
       </c>
       <c r="D33" t="n">
-        <v>11222</v>
+        <v>12010</v>
       </c>
     </row>
     <row r="34">
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>464</v>
+        <v>1087</v>
       </c>
       <c r="C34" t="n">
-        <v>1459</v>
+        <v>2182</v>
       </c>
       <c r="D34" t="n">
-        <v>5256</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="36">
@@ -855,13 +860,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="C37" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="D37" t="n">
-        <v>79.09999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="38">
@@ -871,19 +876,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="C38" t="n">
-        <v>10.3</v>
+        <v>13.7</v>
       </c>
       <c r="D38" t="n">
-        <v>37.1</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 14893</t>
+          <t>Day 5 — Active seconds: 16699</t>
         </is>
       </c>
     </row>
@@ -916,13 +921,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>757</v>
+        <v>1196</v>
       </c>
       <c r="C43" t="n">
-        <v>2310</v>
+        <v>2669</v>
       </c>
       <c r="D43" t="n">
-        <v>11826</v>
+        <v>12834</v>
       </c>
     </row>
     <row r="44">
@@ -932,13 +937,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>476</v>
+        <v>1015</v>
       </c>
       <c r="C44" t="n">
-        <v>1740</v>
+        <v>2249</v>
       </c>
       <c r="D44" t="n">
-        <v>5939</v>
+        <v>8213</v>
       </c>
     </row>
     <row r="46">
@@ -970,13 +975,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="C47" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -986,13 +991,602 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active seconds: 18175</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>814</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15665</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>529</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13372</v>
+      </c>
+      <c r="D4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active seconds: 18250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>220</v>
+      </c>
+      <c r="C13" t="n">
+        <v>16922</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>153</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15429</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active seconds: 19224</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>619</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17319</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>463</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15519</v>
+      </c>
+      <c r="D24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>3.2</v>
       </c>
+      <c r="C27" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active seconds: 19386</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>515</v>
+      </c>
+      <c r="C33" t="n">
+        <v>17888</v>
+      </c>
+      <c r="D33" t="n">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>338</v>
+      </c>
+      <c r="C34" t="n">
+        <v>16135</v>
+      </c>
+      <c r="D34" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active seconds: 19624</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>561</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17896</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>377</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15750</v>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C47" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.9</v>
+      </c>
       <c r="C48" t="n">
-        <v>11.7</v>
+        <v>80.3</v>
       </c>
       <c r="D48" t="n">
-        <v>39.9</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1012,7 +1606,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 13983</t>
+          <t>Day 1 — Active seconds: 18090</t>
         </is>
       </c>
     </row>
@@ -1045,13 +1639,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5921</v>
+        <v>3663</v>
       </c>
       <c r="C3" t="n">
-        <v>114</v>
+        <v>3436</v>
       </c>
       <c r="D3" t="n">
-        <v>7948</v>
+        <v>10991</v>
       </c>
     </row>
     <row r="4">
@@ -1061,13 +1655,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2476</v>
+        <v>3001</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>3277</v>
       </c>
       <c r="D4" t="n">
-        <v>4579</v>
+        <v>8975</v>
       </c>
     </row>
     <row r="6">
@@ -1099,13 +1693,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.3</v>
+        <v>20.2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>56.8</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="8">
@@ -1115,19 +1709,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>18.1</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 17795</t>
+          <t>Day 2 — Active seconds: 21108</t>
         </is>
       </c>
     </row>
@@ -1160,13 +1754,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5245</v>
+        <v>2990</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>4575</v>
       </c>
       <c r="D13" t="n">
-        <v>12447</v>
+        <v>13543</v>
       </c>
     </row>
     <row r="14">
@@ -1176,13 +1770,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2678</v>
+        <v>2629</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>4368</v>
       </c>
       <c r="D14" t="n">
-        <v>9171</v>
+        <v>12660</v>
       </c>
     </row>
     <row r="16">
@@ -1214,13 +1808,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.5</v>
+        <v>14.2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>21.7</v>
       </c>
       <c r="D17" t="n">
-        <v>69.90000000000001</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
@@ -1230,19 +1824,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4</v>
+        <v>20.7</v>
       </c>
       <c r="D18" t="n">
-        <v>51.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 17546</t>
+          <t>Day 3 — Active seconds: 20458</t>
         </is>
       </c>
     </row>
@@ -1275,13 +1869,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4807</v>
+        <v>3362</v>
       </c>
       <c r="C23" t="n">
-        <v>218</v>
+        <v>3535</v>
       </c>
       <c r="D23" t="n">
-        <v>12521</v>
+        <v>13561</v>
       </c>
     </row>
     <row r="24">
@@ -1291,13 +1885,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2537</v>
+        <v>2904</v>
       </c>
       <c r="C24" t="n">
-        <v>121</v>
+        <v>3448</v>
       </c>
       <c r="D24" t="n">
-        <v>10287</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="26">
@@ -1329,13 +1923,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.4</v>
+        <v>16.4</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>17.3</v>
       </c>
       <c r="D27" t="n">
-        <v>71.40000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="28">
@@ -1345,19 +1939,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7</v>
+        <v>16.9</v>
       </c>
       <c r="D28" t="n">
-        <v>58.6</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 17030</t>
+          <t>Day 4 — Active seconds: 21521</t>
         </is>
       </c>
     </row>
@@ -1390,13 +1984,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4591</v>
+        <v>2716</v>
       </c>
       <c r="C33" t="n">
-        <v>146</v>
+        <v>4169</v>
       </c>
       <c r="D33" t="n">
-        <v>12293</v>
+        <v>14636</v>
       </c>
     </row>
     <row r="34">
@@ -1406,13 +2000,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2334</v>
+        <v>2488</v>
       </c>
       <c r="C34" t="n">
-        <v>78</v>
+        <v>4038</v>
       </c>
       <c r="D34" t="n">
-        <v>9106</v>
+        <v>13776</v>
       </c>
     </row>
     <row r="36">
@@ -1444,13 +2038,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
+        <v>12.6</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9</v>
+        <v>19.4</v>
       </c>
       <c r="D37" t="n">
-        <v>72.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -1460,19 +2054,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5</v>
+        <v>18.8</v>
       </c>
       <c r="D38" t="n">
-        <v>53.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 16793</t>
+          <t>Day 5 — Active seconds: 22067</t>
         </is>
       </c>
     </row>
@@ -1505,13 +2099,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1871</v>
+        <v>2469</v>
       </c>
       <c r="C43" t="n">
-        <v>60</v>
+        <v>4216</v>
       </c>
       <c r="D43" t="n">
-        <v>14862</v>
+        <v>15382</v>
       </c>
     </row>
     <row r="44">
@@ -1521,13 +2115,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>837</v>
+        <v>2426</v>
       </c>
       <c r="C44" t="n">
-        <v>30</v>
+        <v>4100</v>
       </c>
       <c r="D44" t="n">
-        <v>10839</v>
+        <v>14577</v>
       </c>
     </row>
     <row r="46">
@@ -1559,13 +2153,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4</v>
+        <v>19.1</v>
       </c>
       <c r="D47" t="n">
-        <v>88.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="48">
@@ -1575,13 +2169,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2</v>
+        <v>18.6</v>
       </c>
       <c r="D48" t="n">
-        <v>64.5</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +2195,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 12803</t>
+          <t>Day 1 — Active seconds: 17831</t>
         </is>
       </c>
     </row>
@@ -1634,13 +2228,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>8734</v>
       </c>
       <c r="C3" t="n">
-        <v>11878</v>
+        <v>170</v>
       </c>
       <c r="D3" t="n">
-        <v>911</v>
+        <v>8927</v>
       </c>
     </row>
     <row r="4">
@@ -1650,13 +2244,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="C4" t="n">
-        <v>3182</v>
+        <v>116</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="6">
@@ -1688,13 +2282,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>92.8</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="8">
@@ -1704,19 +2298,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="C8" t="n">
-        <v>24.9</v>
+        <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 12988</t>
+          <t>Day 2 — Active seconds: 20674</t>
         </is>
       </c>
     </row>
@@ -1749,13 +2343,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6833</v>
       </c>
       <c r="C13" t="n">
-        <v>12566</v>
+        <v>166</v>
       </c>
       <c r="D13" t="n">
-        <v>417</v>
+        <v>13675</v>
       </c>
     </row>
     <row r="14">
@@ -1765,13 +2359,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6303</v>
       </c>
       <c r="C14" t="n">
-        <v>5305</v>
+        <v>117</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>12149</v>
       </c>
     </row>
     <row r="16">
@@ -1803,13 +2397,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>33.1</v>
       </c>
       <c r="C17" t="n">
-        <v>96.8</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1819,19 +2413,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="C18" t="n">
-        <v>40.8</v>
+        <v>0.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 14425</t>
+          <t>Day 3 — Active seconds: 20407</t>
         </is>
       </c>
     </row>
@@ -1864,13 +2458,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6561</v>
       </c>
       <c r="C23" t="n">
-        <v>13603</v>
+        <v>134</v>
       </c>
       <c r="D23" t="n">
-        <v>818</v>
+        <v>13712</v>
       </c>
     </row>
     <row r="24">
@@ -1880,13 +2474,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5729</v>
       </c>
       <c r="C24" t="n">
-        <v>5321</v>
+        <v>188</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>12504</v>
       </c>
     </row>
     <row r="26">
@@ -1918,13 +2512,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="C27" t="n">
-        <v>94.3</v>
+        <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>5.7</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="28">
@@ -1934,19 +2528,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="C28" t="n">
-        <v>36.9</v>
+        <v>0.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 14281</t>
+          <t>Day 4 — Active seconds: 20424</t>
         </is>
       </c>
     </row>
@@ -1979,13 +2573,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>6478</v>
       </c>
       <c r="C33" t="n">
-        <v>13547</v>
+        <v>196</v>
       </c>
       <c r="D33" t="n">
-        <v>733</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="34">
@@ -1995,13 +2589,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>5883</v>
       </c>
       <c r="C34" t="n">
-        <v>6050</v>
+        <v>148</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>12012</v>
       </c>
     </row>
     <row r="36">
@@ -2033,13 +2627,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="C37" t="n">
-        <v>94.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>5.1</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="38">
@@ -2049,19 +2643,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="C38" t="n">
-        <v>42.4</v>
+        <v>0.7</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 15776</t>
+          <t>Day 5 — Active seconds: 19332</t>
         </is>
       </c>
     </row>
@@ -2094,13 +2688,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>2782</v>
       </c>
       <c r="C43" t="n">
-        <v>15344</v>
+        <v>95</v>
       </c>
       <c r="D43" t="n">
-        <v>428</v>
+        <v>16455</v>
       </c>
     </row>
     <row r="44">
@@ -2110,13 +2704,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>2267</v>
       </c>
       <c r="C44" t="n">
-        <v>5059</v>
+        <v>49</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>14249</v>
       </c>
     </row>
     <row r="46">
@@ -2148,13 +2742,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="C47" t="n">
-        <v>97.3</v>
+        <v>0.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2.7</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2164,13 +2758,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="C48" t="n">
-        <v>32.1</v>
+        <v>0.3</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>73.7</v>
       </c>
     </row>
   </sheetData>
@@ -2190,7 +2784,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 18260</t>
+          <t>Day 1 — Active seconds: 19278</t>
         </is>
       </c>
     </row>
@@ -2223,13 +2817,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9616</v>
+        <v>9508</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D3" t="n">
-        <v>8644</v>
+        <v>9580</v>
       </c>
     </row>
     <row r="4">
@@ -2239,13 +2833,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8178</v>
+        <v>7956</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="D4" t="n">
-        <v>6371</v>
+        <v>8515</v>
       </c>
     </row>
     <row r="6">
@@ -2277,13 +2871,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52.7</v>
+        <v>49.3</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>47.3</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="8">
@@ -2293,19 +2887,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.8</v>
+        <v>41.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="n">
-        <v>34.9</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 19929</t>
+          <t>Day 2 — Active seconds: 22130</t>
         </is>
       </c>
     </row>
@@ -2338,13 +2932,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7948</v>
+        <v>7345</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D13" t="n">
-        <v>11981</v>
+        <v>14620</v>
       </c>
     </row>
     <row r="14">
@@ -2354,13 +2948,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6605</v>
+        <v>6776</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D14" t="n">
-        <v>9663</v>
+        <v>14289</v>
       </c>
     </row>
     <row r="16">
@@ -2392,13 +2986,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.9</v>
+        <v>33.2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D17" t="n">
-        <v>60.1</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2408,19 +3002,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33.1</v>
+        <v>30.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D18" t="n">
-        <v>48.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 18649</t>
+          <t>Day 3 — Active seconds: 21289</t>
         </is>
       </c>
     </row>
@@ -2453,13 +3047,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8094</v>
+        <v>6984</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="D23" t="n">
-        <v>10555</v>
+        <v>14096</v>
       </c>
     </row>
     <row r="24">
@@ -2469,13 +3063,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5785</v>
+        <v>6043</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="D24" t="n">
-        <v>7263</v>
+        <v>13697</v>
       </c>
     </row>
     <row r="26">
@@ -2507,13 +3101,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>43.4</v>
+        <v>32.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>56.6</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="28">
@@ -2523,19 +3117,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>28.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D28" t="n">
-        <v>38.9</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 19816</t>
+          <t>Day 4 — Active seconds: 21991</t>
         </is>
       </c>
     </row>
@@ -2568,13 +3162,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7636</v>
+        <v>7124</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="D33" t="n">
-        <v>12180</v>
+        <v>14737</v>
       </c>
     </row>
     <row r="34">
@@ -2584,13 +3178,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6699</v>
+        <v>6453</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="D34" t="n">
-        <v>9843</v>
+        <v>14305</v>
       </c>
     </row>
     <row r="36">
@@ -2622,13 +3216,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>38.5</v>
+        <v>32.4</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D37" t="n">
-        <v>61.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
@@ -2638,19 +3232,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>33.8</v>
+        <v>29.3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D38" t="n">
-        <v>49.7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 19805</t>
+          <t>Day 5 — Active seconds: 21831</t>
         </is>
       </c>
     </row>
@@ -2683,13 +3277,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10296</v>
+        <v>3541</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>9509</v>
+        <v>18211</v>
       </c>
     </row>
     <row r="44">
@@ -2699,13 +3293,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8665</v>
+        <v>2893</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D44" t="n">
-        <v>7836</v>
+        <v>17811</v>
       </c>
     </row>
     <row r="46">
@@ -2737,13 +3331,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52</v>
+        <v>16.2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2753,13 +3347,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>43.8</v>
+        <v>13.3</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D48" t="n">
-        <v>39.6</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +3373,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 13909</t>
+          <t>Day 1 — Active seconds: 14630</t>
         </is>
       </c>
     </row>
@@ -2812,13 +3406,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>580</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>11592</v>
+        <v>13654</v>
       </c>
       <c r="D3" t="n">
-        <v>1737</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4">
@@ -2828,13 +3422,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>334</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7433</v>
+        <v>4516</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2866,13 +3460,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>0.1</v>
       </c>
       <c r="C7" t="n">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8">
@@ -2882,10 +3476,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>53.4</v>
+        <v>30.9</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2894,7 +3488,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 13371</t>
+          <t>Day 2 — Active seconds: 16319</t>
         </is>
       </c>
     </row>
@@ -2927,13 +3521,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>12098</v>
+        <v>15814</v>
       </c>
       <c r="D13" t="n">
-        <v>1129</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
@@ -2943,10 +3537,599 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>9126</v>
+        <v>8940</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active seconds: 16080</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15309</v>
+      </c>
+      <c r="D23" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7981</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active seconds: 16366</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15588</v>
+      </c>
+      <c r="D33" t="n">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8763</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active seconds: 17317</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>16875</v>
+      </c>
+      <c r="D43" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7480</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active seconds: 16815</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15817</v>
+      </c>
+      <c r="D3" t="n">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10598</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>63</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active seconds: 19269</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18714</v>
+      </c>
+      <c r="D13" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16294</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
@@ -2981,13 +4164,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>90.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -2997,10 +4180,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>68.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3009,7 +4192,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 15014</t>
+          <t>Day 3 — Active seconds: 19440</t>
         </is>
       </c>
     </row>
@@ -3042,13 +4225,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>490</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13273</v>
+        <v>18615</v>
       </c>
       <c r="D23" t="n">
-        <v>1251</v>
+        <v>803</v>
       </c>
     </row>
     <row r="24">
@@ -3058,13 +4241,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>346</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>9501</v>
+        <v>15745</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -3096,13 +4279,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="C27" t="n">
-        <v>88.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="D27" t="n">
-        <v>8.300000000000001</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28">
@@ -3112,10 +4295,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="C28" t="n">
-        <v>63.3</v>
+        <v>81</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -3124,7 +4307,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 16393</t>
+          <t>Day 4 — Active seconds: 19294</t>
         </is>
       </c>
     </row>
@@ -3157,13 +4340,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>429</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>14964</v>
+        <v>18489</v>
       </c>
       <c r="D33" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
     </row>
     <row r="34">
@@ -3173,13 +4356,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>265</v>
+        <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>10592</v>
+        <v>16128</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3211,13 +4394,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="C37" t="n">
-        <v>91.3</v>
+        <v>95.8</v>
       </c>
       <c r="D37" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="38">
@@ -3227,10 +4410,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="C38" t="n">
-        <v>64.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3239,7 +4422,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 16456</t>
+          <t>Day 5 — Active seconds: 20491</t>
         </is>
       </c>
     </row>
@@ -3272,13 +4455,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>427</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
-        <v>14729</v>
+        <v>19991</v>
       </c>
       <c r="D43" t="n">
-        <v>1300</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44">
@@ -3288,13 +4471,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>265</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9966</v>
+        <v>16133</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3326,13 +4509,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="C47" t="n">
-        <v>89.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="48">
@@ -3342,13 +4525,1780 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>60.6</v>
+        <v>78.7</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active seconds: 20307</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11323</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8984</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10669</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active seconds: 21206</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8829</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12377</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8158</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11009</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active seconds: 20249</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9370</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10879</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8662</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9094</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active seconds: 20938</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12529</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7961</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10872</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>38</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active seconds: 21295</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11403</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9892</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>10625</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active seconds: 21077</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11837</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11277</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8130</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active seconds: 21893</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9230</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12663</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8635</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11790</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active seconds: 21132</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9915</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11217</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9322</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10008</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active seconds: 21868</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8960</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12908</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8554</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11924</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>41</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active seconds: 21834</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11701</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>10133</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>10899</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9507</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active seconds: 15082</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>648</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12660</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>463</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8763</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active seconds: 14021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>147</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12631</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>114</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9964</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active seconds: 15847</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>564</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13952</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>436</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10650</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>88</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active seconds: 17780</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>478</v>
+      </c>
+      <c r="C33" t="n">
+        <v>16208</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>318</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12447</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>70</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active seconds: 17755</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>487</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15979</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>352</v>
+      </c>
+      <c r="C44" t="n">
+        <v>11888</v>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C47" t="n">
+        <v>90</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>67</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -7,16 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AAPL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AAPL_back" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AMZN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AMZN_back" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="GE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GE_back" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="IVV" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="IVV_back" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="M" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="M_back" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="AAPL_Opt_F" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AAPL_Opt_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AAPL_Base_F" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AAPL_Base_B" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="AMZN_Opt_F" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AMZN_Opt_B" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AMZN_Base_F" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AMZN_Base_B" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GE_Opt_F" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="GE_Opt_B" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GE_Base_F" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GE_Base_B" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IVV_Opt_F" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="IVV_Opt_B" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="IVV_Base_F" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="IVV_Base_B" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="M_Opt_F" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="M_Opt_B" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="M_Base_F" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="M_Base_B" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +438,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 13013</t>
+          <t>Day 1 — Active bid: 12757 ask: 13216</t>
         </is>
       </c>
     </row>
@@ -461,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1788</v>
+        <v>741</v>
       </c>
       <c r="C3" t="n">
-        <v>2104</v>
+        <v>1468</v>
       </c>
       <c r="D3" t="n">
-        <v>9121</v>
+        <v>10548</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1199</v>
+        <v>861</v>
       </c>
       <c r="C4" t="n">
-        <v>1531</v>
+        <v>1614</v>
       </c>
       <c r="D4" t="n">
-        <v>4041</v>
+        <v>10741</v>
       </c>
     </row>
     <row r="6">
@@ -515,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.7</v>
+        <v>5.8</v>
       </c>
       <c r="C7" t="n">
-        <v>16.2</v>
+        <v>11.5</v>
       </c>
       <c r="D7" t="n">
-        <v>70.09999999999999</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="8">
@@ -531,19 +541,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="C8" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="D8" t="n">
-        <v>31.1</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 15868</t>
+          <t>Day 2 — Active bid: 15575 ask: 15928</t>
         </is>
       </c>
     </row>
@@ -576,13 +586,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1508</v>
+        <v>667</v>
       </c>
       <c r="C13" t="n">
-        <v>2900</v>
+        <v>1389</v>
       </c>
       <c r="D13" t="n">
-        <v>11460</v>
+        <v>13519</v>
       </c>
     </row>
     <row r="14">
@@ -592,13 +602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1205</v>
+        <v>834</v>
       </c>
       <c r="C14" t="n">
-        <v>2473</v>
+        <v>1500</v>
       </c>
       <c r="D14" t="n">
-        <v>7061</v>
+        <v>13594</v>
       </c>
     </row>
     <row r="16">
@@ -630,13 +640,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="C17" t="n">
-        <v>18.3</v>
+        <v>8.9</v>
       </c>
       <c r="D17" t="n">
-        <v>72.2</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="18">
@@ -646,19 +656,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="C18" t="n">
-        <v>15.6</v>
+        <v>9.4</v>
       </c>
       <c r="D18" t="n">
-        <v>44.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 15422</t>
+          <t>Day 3 — Active bid: 15240 ask: 15275</t>
         </is>
       </c>
     </row>
@@ -691,13 +701,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1864</v>
+        <v>784</v>
       </c>
       <c r="C23" t="n">
-        <v>1932</v>
+        <v>1818</v>
       </c>
       <c r="D23" t="n">
-        <v>11626</v>
+        <v>12638</v>
       </c>
     </row>
     <row r="24">
@@ -707,13 +717,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1352</v>
+        <v>825</v>
       </c>
       <c r="C24" t="n">
-        <v>1479</v>
+        <v>1815</v>
       </c>
       <c r="D24" t="n">
-        <v>7149</v>
+        <v>12635</v>
       </c>
     </row>
     <row r="26">
@@ -745,13 +755,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.1</v>
+        <v>5.1</v>
       </c>
       <c r="C27" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="D27" t="n">
-        <v>75.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -761,19 +771,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="C28" t="n">
-        <v>9.6</v>
+        <v>11.9</v>
       </c>
       <c r="D28" t="n">
-        <v>46.4</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 15957</t>
+          <t>Day 4 — Active bid: 15785 ask: 15740</t>
         </is>
       </c>
     </row>
@@ -806,13 +816,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1366</v>
+        <v>712</v>
       </c>
       <c r="C33" t="n">
-        <v>2581</v>
+        <v>1257</v>
       </c>
       <c r="D33" t="n">
-        <v>12010</v>
+        <v>13816</v>
       </c>
     </row>
     <row r="34">
@@ -822,13 +832,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1087</v>
+        <v>802</v>
       </c>
       <c r="C34" t="n">
-        <v>2182</v>
+        <v>1253</v>
       </c>
       <c r="D34" t="n">
-        <v>7400</v>
+        <v>13685</v>
       </c>
     </row>
     <row r="36">
@@ -860,13 +870,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="C37" t="n">
-        <v>16.2</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>75.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="38">
@@ -876,19 +886,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="C38" t="n">
-        <v>13.7</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>46.4</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 16699</t>
+          <t>Day 5 — Active bid: 16547 ask: 16051</t>
         </is>
       </c>
     </row>
@@ -921,13 +931,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1196</v>
+        <v>599</v>
       </c>
       <c r="C43" t="n">
-        <v>2669</v>
+        <v>1000</v>
       </c>
       <c r="D43" t="n">
-        <v>12834</v>
+        <v>14948</v>
       </c>
     </row>
     <row r="44">
@@ -937,13 +947,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1015</v>
+        <v>769</v>
       </c>
       <c r="C44" t="n">
-        <v>2249</v>
+        <v>1014</v>
       </c>
       <c r="D44" t="n">
-        <v>8213</v>
+        <v>14268</v>
       </c>
     </row>
     <row r="46">
@@ -975,13 +985,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>76.90000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="48">
@@ -991,13 +1001,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="C48" t="n">
-        <v>13.5</v>
+        <v>6.3</v>
       </c>
       <c r="D48" t="n">
-        <v>49.2</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1027,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 18175</t>
+          <t>Day 1 — Active bid: 23401 ask: 23401</t>
         </is>
       </c>
     </row>
@@ -1050,13 +1060,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>814</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>15665</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>1696</v>
+        <v>23361</v>
       </c>
     </row>
     <row r="4">
@@ -1066,13 +1076,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>529</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>13372</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>23368</v>
       </c>
     </row>
     <row r="6">
@@ -1104,13 +1114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="C7" t="n">
-        <v>86.2</v>
+        <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>9.300000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="8">
@@ -1120,19 +1130,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>73.59999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 18250</t>
+          <t>Day 2 — Active bid: 23401 ask: 23401</t>
         </is>
       </c>
     </row>
@@ -1165,13 +1175,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>16922</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>1108</v>
+        <v>23386</v>
       </c>
     </row>
     <row r="14">
@@ -1181,13 +1191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>15429</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>23389</v>
       </c>
     </row>
     <row r="16">
@@ -1219,13 +1229,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>92.7</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.1</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1235,19 +1245,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>84.5</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 19224</t>
+          <t>Day 3 — Active bid: 23401 ask: 23401</t>
         </is>
       </c>
     </row>
@@ -1280,13 +1290,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>619</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>17319</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>1286</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="24">
@@ -1296,13 +1306,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>463</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>15519</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>23393</v>
       </c>
     </row>
     <row r="26">
@@ -1334,13 +1344,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>90.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>6.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1350,19 +1360,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>80.7</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 19386</t>
+          <t>Day 4 — Active bid: 23401 ask: 23401</t>
         </is>
       </c>
     </row>
@@ -1395,13 +1405,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>515</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>17888</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>983</v>
+        <v>23393</v>
       </c>
     </row>
     <row r="34">
@@ -1411,13 +1421,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>338</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>16135</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>23396</v>
       </c>
     </row>
     <row r="36">
@@ -1449,13 +1459,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>92.3</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>5.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -1465,19 +1475,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>83.2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 19624</t>
+          <t>Day 5 — Active bid: 23401 ask: 23401</t>
         </is>
       </c>
     </row>
@@ -1510,13 +1520,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>561</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>17896</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>1167</v>
+        <v>23394</v>
       </c>
     </row>
     <row r="44">
@@ -1526,13 +1536,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>377</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>15750</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="46">
@@ -1564,13 +1574,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>5.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -1580,13 +1590,5314 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 14605 ask: 9576</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13640</v>
+      </c>
+      <c r="D3" t="n">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8598</v>
+      </c>
+      <c r="D4" t="n">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 16319 ask: 13632</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15824</v>
+      </c>
+      <c r="D13" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>13061</v>
+      </c>
+      <c r="D14" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>97</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 16086 ask: 12836</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15325</v>
+      </c>
+      <c r="D23" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>12065</v>
+      </c>
+      <c r="D24" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>94</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 16360 ask: 13354</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15594</v>
+      </c>
+      <c r="D33" t="n">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12646</v>
+      </c>
+      <c r="D34" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 17308 ask: 10896</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>16864</v>
+      </c>
+      <c r="D43" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10481</v>
+      </c>
+      <c r="D44" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 19247 ask: 19455</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>18177</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18366</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 21564 ask: 21554</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20988</v>
+      </c>
+      <c r="D13" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20937</v>
+      </c>
+      <c r="D14" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 20804 ask: 21049</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19988</v>
+      </c>
+      <c r="D23" t="n">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>20220</v>
+      </c>
+      <c r="D24" t="n">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 21295 ask: 21350</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" t="n">
+        <v>20477</v>
+      </c>
+      <c r="D33" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>41</v>
+      </c>
+      <c r="C34" t="n">
+        <v>20554</v>
+      </c>
+      <c r="D34" t="n">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 21942 ask: 21760</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>13</v>
+      </c>
+      <c r="C43" t="n">
+        <v>21441</v>
+      </c>
+      <c r="D43" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>21284</v>
+      </c>
+      <c r="D44" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 22441 ask: 22474</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1468</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2137</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18836</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1487</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2155</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18832</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>83.90000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 22907 ask: 22868</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1131</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20646</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1134</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1143</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20591</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>90.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 22169 ask: 21914</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1446</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1157</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19566</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1426</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19320</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 22768 ask: 22638</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1374</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20255</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1429</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20010</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>88.40000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 22726 ask: 22788</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2090</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18916</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D44" t="n">
+        <v>18923</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 23259 ask: 23223</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1627</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2233</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1539</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2264</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19420</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 23224 ask: 23268</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1191</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20866</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20967</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>90.09999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 23005 ask: 23103</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D23" t="n">
+        <v>20168</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1598</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1245</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20260</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 23243 ask: 23127</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1179</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20602</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1521</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20414</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 23065 ask: 23257</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2209</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D43" t="n">
+        <v>19075</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1701</v>
+      </c>
+      <c r="D44" t="n">
+        <v>19286</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 18721 ask: 19055</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14388</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1724</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14368</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 19391 ask: 18097</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1378</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15447</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1161</v>
+      </c>
+      <c r="C14" t="n">
+        <v>14687</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 18945 ask: 18124</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1506</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14431</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1423</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13896</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 18324 ask: 17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C33" t="n">
+        <v>13957</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1473</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12744</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>75</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 20024 ask: 19037</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1661</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15953</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15468</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 20401 ask: 20925</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16063</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2061</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16118</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>77</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 21170 ask: 20490</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1489</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17496</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1390</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17181</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 20723 ask: 20410</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1785</v>
+      </c>
+      <c r="C23" t="n">
+        <v>16308</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1857</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16054</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 19971 ask: 20140</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1607</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15869</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1821</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15662</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 21124 ask: 20646</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17188</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1515</v>
+      </c>
+      <c r="C44" t="n">
+        <v>16965</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 21234 ask: 21085</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>390</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20844</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>362</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20723</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>98.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 22155 ask: 22385</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>260</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21895</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>220</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 22230 ask: 22024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>380</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>21850</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>331</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>21693</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 22399 ask: 22259</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>415</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21984</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>365</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>21894</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>1.9</v>
       </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 22347 ask: 22183</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>439</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>21908</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>403</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>21780</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.8</v>
+      </c>
       <c r="C48" t="n">
-        <v>80.3</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
+        <v>98.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 23326 ask: 23303</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>664</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22662</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>678</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 23373 ask: 23367</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>364</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23009</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>350</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 23311 ask: 23309</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>450</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>22861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>470</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>22839</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 23340 ask: 23271</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>512</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>22828</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>485</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22786</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 23307 ask: 23296</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>536</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>22771</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>526</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>22770</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>97.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 15083 ask: 15153</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13297</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13422</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 14032 ask: 17330</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12797</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16174</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 15845 ask: 16672</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15385</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 17786 ask: 16709</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15697</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 17744 ask: 16146</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>21</v>
+      </c>
+      <c r="C43" t="n">
+        <v>16415</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15128</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6917,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 18090</t>
+          <t>Day 1 — Active bid: 17252 ask: 17557</t>
         </is>
       </c>
     </row>
@@ -1639,13 +6950,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3663</v>
+        <v>1763</v>
       </c>
       <c r="C3" t="n">
-        <v>3436</v>
+        <v>2196</v>
       </c>
       <c r="D3" t="n">
-        <v>10991</v>
+        <v>13293</v>
       </c>
     </row>
     <row r="4">
@@ -1655,13 +6966,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3001</v>
+        <v>1895</v>
       </c>
       <c r="C4" t="n">
-        <v>3277</v>
+        <v>2367</v>
       </c>
       <c r="D4" t="n">
-        <v>8975</v>
+        <v>13295</v>
       </c>
     </row>
     <row r="6">
@@ -1693,13 +7004,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.2</v>
+        <v>10.2</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>12.7</v>
       </c>
       <c r="D7" t="n">
-        <v>60.8</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1709,19 +7020,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.6</v>
+        <v>10.8</v>
       </c>
       <c r="C8" t="n">
-        <v>18.1</v>
+        <v>13.5</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 21108</t>
+          <t>Day 2 — Active bid: 20056 ask: 20355</t>
         </is>
       </c>
     </row>
@@ -1754,13 +7065,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2990</v>
+        <v>1506</v>
       </c>
       <c r="C13" t="n">
-        <v>4575</v>
+        <v>2067</v>
       </c>
       <c r="D13" t="n">
-        <v>13543</v>
+        <v>16483</v>
       </c>
     </row>
     <row r="14">
@@ -1770,13 +7081,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2629</v>
+        <v>1580</v>
       </c>
       <c r="C14" t="n">
-        <v>4368</v>
+        <v>2209</v>
       </c>
       <c r="D14" t="n">
-        <v>12660</v>
+        <v>16566</v>
       </c>
     </row>
     <row r="16">
@@ -1808,13 +7119,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.2</v>
+        <v>7.5</v>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>10.3</v>
       </c>
       <c r="D17" t="n">
-        <v>64.2</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="18">
@@ -1824,19 +7135,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="C18" t="n">
-        <v>20.7</v>
+        <v>10.9</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 20458</t>
+          <t>Day 3 — Active bid: 19614 ask: 19729</t>
         </is>
       </c>
     </row>
@@ -1869,13 +7180,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3362</v>
+        <v>1705</v>
       </c>
       <c r="C23" t="n">
-        <v>3535</v>
+        <v>2538</v>
       </c>
       <c r="D23" t="n">
-        <v>13561</v>
+        <v>15371</v>
       </c>
     </row>
     <row r="24">
@@ -1885,13 +7196,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2904</v>
+        <v>1711</v>
       </c>
       <c r="C24" t="n">
-        <v>3448</v>
+        <v>2569</v>
       </c>
       <c r="D24" t="n">
-        <v>12290</v>
+        <v>15449</v>
       </c>
     </row>
     <row r="26">
@@ -1923,13 +7234,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>17.3</v>
+        <v>12.9</v>
       </c>
       <c r="D27" t="n">
-        <v>66.3</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1939,19 +7250,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>16.9</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>60.1</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 21521</t>
+          <t>Day 4 — Active bid: 20633 ask: 20586</t>
         </is>
       </c>
     </row>
@@ -1984,13 +7295,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2716</v>
+        <v>1552</v>
       </c>
       <c r="C33" t="n">
-        <v>4169</v>
+        <v>1772</v>
       </c>
       <c r="D33" t="n">
-        <v>14636</v>
+        <v>17309</v>
       </c>
     </row>
     <row r="34">
@@ -2000,13 +7311,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2488</v>
+        <v>1601</v>
       </c>
       <c r="C34" t="n">
-        <v>4038</v>
+        <v>1830</v>
       </c>
       <c r="D34" t="n">
-        <v>13776</v>
+        <v>17155</v>
       </c>
     </row>
     <row r="36">
@@ -2038,13 +7349,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12.6</v>
+        <v>7.5</v>
       </c>
       <c r="C37" t="n">
-        <v>19.4</v>
+        <v>8.6</v>
       </c>
       <c r="D37" t="n">
-        <v>68</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2054,19 +7365,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.6</v>
+        <v>7.8</v>
       </c>
       <c r="C38" t="n">
-        <v>18.8</v>
+        <v>8.9</v>
       </c>
       <c r="D38" t="n">
-        <v>64</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 22067</t>
+          <t>Day 5 — Active bid: 21449 ask: 21248</t>
         </is>
       </c>
     </row>
@@ -2099,13 +7410,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2469</v>
+        <v>1455</v>
       </c>
       <c r="C43" t="n">
-        <v>4216</v>
+        <v>1550</v>
       </c>
       <c r="D43" t="n">
-        <v>15382</v>
+        <v>18444</v>
       </c>
     </row>
     <row r="44">
@@ -2115,13 +7426,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2426</v>
+        <v>1582</v>
       </c>
       <c r="C44" t="n">
-        <v>4100</v>
+        <v>1532</v>
       </c>
       <c r="D44" t="n">
-        <v>14577</v>
+        <v>18134</v>
       </c>
     </row>
     <row r="46">
@@ -2153,13 +7464,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11.2</v>
+        <v>6.8</v>
       </c>
       <c r="C47" t="n">
-        <v>19.1</v>
+        <v>7.2</v>
       </c>
       <c r="D47" t="n">
-        <v>69.7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48">
@@ -2169,13 +7480,602 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="C48" t="n">
-        <v>18.6</v>
+        <v>7.2</v>
       </c>
       <c r="D48" t="n">
-        <v>66.09999999999999</v>
+        <v>85.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Day 1 — Active bid: 19824 ask: 19291</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>171</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17942</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>188</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17626</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Day 2 — Active bid: 20397 ask: 20523</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>66</v>
+      </c>
+      <c r="C13" t="n">
+        <v>19209</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>71</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19443</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Day 3 — Active bid: 20983 ask: 20714</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>125</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19682</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>108</v>
+      </c>
+      <c r="C24" t="n">
+        <v>19554</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Day 4 — Active bid: 20416 ask: 20644</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>59</v>
+      </c>
+      <c r="C33" t="n">
+        <v>19294</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>74</v>
+      </c>
+      <c r="C34" t="n">
+        <v>19528</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Day 5 — Active bid: 20497 ask: 20355</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>85</v>
+      </c>
+      <c r="C43" t="n">
+        <v>19269</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>68</v>
+      </c>
+      <c r="C44" t="n">
+        <v>19275</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Percentages (%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inside NBBO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>At NBBO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Outside NBBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>94</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +8095,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 17831</t>
+          <t>Day 1 — Active bid: 9967 ask: 10607</t>
         </is>
       </c>
     </row>
@@ -2228,13 +8128,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8734</v>
+        <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>170</v>
+        <v>5790</v>
       </c>
       <c r="D3" t="n">
-        <v>8927</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="4">
@@ -2244,13 +8144,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7272</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>6423</v>
       </c>
       <c r="D4" t="n">
-        <v>6710</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="6">
@@ -2282,13 +8182,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>58.1</v>
       </c>
       <c r="D7" t="n">
-        <v>50.1</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="8">
@@ -2298,19 +8198,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40.8</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>60.6</v>
       </c>
       <c r="D8" t="n">
-        <v>37.6</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 20674</t>
+          <t>Day 2 — Active bid: 11238 ask: 12199</t>
         </is>
       </c>
     </row>
@@ -2343,13 +8243,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6833</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>166</v>
+        <v>7508</v>
       </c>
       <c r="D13" t="n">
-        <v>13675</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="14">
@@ -2359,13 +8259,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6303</v>
+        <v>181</v>
       </c>
       <c r="C14" t="n">
-        <v>117</v>
+        <v>8273</v>
       </c>
       <c r="D14" t="n">
-        <v>12149</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="16">
@@ -2397,13 +8297,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33.1</v>
+        <v>0.4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8</v>
+        <v>66.8</v>
       </c>
       <c r="D17" t="n">
-        <v>66.09999999999999</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="18">
@@ -2413,19 +8313,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.5</v>
+        <v>1.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>67.8</v>
       </c>
       <c r="D18" t="n">
-        <v>58.8</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 20407</t>
+          <t>Day 3 — Active bid: 11934 ask: 11561</t>
         </is>
       </c>
     </row>
@@ -2458,13 +8358,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6561</v>
+        <v>141</v>
       </c>
       <c r="C23" t="n">
-        <v>134</v>
+        <v>7762</v>
       </c>
       <c r="D23" t="n">
-        <v>13712</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="24">
@@ -2474,13 +8374,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5729</v>
+        <v>117</v>
       </c>
       <c r="C24" t="n">
-        <v>188</v>
+        <v>7589</v>
       </c>
       <c r="D24" t="n">
-        <v>12504</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="26">
@@ -2512,13 +8412,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.2</v>
+        <v>1.2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7</v>
+        <v>65</v>
       </c>
       <c r="D27" t="n">
-        <v>67.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="28">
@@ -2528,19 +8428,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.1</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>61.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 20424</t>
+          <t>Day 4 — Active bid: 12053 ask: 11262</t>
         </is>
       </c>
     </row>
@@ -2573,13 +8473,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6478</v>
+        <v>61</v>
       </c>
       <c r="C33" t="n">
-        <v>196</v>
+        <v>8005</v>
       </c>
       <c r="D33" t="n">
-        <v>13750</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="34">
@@ -2589,13 +8489,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5883</v>
+        <v>60</v>
       </c>
       <c r="C34" t="n">
-        <v>148</v>
+        <v>7630</v>
       </c>
       <c r="D34" t="n">
-        <v>12012</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="36">
@@ -2627,13 +8527,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.7</v>
+        <v>0.5</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>67.3</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="38">
@@ -2643,19 +8543,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.8</v>
+        <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7</v>
+        <v>67.7</v>
       </c>
       <c r="D38" t="n">
-        <v>58.8</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 19332</t>
+          <t>Day 5 — Active bid: 11769 ask: 11732</t>
         </is>
       </c>
     </row>
@@ -2688,13 +8588,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2782</v>
+        <v>37</v>
       </c>
       <c r="C43" t="n">
-        <v>95</v>
+        <v>7828</v>
       </c>
       <c r="D43" t="n">
-        <v>16455</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="44">
@@ -2704,13 +8604,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2267</v>
+        <v>93</v>
       </c>
       <c r="C44" t="n">
-        <v>49</v>
+        <v>8254</v>
       </c>
       <c r="D44" t="n">
-        <v>14249</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="46">
@@ -2742,13 +8642,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.4</v>
+        <v>0.3</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5</v>
+        <v>66.5</v>
       </c>
       <c r="D47" t="n">
-        <v>85.09999999999999</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="48">
@@ -2758,13 +8658,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>73.7</v>
+        <v>28.9</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +8684,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 19278</t>
+          <t>Day 1 — Active bid: 11901 ask: 12077</t>
         </is>
       </c>
     </row>
@@ -2817,13 +8717,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9508</v>
+        <v>274</v>
       </c>
       <c r="C3" t="n">
-        <v>190</v>
+        <v>7235</v>
       </c>
       <c r="D3" t="n">
-        <v>9580</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="4">
@@ -2833,13 +8733,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7956</v>
+        <v>268</v>
       </c>
       <c r="C4" t="n">
-        <v>171</v>
+        <v>7555</v>
       </c>
       <c r="D4" t="n">
-        <v>8515</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="6">
@@ -2871,13 +8771,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.3</v>
+        <v>2.3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>60.8</v>
       </c>
       <c r="D7" t="n">
-        <v>49.7</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="8">
@@ -2887,19 +8787,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.3</v>
+        <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>62.6</v>
       </c>
       <c r="D8" t="n">
-        <v>44.2</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 22130</t>
+          <t>Day 2 — Active bid: 13998 ask: 14001</t>
         </is>
       </c>
     </row>
@@ -2932,13 +8832,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7345</v>
+        <v>310</v>
       </c>
       <c r="C13" t="n">
-        <v>165</v>
+        <v>9845</v>
       </c>
       <c r="D13" t="n">
-        <v>14620</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="14">
@@ -2948,13 +8848,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6776</v>
+        <v>484</v>
       </c>
       <c r="C14" t="n">
-        <v>125</v>
+        <v>9820</v>
       </c>
       <c r="D14" t="n">
-        <v>14289</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="16">
@@ -2986,13 +8886,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33.2</v>
+        <v>2.2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7</v>
+        <v>70.3</v>
       </c>
       <c r="D17" t="n">
-        <v>66.09999999999999</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="18">
@@ -3002,19 +8902,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.6</v>
+        <v>3.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>64.59999999999999</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 21289</t>
+          <t>Day 3 — Active bid: 14075 ask: 13656</t>
         </is>
       </c>
     </row>
@@ -3047,13 +8947,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6984</v>
+        <v>444</v>
       </c>
       <c r="C23" t="n">
-        <v>209</v>
+        <v>9534</v>
       </c>
       <c r="D23" t="n">
-        <v>14096</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="24">
@@ -3063,13 +8963,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6043</v>
+        <v>450</v>
       </c>
       <c r="C24" t="n">
-        <v>135</v>
+        <v>9516</v>
       </c>
       <c r="D24" t="n">
-        <v>13697</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="26">
@@ -3101,13 +9001,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.8</v>
+        <v>3.2</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>67.7</v>
       </c>
       <c r="D27" t="n">
-        <v>66.2</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="28">
@@ -3117,19 +9017,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.4</v>
+        <v>3.3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6</v>
+        <v>69.7</v>
       </c>
       <c r="D28" t="n">
-        <v>64.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 21991</t>
+          <t>Day 4 — Active bid: 14540 ask: 13035</t>
         </is>
       </c>
     </row>
@@ -3162,13 +9062,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7124</v>
+        <v>349</v>
       </c>
       <c r="C33" t="n">
-        <v>130</v>
+        <v>10003</v>
       </c>
       <c r="D33" t="n">
-        <v>14737</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="34">
@@ -3178,13 +9078,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6453</v>
+        <v>309</v>
       </c>
       <c r="C34" t="n">
-        <v>181</v>
+        <v>9378</v>
       </c>
       <c r="D34" t="n">
-        <v>14305</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="36">
@@ -3216,13 +9116,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.4</v>
+        <v>2.4</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6</v>
+        <v>68.8</v>
       </c>
       <c r="D37" t="n">
-        <v>67</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="38">
@@ -3232,19 +9132,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.3</v>
+        <v>2.4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>65</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 21831</t>
+          <t>Day 5 — Active bid: 14546 ask: 13533</t>
         </is>
       </c>
     </row>
@@ -3277,13 +9177,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3541</v>
+        <v>219</v>
       </c>
       <c r="C43" t="n">
-        <v>79</v>
+        <v>10403</v>
       </c>
       <c r="D43" t="n">
-        <v>18211</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="44">
@@ -3293,13 +9193,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2893</v>
+        <v>382</v>
       </c>
       <c r="C44" t="n">
-        <v>63</v>
+        <v>9747</v>
       </c>
       <c r="D44" t="n">
-        <v>17811</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="46">
@@ -3331,13 +9231,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.2</v>
+        <v>1.5</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4</v>
+        <v>71.5</v>
       </c>
       <c r="D47" t="n">
-        <v>83.40000000000001</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -3347,13 +9247,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13.3</v>
+        <v>2.8</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3</v>
+        <v>72</v>
       </c>
       <c r="D48" t="n">
-        <v>81.59999999999999</v>
+        <v>25.2</v>
       </c>
     </row>
   </sheetData>
@@ -3373,7 +9273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 14630</t>
+          <t>Day 1 — Active bid: 17337 ask: 17437</t>
         </is>
       </c>
     </row>
@@ -3406,13 +9306,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>10266</v>
       </c>
       <c r="C3" t="n">
-        <v>13654</v>
+        <v>262</v>
       </c>
       <c r="D3" t="n">
-        <v>962</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="4">
@@ -3422,13 +9322,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>10372</v>
       </c>
       <c r="C4" t="n">
-        <v>4516</v>
+        <v>276</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="6">
@@ -3460,13 +9360,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>59.2</v>
       </c>
       <c r="C7" t="n">
-        <v>93.3</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.6</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="8">
@@ -3476,19 +9376,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="C8" t="n">
-        <v>30.9</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 16319</t>
+          <t>Day 2 — Active bid: 19706 ask: 19604</t>
         </is>
       </c>
     </row>
@@ -3521,13 +9421,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>10061</v>
       </c>
       <c r="C13" t="n">
-        <v>15814</v>
+        <v>336</v>
       </c>
       <c r="D13" t="n">
-        <v>500</v>
+        <v>9309</v>
       </c>
     </row>
     <row r="14">
@@ -3537,13 +9437,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>10069</v>
       </c>
       <c r="C14" t="n">
-        <v>8940</v>
+        <v>318</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>9217</v>
       </c>
     </row>
     <row r="16">
@@ -3575,13 +9475,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>51.1</v>
       </c>
       <c r="C17" t="n">
-        <v>96.90000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="18">
@@ -3591,19 +9491,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>51.4</v>
       </c>
       <c r="C18" t="n">
-        <v>54.8</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 16080</t>
+          <t>Day 3 — Active bid: 19542 ask: 19981</t>
         </is>
       </c>
     </row>
@@ -3636,13 +9536,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>9712</v>
       </c>
       <c r="C23" t="n">
-        <v>15309</v>
+        <v>514</v>
       </c>
       <c r="D23" t="n">
-        <v>761</v>
+        <v>9316</v>
       </c>
     </row>
     <row r="24">
@@ -3652,13 +9552,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>9951</v>
       </c>
       <c r="C24" t="n">
-        <v>7981</v>
+        <v>539</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>9491</v>
       </c>
     </row>
     <row r="26">
@@ -3690,13 +9590,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1</v>
+        <v>49.7</v>
       </c>
       <c r="C27" t="n">
-        <v>95.2</v>
+        <v>2.6</v>
       </c>
       <c r="D27" t="n">
-        <v>4.7</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="28">
@@ -3706,19 +9606,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1</v>
+        <v>49.8</v>
       </c>
       <c r="C28" t="n">
-        <v>49.6</v>
+        <v>2.7</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 16366</t>
+          <t>Day 4 — Active bid: 19466 ask: 19594</t>
         </is>
       </c>
     </row>
@@ -3751,13 +9651,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>8464</v>
       </c>
       <c r="C33" t="n">
-        <v>15588</v>
+        <v>517</v>
       </c>
       <c r="D33" t="n">
-        <v>772</v>
+        <v>10485</v>
       </c>
     </row>
     <row r="34">
@@ -3767,13 +9667,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>8690</v>
       </c>
       <c r="C34" t="n">
-        <v>8763</v>
+        <v>508</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="36">
@@ -3805,13 +9705,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="C37" t="n">
-        <v>95.2</v>
+        <v>2.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="38">
@@ -3821,19 +9721,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="C38" t="n">
-        <v>53.5</v>
+        <v>2.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 17317</t>
+          <t>Day 5 — Active bid: 18452 ask: 18622</t>
         </is>
       </c>
     </row>
@@ -3866,13 +9766,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>4527</v>
       </c>
       <c r="C43" t="n">
-        <v>16875</v>
+        <v>295</v>
       </c>
       <c r="D43" t="n">
-        <v>441</v>
+        <v>13630</v>
       </c>
     </row>
     <row r="44">
@@ -3882,13 +9782,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>4561</v>
       </c>
       <c r="C44" t="n">
-        <v>7480</v>
+        <v>356</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>13705</v>
       </c>
     </row>
     <row r="46">
@@ -3920,13 +9820,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="C47" t="n">
-        <v>97.40000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="D47" t="n">
-        <v>2.5</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3936,13 +9836,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="C48" t="n">
-        <v>43.2</v>
+        <v>1.9</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3962,7 +9862,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 16815</t>
+          <t>Day 1 — Active bid: 18272 ask: 18370</t>
         </is>
       </c>
     </row>
@@ -3995,13 +9895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>10743</v>
       </c>
       <c r="C3" t="n">
-        <v>15817</v>
+        <v>277</v>
       </c>
       <c r="D3" t="n">
-        <v>963</v>
+        <v>7252</v>
       </c>
     </row>
     <row r="4">
@@ -4011,13 +9911,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>10924</v>
       </c>
       <c r="C4" t="n">
-        <v>10598</v>
+        <v>287</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7159</v>
       </c>
     </row>
     <row r="6">
@@ -4049,13 +9949,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>58.8</v>
       </c>
       <c r="C7" t="n">
-        <v>94.09999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="8">
@@ -4065,19 +9965,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 19269</t>
+          <t>Day 2 — Active bid: 20651 ask: 20715</t>
         </is>
       </c>
     </row>
@@ -4110,13 +10010,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10544</v>
       </c>
       <c r="C13" t="n">
-        <v>18714</v>
+        <v>350</v>
       </c>
       <c r="D13" t="n">
-        <v>546</v>
+        <v>9757</v>
       </c>
     </row>
     <row r="14">
@@ -4126,13 +10026,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>10609</v>
       </c>
       <c r="C14" t="n">
-        <v>16294</v>
+        <v>339</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>9767</v>
       </c>
     </row>
     <row r="16">
@@ -4164,13 +10064,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>51.1</v>
       </c>
       <c r="C17" t="n">
-        <v>97.09999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="18">
@@ -4180,19 +10080,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="C18" t="n">
-        <v>84.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 19440</t>
+          <t>Day 3 — Active bid: 20426 ask: 20850</t>
         </is>
       </c>
     </row>
@@ -4225,13 +10125,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>10217</v>
       </c>
       <c r="C23" t="n">
-        <v>18615</v>
+        <v>541</v>
       </c>
       <c r="D23" t="n">
-        <v>803</v>
+        <v>9668</v>
       </c>
     </row>
     <row r="24">
@@ -4241,13 +10141,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>10510</v>
       </c>
       <c r="C24" t="n">
-        <v>15745</v>
+        <v>565</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>9775</v>
       </c>
     </row>
     <row r="26">
@@ -4279,13 +10179,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1</v>
+        <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>95.8</v>
+        <v>2.6</v>
       </c>
       <c r="D27" t="n">
-        <v>4.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="28">
@@ -4295,19 +10195,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1</v>
+        <v>50.4</v>
       </c>
       <c r="C28" t="n">
-        <v>81</v>
+        <v>2.7</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 19294</t>
+          <t>Day 4 — Active bid: 20736 ask: 20973</t>
         </is>
       </c>
     </row>
@@ -4340,13 +10240,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>9031</v>
       </c>
       <c r="C33" t="n">
-        <v>18489</v>
+        <v>550</v>
       </c>
       <c r="D33" t="n">
-        <v>790</v>
+        <v>11155</v>
       </c>
     </row>
     <row r="34">
@@ -4356,13 +10256,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17</v>
+        <v>9318</v>
       </c>
       <c r="C34" t="n">
-        <v>16128</v>
+        <v>539</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>11116</v>
       </c>
     </row>
     <row r="36">
@@ -4394,13 +10294,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1</v>
+        <v>43.6</v>
       </c>
       <c r="C37" t="n">
-        <v>95.8</v>
+        <v>2.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="38">
@@ -4410,19 +10310,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1</v>
+        <v>44.4</v>
       </c>
       <c r="C38" t="n">
-        <v>83.59999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 20491</t>
+          <t>Day 5 — Active bid: 20661 ask: 20657</t>
         </is>
       </c>
     </row>
@@ -4455,13 +10355,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>5239</v>
       </c>
       <c r="C43" t="n">
-        <v>19991</v>
+        <v>348</v>
       </c>
       <c r="D43" t="n">
-        <v>487</v>
+        <v>15074</v>
       </c>
     </row>
     <row r="44">
@@ -4471,13 +10371,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>5235</v>
       </c>
       <c r="C44" t="n">
-        <v>16133</v>
+        <v>388</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>15034</v>
       </c>
     </row>
     <row r="46">
@@ -4509,13 +10409,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1</v>
+        <v>25.4</v>
       </c>
       <c r="C47" t="n">
-        <v>97.59999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="D47" t="n">
-        <v>2.4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48">
@@ -4525,13 +10425,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="C48" t="n">
-        <v>78.7</v>
+        <v>1.9</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
     </row>
   </sheetData>
@@ -4551,7 +10451,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 20307</t>
+          <t>Day 1 — Active bid: 17905 ask: 17684</t>
         </is>
       </c>
     </row>
@@ -4584,13 +10484,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11323</v>
+        <v>510</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>14577</v>
       </c>
       <c r="D3" t="n">
-        <v>8984</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="4">
@@ -4600,13 +10500,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10669</v>
+        <v>301</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>14618</v>
       </c>
       <c r="D4" t="n">
-        <v>7450</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="6">
@@ -4638,13 +10538,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55.8</v>
+        <v>2.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>44.2</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="8">
@@ -4654,19 +10554,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.5</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>82.7</v>
       </c>
       <c r="D8" t="n">
-        <v>36.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 21206</t>
+          <t>Day 2 — Active bid: 19238 ask: 19184</t>
         </is>
       </c>
     </row>
@@ -4699,13 +10599,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8829</v>
+        <v>314</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>16895</v>
       </c>
       <c r="D13" t="n">
-        <v>12377</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="14">
@@ -4715,13 +10615,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8158</v>
+        <v>367</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16667</v>
       </c>
       <c r="D14" t="n">
-        <v>11009</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="16">
@@ -4753,13 +10653,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.6</v>
+        <v>1.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="D17" t="n">
-        <v>58.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="18">
@@ -4769,19 +10669,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.5</v>
+        <v>1.9</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>51.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 20249</t>
+          <t>Day 3 — Active bid: 19112 ask: 19665</t>
         </is>
       </c>
     </row>
@@ -4814,13 +10714,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9370</v>
+        <v>412</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>16616</v>
       </c>
       <c r="D23" t="n">
-        <v>10879</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="24">
@@ -4830,13 +10730,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8662</v>
+        <v>542</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="D24" t="n">
-        <v>9094</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="26">
@@ -4868,13 +10768,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>46.3</v>
+        <v>2.2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>53.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="28">
@@ -4884,19 +10784,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42.8</v>
+        <v>2.8</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>44.9</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 20938</t>
+          <t>Day 4 — Active bid: 19123 ask: 18928</t>
         </is>
       </c>
     </row>
@@ -4929,13 +10829,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8409</v>
+        <v>336</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>16674</v>
       </c>
       <c r="D33" t="n">
-        <v>12529</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="34">
@@ -4945,13 +10845,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7961</v>
+        <v>349</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>16687</v>
       </c>
       <c r="D34" t="n">
-        <v>10872</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="36">
@@ -4983,13 +10883,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.2</v>
+        <v>1.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>87.2</v>
       </c>
       <c r="D37" t="n">
-        <v>59.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -4999,19 +10899,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>1.8</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="D38" t="n">
-        <v>51.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 21295</t>
+          <t>Day 5 — Active bid: 17101 ask: 16975</t>
         </is>
       </c>
     </row>
@@ -5044,13 +10944,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11403</v>
+        <v>348</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>13940</v>
       </c>
       <c r="D43" t="n">
-        <v>9892</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="44">
@@ -5060,13 +10960,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10625</v>
+        <v>360</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>13986</v>
       </c>
       <c r="D44" t="n">
-        <v>8821</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="46">
@@ -5098,13 +10998,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53.5</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>81.5</v>
       </c>
       <c r="D47" t="n">
-        <v>46.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="48">
@@ -5114,13 +11014,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>49.9</v>
+        <v>2.1</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>41.4</v>
+        <v>15.5</v>
       </c>
     </row>
   </sheetData>
@@ -5140,7 +11040,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 21077</t>
+          <t>Day 1 — Active bid: 19462 ask: 19054</t>
         </is>
       </c>
     </row>
@@ -5173,13 +11073,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11837</v>
+        <v>603</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>16157</v>
       </c>
       <c r="D3" t="n">
-        <v>9240</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="4">
@@ -5189,13 +11089,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11277</v>
+        <v>417</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="D4" t="n">
-        <v>8130</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="6">
@@ -5227,13 +11127,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56.2</v>
+        <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>43.8</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="8">
@@ -5243,19 +11143,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53.5</v>
+        <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="D8" t="n">
-        <v>38.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 21893</t>
+          <t>Day 2 — Active bid: 20332 ask: 20256</t>
         </is>
       </c>
     </row>
@@ -5288,13 +11188,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9230</v>
+        <v>355</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>18058</v>
       </c>
       <c r="D13" t="n">
-        <v>12663</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="14">
@@ -5304,13 +11204,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8635</v>
+        <v>392</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>17846</v>
       </c>
       <c r="D14" t="n">
-        <v>11790</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="16">
@@ -5342,13 +11242,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.2</v>
+        <v>1.7</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="D17" t="n">
-        <v>57.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="18">
@@ -5358,19 +11258,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.4</v>
+        <v>1.9</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>53.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 21132</t>
+          <t>Day 3 — Active bid: 20451 ask: 20783</t>
         </is>
       </c>
     </row>
@@ -5403,13 +11303,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9915</v>
+        <v>464</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>18127</v>
       </c>
       <c r="D23" t="n">
-        <v>11217</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="24">
@@ -5419,13 +11319,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9322</v>
+        <v>612</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D24" t="n">
-        <v>10008</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="26">
@@ -5457,13 +11357,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>46.9</v>
+        <v>2.3</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>53.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="28">
@@ -5473,19 +11373,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44.1</v>
+        <v>2.9</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>47.4</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 21868</t>
+          <t>Day 4 — Active bid: 20223 ask: 19957</t>
         </is>
       </c>
     </row>
@@ -5518,13 +11418,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8960</v>
+        <v>378</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>17828</v>
       </c>
       <c r="D33" t="n">
-        <v>12908</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="34">
@@ -5534,13 +11434,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8554</v>
+        <v>406</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>17805</v>
       </c>
       <c r="D34" t="n">
-        <v>11924</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="36">
@@ -5572,13 +11472,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41</v>
+        <v>1.9</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -5588,19 +11488,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39.1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="D38" t="n">
-        <v>54.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 21834</t>
+          <t>Day 5 — Active bid: 18282 ask: 18474</t>
         </is>
       </c>
     </row>
@@ -5633,13 +11533,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11701</v>
+        <v>405</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>15322</v>
       </c>
       <c r="D43" t="n">
-        <v>10133</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="44">
@@ -5649,13 +11549,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10899</v>
+        <v>447</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>15537</v>
       </c>
       <c r="D44" t="n">
-        <v>9507</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="46">
@@ -5687,13 +11587,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53.6</v>
+        <v>2.2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="D47" t="n">
-        <v>46.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -5703,13 +11603,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>49.9</v>
+        <v>2.4</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>43.5</v>
+        <v>13.5</v>
       </c>
     </row>
   </sheetData>
@@ -5729,7 +11629,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active seconds: 15082</t>
+          <t>Day 1 — Active bid: 23119 ask: 23114</t>
         </is>
       </c>
     </row>
@@ -5762,13 +11662,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>12660</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>1774</v>
+        <v>23101</v>
       </c>
     </row>
     <row r="4">
@@ -5778,13 +11678,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>8763</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="6">
@@ -5816,13 +11716,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>83.90000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -5832,19 +11732,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>58.1</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active seconds: 14021</t>
+          <t>Day 2 — Active bid: 23314 ask: 23320</t>
         </is>
       </c>
     </row>
@@ -5877,13 +11777,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>12631</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>1243</v>
+        <v>23301</v>
       </c>
     </row>
     <row r="14">
@@ -5893,13 +11793,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>9964</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>23314</v>
       </c>
     </row>
     <row r="16">
@@ -5931,13 +11831,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>90.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>8.9</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -5947,19 +11847,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>71.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active seconds: 15847</t>
+          <t>Day 3 — Active bid: 23334 ask: 23343</t>
         </is>
       </c>
     </row>
@@ -5992,13 +11892,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>13952</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>1331</v>
+        <v>23324</v>
       </c>
     </row>
     <row r="24">
@@ -6008,13 +11908,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>10650</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>23338</v>
       </c>
     </row>
     <row r="26">
@@ -6046,13 +11946,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -6062,19 +11962,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>67.2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active seconds: 17780</t>
+          <t>Day 4 — Active bid: 23355 ask: 23367</t>
         </is>
       </c>
     </row>
@@ -6107,13 +12007,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>16208</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1094</v>
+        <v>23351</v>
       </c>
     </row>
     <row r="34">
@@ -6123,13 +12023,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>12447</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>23363</v>
       </c>
     </row>
     <row r="36">
@@ -6161,13 +12061,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>6.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -6177,19 +12077,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active seconds: 17755</t>
+          <t>Day 5 — Active bid: 23343 ask: 23331</t>
         </is>
       </c>
     </row>
@@ -6222,13 +12122,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>15979</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>1289</v>
+        <v>23340</v>
       </c>
     </row>
     <row r="44">
@@ -6238,13 +12138,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>11888</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>23324</v>
       </c>
     </row>
     <row r="46">
@@ -6276,13 +12176,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>7.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -6292,13 +12192,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -438,7 +438,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 12757 ask: 13216</t>
+          <t>Day 1 — Active bid: 15393 ask: 15945</t>
         </is>
       </c>
     </row>
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>741</v>
+        <v>252</v>
       </c>
       <c r="C3" t="n">
-        <v>1468</v>
+        <v>1417</v>
       </c>
       <c r="D3" t="n">
-        <v>10548</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="4">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>861</v>
+        <v>396</v>
       </c>
       <c r="C4" t="n">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="D4" t="n">
-        <v>10741</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>82.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="8">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>12.2</v>
+        <v>10.1</v>
       </c>
       <c r="D8" t="n">
-        <v>81.3</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 15575 ask: 15928</t>
+          <t>Day 2 — Active bid: 18456 ask: 18962</t>
         </is>
       </c>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>667</v>
+        <v>196</v>
       </c>
       <c r="C13" t="n">
-        <v>1389</v>
+        <v>1312</v>
       </c>
       <c r="D13" t="n">
-        <v>13519</v>
+        <v>16948</v>
       </c>
     </row>
     <row r="14">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>834</v>
+        <v>239</v>
       </c>
       <c r="C14" t="n">
-        <v>1500</v>
+        <v>1492</v>
       </c>
       <c r="D14" t="n">
-        <v>13594</v>
+        <v>17231</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="D17" t="n">
-        <v>86.8</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="18">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="C18" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="D18" t="n">
-        <v>85.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 15240 ask: 15275</t>
+          <t>Day 3 — Active bid: 17837 ask: 18574</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>784</v>
+        <v>248</v>
       </c>
       <c r="C23" t="n">
-        <v>1818</v>
+        <v>1501</v>
       </c>
       <c r="D23" t="n">
-        <v>12638</v>
+        <v>16088</v>
       </c>
     </row>
     <row r="24">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>825</v>
+        <v>347</v>
       </c>
       <c r="C24" t="n">
-        <v>1815</v>
+        <v>1603</v>
       </c>
       <c r="D24" t="n">
-        <v>12635</v>
+        <v>16624</v>
       </c>
     </row>
     <row r="26">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="C27" t="n">
-        <v>11.9</v>
+        <v>8.4</v>
       </c>
       <c r="D27" t="n">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="28">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="C28" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
       </c>
       <c r="D28" t="n">
-        <v>82.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 15785 ask: 15740</t>
+          <t>Day 4 — Active bid: 18446 ask: 18619</t>
         </is>
       </c>
     </row>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>712</v>
+        <v>158</v>
       </c>
       <c r="C33" t="n">
-        <v>1257</v>
+        <v>1414</v>
       </c>
       <c r="D33" t="n">
-        <v>13816</v>
+        <v>16874</v>
       </c>
     </row>
     <row r="34">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>802</v>
+        <v>261</v>
       </c>
       <c r="C34" t="n">
-        <v>1253</v>
+        <v>1448</v>
       </c>
       <c r="D34" t="n">
-        <v>13685</v>
+        <v>16910</v>
       </c>
     </row>
     <row r="36">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="D37" t="n">
-        <v>87.5</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="38">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D38" t="n">
-        <v>86.90000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 16547 ask: 16051</t>
+          <t>Day 5 — Active bid: 18546 ask: 19214</t>
         </is>
       </c>
     </row>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>599</v>
+        <v>130</v>
       </c>
       <c r="C43" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="D43" t="n">
-        <v>14948</v>
+        <v>17360</v>
       </c>
     </row>
     <row r="44">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>769</v>
+        <v>269</v>
       </c>
       <c r="C44" t="n">
-        <v>1014</v>
+        <v>1428</v>
       </c>
       <c r="D44" t="n">
-        <v>14268</v>
+        <v>17517</v>
       </c>
     </row>
     <row r="46">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="D47" t="n">
-        <v>90.3</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="C48" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="D48" t="n">
-        <v>88.90000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1027,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 23401 ask: 23401</t>
+          <t>Day 1 — Active bid: 19195 ask: 19298</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>475</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>17854</v>
       </c>
       <c r="D3" t="n">
-        <v>23361</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>702</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>17461</v>
       </c>
       <c r="D4" t="n">
-        <v>23368</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
-        <v>99.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>90.5</v>
       </c>
       <c r="D8" t="n">
-        <v>99.90000000000001</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23401 ask: 23401</t>
+          <t>Day 2 — Active bid: 20994 ask: 21277</t>
         </is>
       </c>
     </row>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>20338</v>
       </c>
       <c r="D13" t="n">
-        <v>23386</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>20223</v>
       </c>
       <c r="D14" t="n">
-        <v>23389</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>99.90000000000001</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>99.90000000000001</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23401 ask: 23401</t>
+          <t>Day 3 — Active bid: 20598 ask: 20639</t>
         </is>
       </c>
     </row>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>487</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>19537</v>
       </c>
       <c r="D23" t="n">
-        <v>23392</v>
+        <v>574</v>
       </c>
     </row>
     <row r="24">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>836</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>18900</v>
       </c>
       <c r="D24" t="n">
-        <v>23393</v>
+        <v>903</v>
       </c>
     </row>
     <row r="26">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>94.8</v>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -1360,19 +1360,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23401 ask: 23401</t>
+          <t>Day 4 — Active bid: 20756 ask: 21113</t>
         </is>
       </c>
     </row>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>19909</v>
       </c>
       <c r="D33" t="n">
-        <v>23393</v>
+        <v>545</v>
       </c>
     </row>
     <row r="34">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>485</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>19864</v>
       </c>
       <c r="D34" t="n">
-        <v>23396</v>
+        <v>764</v>
       </c>
     </row>
     <row r="36">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23401 ask: 23401</t>
+          <t>Day 5 — Active bid: 20604 ask: 21158</t>
         </is>
       </c>
     </row>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>20047</v>
       </c>
       <c r="D43" t="n">
-        <v>23394</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>471</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>19885</v>
       </c>
       <c r="D44" t="n">
-        <v>23392</v>
+        <v>802</v>
       </c>
     </row>
     <row r="46">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="48">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +1616,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 14605 ask: 9576</t>
+          <t>Day 1 — Active bid: 17044 ask: 15965</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C3" t="n">
-        <v>13640</v>
+        <v>14980</v>
       </c>
       <c r="D3" t="n">
-        <v>964</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="4">
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C4" t="n">
-        <v>8598</v>
+        <v>14343</v>
       </c>
       <c r="D4" t="n">
-        <v>978</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="6">
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>93.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>6.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="8">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="C8" t="n">
         <v>89.8</v>
       </c>
       <c r="D8" t="n">
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 16319 ask: 13632</t>
+          <t>Day 2 — Active bid: 19301 ask: 17789</t>
         </is>
       </c>
     </row>
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>15824</v>
+        <v>18057</v>
       </c>
       <c r="D13" t="n">
-        <v>494</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="14">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="C14" t="n">
-        <v>13061</v>
+        <v>16967</v>
       </c>
       <c r="D14" t="n">
-        <v>571</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>97</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="18">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C18" t="n">
-        <v>95.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 16086 ask: 12836</t>
+          <t>Day 3 — Active bid: 18324 ask: 18015</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C23" t="n">
-        <v>15325</v>
+        <v>16598</v>
       </c>
       <c r="D23" t="n">
-        <v>761</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="24">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="C24" t="n">
-        <v>12065</v>
+        <v>16857</v>
       </c>
       <c r="D24" t="n">
-        <v>768</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C27" t="n">
-        <v>95.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>4.7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1949,19 +1949,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="C28" t="n">
-        <v>94</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 16360 ask: 13354</t>
+          <t>Day 4 — Active bid: 18505 ask: 18317</t>
         </is>
       </c>
     </row>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C33" t="n">
-        <v>15594</v>
+        <v>17522</v>
       </c>
       <c r="D33" t="n">
-        <v>766</v>
+        <v>950</v>
       </c>
     </row>
     <row r="34">
@@ -2010,13 +2010,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="C34" t="n">
-        <v>12646</v>
+        <v>17314</v>
       </c>
       <c r="D34" t="n">
-        <v>708</v>
+        <v>840</v>
       </c>
     </row>
     <row r="36">
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C37" t="n">
-        <v>95.3</v>
+        <v>94.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="38">
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C38" t="n">
-        <v>94.7</v>
+        <v>94.5</v>
       </c>
       <c r="D38" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 17308 ask: 10896</t>
+          <t>Day 5 — Active bid: 19068 ask: 16571</t>
         </is>
       </c>
     </row>
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>16864</v>
+        <v>18119</v>
       </c>
       <c r="D43" t="n">
-        <v>443</v>
+        <v>924</v>
       </c>
     </row>
     <row r="44">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="C44" t="n">
-        <v>10481</v>
+        <v>15655</v>
       </c>
       <c r="D44" t="n">
-        <v>415</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46">
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C47" t="n">
-        <v>97.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="D47" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="48">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C48" t="n">
-        <v>96.2</v>
+        <v>94.5</v>
       </c>
       <c r="D48" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>
@@ -2205,7 +2205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19247 ask: 19455</t>
+          <t>Day 1 — Active bid: 19651 ask: 19407</t>
         </is>
       </c>
     </row>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="C3" t="n">
-        <v>18177</v>
+        <v>17514</v>
       </c>
       <c r="D3" t="n">
-        <v>1048</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="4">
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>526</v>
       </c>
       <c r="C4" t="n">
-        <v>18366</v>
+        <v>17736</v>
       </c>
       <c r="D4" t="n">
-        <v>1079</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6">
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="C7" t="n">
-        <v>94.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="8">
@@ -2308,19 +2308,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>94.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 21564 ask: 21554</t>
+          <t>Day 2 — Active bid: 21152 ask: 21331</t>
         </is>
       </c>
     </row>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="C13" t="n">
-        <v>20988</v>
+        <v>19850</v>
       </c>
       <c r="D13" t="n">
-        <v>568</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14">
@@ -2369,13 +2369,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="C14" t="n">
-        <v>20937</v>
+        <v>20365</v>
       </c>
       <c r="D14" t="n">
-        <v>613</v>
+        <v>716</v>
       </c>
     </row>
     <row r="16">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C17" t="n">
-        <v>97.3</v>
+        <v>93.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="18">
@@ -2423,19 +2423,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C18" t="n">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20804 ask: 21049</t>
+          <t>Day 3 — Active bid: 20965 ask: 20729</t>
         </is>
       </c>
     </row>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="C23" t="n">
-        <v>19988</v>
+        <v>19242</v>
       </c>
       <c r="D23" t="n">
-        <v>808</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="24">
@@ -2484,13 +2484,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>412</v>
       </c>
       <c r="C24" t="n">
-        <v>20220</v>
+        <v>19468</v>
       </c>
       <c r="D24" t="n">
-        <v>820</v>
+        <v>849</v>
       </c>
     </row>
     <row r="26">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C27" t="n">
-        <v>96.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28">
@@ -2538,19 +2538,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>96.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 21295 ask: 21350</t>
+          <t>Day 4 — Active bid: 20951 ask: 21176</t>
         </is>
       </c>
     </row>
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C33" t="n">
-        <v>20477</v>
+        <v>19937</v>
       </c>
       <c r="D33" t="n">
-        <v>803</v>
+        <v>844</v>
       </c>
     </row>
     <row r="34">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41</v>
+        <v>333</v>
       </c>
       <c r="C34" t="n">
-        <v>20554</v>
+        <v>20123</v>
       </c>
       <c r="D34" t="n">
-        <v>755</v>
+        <v>720</v>
       </c>
     </row>
     <row r="36">
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C37" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="D37" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2653,19 +2653,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="C38" t="n">
-        <v>96.3</v>
+        <v>95</v>
       </c>
       <c r="D38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21942 ask: 21760</t>
+          <t>Day 5 — Active bid: 20738 ask: 21236</t>
         </is>
       </c>
     </row>
@@ -2698,13 +2698,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C43" t="n">
-        <v>21441</v>
+        <v>19823</v>
       </c>
       <c r="D43" t="n">
-        <v>488</v>
+        <v>845</v>
       </c>
     </row>
     <row r="44">
@@ -2714,13 +2714,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>336</v>
       </c>
       <c r="C44" t="n">
-        <v>21284</v>
+        <v>20100</v>
       </c>
       <c r="D44" t="n">
-        <v>471</v>
+        <v>800</v>
       </c>
     </row>
     <row r="46">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C47" t="n">
-        <v>97.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="48">
@@ -2768,13 +2768,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="C48" t="n">
-        <v>97.8</v>
+        <v>94.7</v>
       </c>
       <c r="D48" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -2794,7 +2794,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 22441 ask: 22474</t>
+          <t>Day 1 — Active bid: 19007 ask: 19116</t>
         </is>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1468</v>
+        <v>8892</v>
       </c>
       <c r="C3" t="n">
-        <v>2137</v>
+        <v>8511</v>
       </c>
       <c r="D3" t="n">
-        <v>18836</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="4">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1487</v>
+        <v>8960</v>
       </c>
       <c r="C4" t="n">
-        <v>2155</v>
+        <v>8235</v>
       </c>
       <c r="D4" t="n">
-        <v>18832</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="6">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.5</v>
+        <v>46.8</v>
       </c>
       <c r="C7" t="n">
-        <v>9.5</v>
+        <v>44.8</v>
       </c>
       <c r="D7" t="n">
-        <v>83.90000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8">
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.6</v>
+        <v>46.9</v>
       </c>
       <c r="C8" t="n">
-        <v>9.6</v>
+        <v>43.1</v>
       </c>
       <c r="D8" t="n">
-        <v>83.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 22907 ask: 22868</t>
+          <t>Day 2 — Active bid: 19817 ask: 19046</t>
         </is>
       </c>
     </row>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1131</v>
+        <v>8292</v>
       </c>
       <c r="C13" t="n">
-        <v>1130</v>
+        <v>10022</v>
       </c>
       <c r="D13" t="n">
-        <v>20646</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="14">
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1134</v>
+        <v>8142</v>
       </c>
       <c r="C14" t="n">
-        <v>1143</v>
+        <v>9548</v>
       </c>
       <c r="D14" t="n">
-        <v>20591</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="16">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.9</v>
+        <v>41.8</v>
       </c>
       <c r="C17" t="n">
-        <v>4.9</v>
+        <v>50.6</v>
       </c>
       <c r="D17" t="n">
-        <v>90.09999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="18">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>42.7</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>50.1</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 22169 ask: 21914</t>
+          <t>Day 3 — Active bid: 19823 ask: 18995</t>
         </is>
       </c>
     </row>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1446</v>
+        <v>12745</v>
       </c>
       <c r="C23" t="n">
-        <v>1157</v>
+        <v>5465</v>
       </c>
       <c r="D23" t="n">
-        <v>19566</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="24">
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1426</v>
+        <v>12150</v>
       </c>
       <c r="C24" t="n">
-        <v>1168</v>
+        <v>5290</v>
       </c>
       <c r="D24" t="n">
-        <v>19320</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="26">
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.5</v>
+        <v>64.3</v>
       </c>
       <c r="C27" t="n">
-        <v>5.2</v>
+        <v>27.6</v>
       </c>
       <c r="D27" t="n">
-        <v>88.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="28">
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.5</v>
+        <v>64</v>
       </c>
       <c r="C28" t="n">
-        <v>5.3</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
-        <v>88.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 22768 ask: 22638</t>
+          <t>Day 4 — Active bid: 17969 ask: 18233</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1374</v>
+        <v>3317</v>
       </c>
       <c r="C33" t="n">
-        <v>1139</v>
+        <v>12692</v>
       </c>
       <c r="D33" t="n">
-        <v>20255</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="34">
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1429</v>
+        <v>3490</v>
       </c>
       <c r="C34" t="n">
-        <v>1199</v>
+        <v>12201</v>
       </c>
       <c r="D34" t="n">
-        <v>20010</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="36">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>89</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="38">
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.3</v>
+        <v>19.1</v>
       </c>
       <c r="C38" t="n">
-        <v>5.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>88.40000000000001</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 22726 ask: 22788</t>
+          <t>Day 5 — Active bid: 20046 ask: 19184</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2090</v>
+        <v>6562</v>
       </c>
       <c r="C43" t="n">
-        <v>1720</v>
+        <v>12066</v>
       </c>
       <c r="D43" t="n">
-        <v>18916</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="44">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2220</v>
+        <v>6212</v>
       </c>
       <c r="C44" t="n">
-        <v>1645</v>
+        <v>11665</v>
       </c>
       <c r="D44" t="n">
-        <v>18923</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="46">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.199999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="C47" t="n">
-        <v>7.6</v>
+        <v>60.2</v>
       </c>
       <c r="D47" t="n">
-        <v>83.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="48">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.699999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="C48" t="n">
-        <v>7.2</v>
+        <v>60.8</v>
       </c>
       <c r="D48" t="n">
-        <v>83</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3383,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 23259 ask: 23223</t>
+          <t>Day 1 — Active bid: 20096 ask: 20248</t>
         </is>
       </c>
     </row>
@@ -3416,13 +3416,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1627</v>
+        <v>9549</v>
       </c>
       <c r="C3" t="n">
-        <v>2233</v>
+        <v>9149</v>
       </c>
       <c r="D3" t="n">
-        <v>19399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="4">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1539</v>
+        <v>9556</v>
       </c>
       <c r="C4" t="n">
-        <v>2264</v>
+        <v>9032</v>
       </c>
       <c r="D4" t="n">
-        <v>19420</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="6">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D7" t="n">
         <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3486,19 +3486,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.6</v>
+        <v>47.2</v>
       </c>
       <c r="C8" t="n">
-        <v>9.699999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="D8" t="n">
-        <v>83.59999999999999</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23224 ask: 23268</t>
+          <t>Day 2 — Active bid: 20759 ask: 20431</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1191</v>
+        <v>8823</v>
       </c>
       <c r="C13" t="n">
-        <v>1167</v>
+        <v>10740</v>
       </c>
       <c r="D13" t="n">
-        <v>20866</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="14">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1171</v>
+        <v>8699</v>
       </c>
       <c r="C14" t="n">
-        <v>1130</v>
+        <v>10527</v>
       </c>
       <c r="D14" t="n">
-        <v>20967</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="16">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.1</v>
+        <v>42.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>51.7</v>
       </c>
       <c r="D17" t="n">
-        <v>89.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="18">
@@ -3601,19 +3601,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>42.6</v>
       </c>
       <c r="C18" t="n">
-        <v>4.9</v>
+        <v>51.5</v>
       </c>
       <c r="D18" t="n">
-        <v>90.09999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23005 ask: 23103</t>
+          <t>Day 3 — Active bid: 20526 ask: 19870</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1603</v>
+        <v>13196</v>
       </c>
       <c r="C23" t="n">
-        <v>1234</v>
+        <v>5778</v>
       </c>
       <c r="D23" t="n">
-        <v>20168</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="24">
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1598</v>
+        <v>12794</v>
       </c>
       <c r="C24" t="n">
-        <v>1245</v>
+        <v>5679</v>
       </c>
       <c r="D24" t="n">
-        <v>20260</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="26">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>64.3</v>
       </c>
       <c r="C27" t="n">
-        <v>5.4</v>
+        <v>28.1</v>
       </c>
       <c r="D27" t="n">
-        <v>87.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="28">
@@ -3716,19 +3716,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>5.4</v>
+        <v>28.6</v>
       </c>
       <c r="D28" t="n">
-        <v>87.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23243 ask: 23127</t>
+          <t>Day 4 — Active bid: 20254 ask: 20743</t>
         </is>
       </c>
     </row>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1462</v>
+        <v>3888</v>
       </c>
       <c r="C33" t="n">
-        <v>1179</v>
+        <v>14764</v>
       </c>
       <c r="D33" t="n">
-        <v>20602</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="34">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1521</v>
+        <v>4102</v>
       </c>
       <c r="C34" t="n">
-        <v>1192</v>
+        <v>14736</v>
       </c>
       <c r="D34" t="n">
-        <v>20414</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="36">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.3</v>
+        <v>19.2</v>
       </c>
       <c r="C37" t="n">
-        <v>5.1</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>88.59999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="38">
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.6</v>
+        <v>19.8</v>
       </c>
       <c r="C38" t="n">
-        <v>5.2</v>
+        <v>71</v>
       </c>
       <c r="D38" t="n">
-        <v>88.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23065 ask: 23257</t>
+          <t>Day 5 — Active bid: 20990 ask: 20611</t>
         </is>
       </c>
     </row>
@@ -3876,13 +3876,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2209</v>
+        <v>6885</v>
       </c>
       <c r="C43" t="n">
-        <v>1781</v>
+        <v>12892</v>
       </c>
       <c r="D43" t="n">
-        <v>19075</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="44">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2270</v>
+        <v>6602</v>
       </c>
       <c r="C44" t="n">
-        <v>1701</v>
+        <v>12779</v>
       </c>
       <c r="D44" t="n">
-        <v>19286</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="46">
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.6</v>
+        <v>32.8</v>
       </c>
       <c r="C47" t="n">
-        <v>7.7</v>
+        <v>61.4</v>
       </c>
       <c r="D47" t="n">
-        <v>82.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="48">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>7.3</v>
+        <v>62</v>
       </c>
       <c r="D48" t="n">
-        <v>82.90000000000001</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3972,7 +3972,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18721 ask: 19055</t>
+          <t>Day 1 — Active bid: 19712 ask: 19926</t>
         </is>
       </c>
     </row>
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1589</v>
+        <v>1045</v>
       </c>
       <c r="C3" t="n">
-        <v>14388</v>
+        <v>15942</v>
       </c>
       <c r="D3" t="n">
-        <v>2744</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="4">
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1724</v>
+        <v>1476</v>
       </c>
       <c r="C4" t="n">
-        <v>14368</v>
+        <v>15827</v>
       </c>
       <c r="D4" t="n">
-        <v>2963</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="6">
@@ -4059,13 +4059,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="C7" t="n">
-        <v>76.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="8">
@@ -4075,19 +4075,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="C8" t="n">
-        <v>75.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>15.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19391 ask: 18097</t>
+          <t>Day 2 — Active bid: 20361 ask: 19946</t>
         </is>
       </c>
     </row>
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1378</v>
+        <v>916</v>
       </c>
       <c r="C13" t="n">
-        <v>15447</v>
+        <v>16615</v>
       </c>
       <c r="D13" t="n">
-        <v>2566</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="14">
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1161</v>
+        <v>855</v>
       </c>
       <c r="C14" t="n">
-        <v>14687</v>
+        <v>17285</v>
       </c>
       <c r="D14" t="n">
-        <v>2249</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="16">
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="C17" t="n">
-        <v>79.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="18">
@@ -4190,19 +4190,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="C18" t="n">
-        <v>81.2</v>
+        <v>86.7</v>
       </c>
       <c r="D18" t="n">
-        <v>12.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 18945 ask: 18124</t>
+          <t>Day 3 — Active bid: 20553 ask: 19874</t>
         </is>
       </c>
     </row>
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1506</v>
+        <v>1403</v>
       </c>
       <c r="C23" t="n">
-        <v>14431</v>
+        <v>15811</v>
       </c>
       <c r="D23" t="n">
-        <v>3008</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="24">
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1423</v>
+        <v>1442</v>
       </c>
       <c r="C24" t="n">
-        <v>13896</v>
+        <v>16127</v>
       </c>
       <c r="D24" t="n">
-        <v>2805</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="26">
@@ -4289,13 +4289,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="C27" t="n">
-        <v>76.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="28">
@@ -4305,19 +4305,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="C28" t="n">
-        <v>76.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 18324 ask: 17002</t>
+          <t>Day 4 — Active bid: 18254 ask: 18628</t>
         </is>
       </c>
     </row>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1480</v>
+        <v>660</v>
       </c>
       <c r="C33" t="n">
-        <v>13957</v>
+        <v>14830</v>
       </c>
       <c r="D33" t="n">
-        <v>2887</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="34">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1473</v>
+        <v>964</v>
       </c>
       <c r="C34" t="n">
-        <v>12744</v>
+        <v>14867</v>
       </c>
       <c r="D34" t="n">
-        <v>2785</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="36">
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="C37" t="n">
-        <v>76.2</v>
+        <v>81.2</v>
       </c>
       <c r="D37" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="38">
@@ -4420,19 +4420,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="C38" t="n">
-        <v>75</v>
+        <v>79.8</v>
       </c>
       <c r="D38" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20024 ask: 19037</t>
+          <t>Day 5 — Active bid: 20530 ask: 19808</t>
         </is>
       </c>
     </row>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1661</v>
+        <v>871</v>
       </c>
       <c r="C43" t="n">
-        <v>15953</v>
+        <v>17291</v>
       </c>
       <c r="D43" t="n">
-        <v>2410</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="44">
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1401</v>
+        <v>778</v>
       </c>
       <c r="C44" t="n">
-        <v>15468</v>
+        <v>17481</v>
       </c>
       <c r="D44" t="n">
-        <v>2168</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="46">
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="C47" t="n">
-        <v>79.7</v>
+        <v>84.2</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="48">
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="C48" t="n">
-        <v>81.3</v>
+        <v>88.3</v>
       </c>
       <c r="D48" t="n">
-        <v>11.4</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -4561,7 +4561,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 20401 ask: 20925</t>
+          <t>Day 1 — Active bid: 21342 ask: 21925</t>
         </is>
       </c>
     </row>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1840</v>
+        <v>1333</v>
       </c>
       <c r="C3" t="n">
-        <v>16063</v>
+        <v>17646</v>
       </c>
       <c r="D3" t="n">
-        <v>2498</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="4">
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2061</v>
+        <v>1801</v>
       </c>
       <c r="C4" t="n">
-        <v>16118</v>
+        <v>17754</v>
       </c>
       <c r="D4" t="n">
-        <v>2746</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="6">
@@ -4648,13 +4648,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="C7" t="n">
-        <v>78.7</v>
+        <v>82.7</v>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
@@ -4664,19 +4664,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 21170 ask: 20490</t>
+          <t>Day 2 — Active bid: 21671 ask: 22053</t>
         </is>
       </c>
     </row>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1489</v>
+        <v>1061</v>
       </c>
       <c r="C13" t="n">
-        <v>17496</v>
+        <v>18248</v>
       </c>
       <c r="D13" t="n">
-        <v>2185</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="14">
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1390</v>
+        <v>1102</v>
       </c>
       <c r="C14" t="n">
-        <v>17181</v>
+        <v>19346</v>
       </c>
       <c r="D14" t="n">
-        <v>1919</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="16">
@@ -4763,13 +4763,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="C17" t="n">
-        <v>82.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D17" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="18">
@@ -4779,19 +4779,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>83.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D18" t="n">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20723 ask: 20410</t>
+          <t>Day 3 — Active bid: 21755 ask: 21804</t>
         </is>
       </c>
     </row>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1785</v>
+        <v>1532</v>
       </c>
       <c r="C23" t="n">
-        <v>16308</v>
+        <v>17153</v>
       </c>
       <c r="D23" t="n">
-        <v>2630</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="24">
@@ -4840,13 +4840,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1857</v>
+        <v>1809</v>
       </c>
       <c r="C24" t="n">
-        <v>16054</v>
+        <v>17895</v>
       </c>
       <c r="D24" t="n">
-        <v>2499</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="26">
@@ -4878,13 +4878,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D27" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="28">
@@ -4894,19 +4894,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>78.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19971 ask: 20140</t>
+          <t>Day 4 — Active bid: 20984 ask: 21613</t>
         </is>
       </c>
     </row>
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1607</v>
+        <v>1006</v>
       </c>
       <c r="C33" t="n">
-        <v>15869</v>
+        <v>17536</v>
       </c>
       <c r="D33" t="n">
-        <v>2495</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="34">
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1821</v>
+        <v>1419</v>
       </c>
       <c r="C34" t="n">
-        <v>15662</v>
+        <v>18072</v>
       </c>
       <c r="D34" t="n">
-        <v>2657</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="36">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="C37" t="n">
-        <v>79.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="38">
@@ -5009,19 +5009,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="C38" t="n">
-        <v>77.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21124 ask: 20646</t>
+          <t>Day 5 — Active bid: 21733 ask: 21723</t>
         </is>
       </c>
     </row>
@@ -5054,13 +5054,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1723</v>
+        <v>951</v>
       </c>
       <c r="C43" t="n">
-        <v>17188</v>
+        <v>18666</v>
       </c>
       <c r="D43" t="n">
-        <v>2213</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="44">
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1515</v>
+        <v>1010</v>
       </c>
       <c r="C44" t="n">
-        <v>16965</v>
+        <v>19255</v>
       </c>
       <c r="D44" t="n">
-        <v>2166</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="46">
@@ -5108,13 +5108,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="C47" t="n">
-        <v>81.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5124,13 +5124,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.3</v>
+        <v>4.6</v>
       </c>
       <c r="C48" t="n">
-        <v>82.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -5150,7 +5150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 21234 ask: 21085</t>
+          <t>Day 1 — Active bid: 21626 ask: 21811</t>
         </is>
       </c>
     </row>
@@ -5183,13 +5183,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2542</v>
       </c>
       <c r="D3" t="n">
-        <v>20844</v>
+        <v>18810</v>
       </c>
     </row>
     <row r="4">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>362</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="D4" t="n">
-        <v>20723</v>
+        <v>18816</v>
       </c>
     </row>
     <row r="6">
@@ -5237,13 +5237,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="D7" t="n">
-        <v>98.2</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -5253,19 +5253,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D8" t="n">
-        <v>98.3</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 22155 ask: 22385</t>
+          <t>Day 2 — Active bid: 22706 ask: 22874</t>
         </is>
       </c>
     </row>
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1211</v>
       </c>
       <c r="D13" t="n">
-        <v>21895</v>
+        <v>21370</v>
       </c>
     </row>
     <row r="14">
@@ -5314,13 +5314,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="D14" t="n">
-        <v>22165</v>
+        <v>21531</v>
       </c>
     </row>
     <row r="16">
@@ -5352,13 +5352,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="D17" t="n">
-        <v>98.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -5368,19 +5368,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="D18" t="n">
-        <v>99</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 22230 ask: 22024</t>
+          <t>Day 3 — Active bid: 22623 ask: 22729</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1917</v>
       </c>
       <c r="D23" t="n">
-        <v>21850</v>
+        <v>20356</v>
       </c>
     </row>
     <row r="24">
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="D24" t="n">
-        <v>21693</v>
+        <v>20399</v>
       </c>
     </row>
     <row r="26">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D27" t="n">
-        <v>98.3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
@@ -5486,16 +5486,16 @@
         <v>1.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>98.5</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 22399 ask: 22259</t>
+          <t>Day 4 — Active bid: 22703 ask: 22714</t>
         </is>
       </c>
     </row>
@@ -5528,13 +5528,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>415</v>
+        <v>363</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1713</v>
       </c>
       <c r="D33" t="n">
-        <v>21984</v>
+        <v>20627</v>
       </c>
     </row>
     <row r="34">
@@ -5544,13 +5544,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1651</v>
       </c>
       <c r="D34" t="n">
-        <v>21894</v>
+        <v>20697</v>
       </c>
     </row>
     <row r="36">
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="D37" t="n">
-        <v>98.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -5601,16 +5601,16 @@
         <v>1.6</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="D38" t="n">
-        <v>98.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 22347 ask: 22183</t>
+          <t>Day 5 — Active bid: 22791 ask: 22768</t>
         </is>
       </c>
     </row>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>439</v>
+        <v>368</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1322</v>
       </c>
       <c r="D43" t="n">
-        <v>21908</v>
+        <v>21101</v>
       </c>
     </row>
     <row r="44">
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="D44" t="n">
-        <v>21780</v>
+        <v>21012</v>
       </c>
     </row>
     <row r="46">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="D48" t="n">
-        <v>98.2</v>
+        <v>92.3</v>
       </c>
     </row>
   </sheetData>
@@ -5739,7 +5739,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 23326 ask: 23303</t>
+          <t>Day 1 — Active bid: 22728 ask: 22859</t>
         </is>
       </c>
     </row>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>664</v>
+        <v>408</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2965</v>
       </c>
       <c r="D3" t="n">
-        <v>22662</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="4">
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>678</v>
+        <v>497</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="D4" t="n">
-        <v>22625</v>
+        <v>19351</v>
       </c>
     </row>
     <row r="6">
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>97.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="8">
@@ -5842,19 +5842,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="D8" t="n">
-        <v>97.09999999999999</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23373 ask: 23367</t>
+          <t>Day 2 — Active bid: 23248 ask: 23263</t>
         </is>
       </c>
     </row>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>364</v>
+        <v>152</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1366</v>
       </c>
       <c r="D13" t="n">
-        <v>23009</v>
+        <v>21730</v>
       </c>
     </row>
     <row r="14">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="D14" t="n">
-        <v>23017</v>
+        <v>21765</v>
       </c>
     </row>
     <row r="16">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="D17" t="n">
-        <v>98.40000000000001</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="18">
@@ -5957,19 +5957,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="D18" t="n">
-        <v>98.5</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23311 ask: 23309</t>
+          <t>Day 3 — Active bid: 23148 ask: 23253</t>
         </is>
       </c>
     </row>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>450</v>
+        <v>385</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="D23" t="n">
-        <v>22861</v>
+        <v>20711</v>
       </c>
     </row>
     <row r="24">
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>470</v>
+        <v>389</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2087</v>
       </c>
       <c r="D24" t="n">
-        <v>22839</v>
+        <v>20777</v>
       </c>
     </row>
     <row r="26">
@@ -6056,13 +6056,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="D27" t="n">
-        <v>98.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="28">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>98</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23340 ask: 23271</t>
+          <t>Day 4 — Active bid: 23172 ask: 23156</t>
         </is>
       </c>
     </row>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>512</v>
+        <v>404</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1891</v>
       </c>
       <c r="D33" t="n">
-        <v>22828</v>
+        <v>20877</v>
       </c>
     </row>
     <row r="34">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>485</v>
+        <v>420</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1888</v>
       </c>
       <c r="D34" t="n">
-        <v>22786</v>
+        <v>20848</v>
       </c>
     </row>
     <row r="36">
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>97.8</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -6187,19 +6187,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>97.90000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23307 ask: 23296</t>
+          <t>Day 5 — Active bid: 23227 ask: 23199</t>
         </is>
       </c>
     </row>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>536</v>
+        <v>429</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1490</v>
       </c>
       <c r="D43" t="n">
-        <v>22771</v>
+        <v>21308</v>
       </c>
     </row>
     <row r="44">
@@ -6248,13 +6248,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>526</v>
+        <v>380</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1531</v>
       </c>
       <c r="D44" t="n">
-        <v>22770</v>
+        <v>21288</v>
       </c>
     </row>
     <row r="46">
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="D47" t="n">
-        <v>97.7</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="48">
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="D48" t="n">
-        <v>97.7</v>
+        <v>91.8</v>
       </c>
     </row>
   </sheetData>
@@ -6328,7 +6328,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 15083 ask: 15153</t>
+          <t>Day 1 — Active bid: 18937 ask: 18474</t>
         </is>
       </c>
     </row>
@@ -6361,13 +6361,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="C3" t="n">
-        <v>13297</v>
+        <v>16940</v>
       </c>
       <c r="D3" t="n">
-        <v>1772</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="4">
@@ -6377,13 +6377,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="C4" t="n">
-        <v>13422</v>
+        <v>16414</v>
       </c>
       <c r="D4" t="n">
-        <v>1696</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="6">
@@ -6415,13 +6415,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C7" t="n">
-        <v>88.2</v>
+        <v>89.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -6431,19 +6431,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="C8" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="D8" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 14032 ask: 17330</t>
+          <t>Day 2 — Active bid: 18602 ask: 20321</t>
         </is>
       </c>
     </row>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="C13" t="n">
-        <v>12797</v>
+        <v>17382</v>
       </c>
       <c r="D13" t="n">
-        <v>1227</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="14">
@@ -6492,13 +6492,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="C14" t="n">
-        <v>16174</v>
+        <v>19105</v>
       </c>
       <c r="D14" t="n">
-        <v>1148</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="16">
@@ -6530,13 +6530,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>91.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -6546,19 +6546,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>93.3</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 15845 ask: 16672</t>
+          <t>Day 3 — Active bid: 19624 ask: 20213</t>
         </is>
       </c>
     </row>
@@ -6591,13 +6591,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="C23" t="n">
-        <v>14500</v>
+        <v>18347</v>
       </c>
       <c r="D23" t="n">
-        <v>1334</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="24">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="C24" t="n">
-        <v>15385</v>
+        <v>18884</v>
       </c>
       <c r="D24" t="n">
-        <v>1279</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="26">
@@ -6645,13 +6645,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="C27" t="n">
-        <v>91.5</v>
+        <v>93.5</v>
       </c>
       <c r="D27" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="28">
@@ -6661,19 +6661,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C28" t="n">
-        <v>92.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 17786 ask: 16709</t>
+          <t>Day 4 — Active bid: 20565 ask: 20564</t>
         </is>
       </c>
     </row>
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C33" t="n">
-        <v>16660</v>
+        <v>19374</v>
       </c>
       <c r="D33" t="n">
-        <v>1113</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="34">
@@ -6722,13 +6722,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C34" t="n">
-        <v>15697</v>
+        <v>19333</v>
       </c>
       <c r="D34" t="n">
-        <v>1004</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="36">
@@ -6760,13 +6760,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C37" t="n">
-        <v>93.7</v>
+        <v>94.2</v>
       </c>
       <c r="D37" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="38">
@@ -6776,19 +6776,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C38" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 17744 ask: 16146</t>
+          <t>Day 5 — Active bid: 20270 ask: 20065</t>
         </is>
       </c>
     </row>
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>16415</v>
+        <v>19022</v>
       </c>
       <c r="D43" t="n">
-        <v>1308</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="44">
@@ -6837,13 +6837,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="C44" t="n">
-        <v>15128</v>
+        <v>18841</v>
       </c>
       <c r="D44" t="n">
-        <v>1000</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="46">
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C47" t="n">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="D47" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="48">
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C48" t="n">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -6917,7 +6917,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 17252 ask: 17557</t>
+          <t>Day 1 — Active bid: 20617 ask: 20729</t>
         </is>
       </c>
     </row>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1763</v>
+        <v>1039</v>
       </c>
       <c r="C3" t="n">
-        <v>2196</v>
+        <v>2052</v>
       </c>
       <c r="D3" t="n">
-        <v>13293</v>
+        <v>17526</v>
       </c>
     </row>
     <row r="4">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1895</v>
+        <v>1142</v>
       </c>
       <c r="C4" t="n">
-        <v>2367</v>
+        <v>2236</v>
       </c>
       <c r="D4" t="n">
-        <v>13295</v>
+        <v>17351</v>
       </c>
     </row>
     <row r="6">
@@ -7004,13 +7004,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>77.09999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -7020,19 +7020,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C8" t="n">
         <v>10.8</v>
       </c>
-      <c r="C8" t="n">
-        <v>13.5</v>
-      </c>
       <c r="D8" t="n">
-        <v>75.7</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20056 ask: 20355</t>
+          <t>Day 2 — Active bid: 22397 ask: 22565</t>
         </is>
       </c>
     </row>
@@ -7065,13 +7065,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1506</v>
+        <v>667</v>
       </c>
       <c r="C13" t="n">
-        <v>2067</v>
+        <v>1738</v>
       </c>
       <c r="D13" t="n">
-        <v>16483</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="14">
@@ -7081,13 +7081,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1580</v>
+        <v>604</v>
       </c>
       <c r="C14" t="n">
-        <v>2209</v>
+        <v>2023</v>
       </c>
       <c r="D14" t="n">
-        <v>16566</v>
+        <v>19938</v>
       </c>
     </row>
     <row r="16">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>10.3</v>
+        <v>7.8</v>
       </c>
       <c r="D17" t="n">
-        <v>82.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="18">
@@ -7135,19 +7135,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
       <c r="C18" t="n">
-        <v>10.9</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>81.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19614 ask: 19729</t>
+          <t>Day 3 — Active bid: 22255 ask: 22355</t>
         </is>
       </c>
     </row>
@@ -7180,13 +7180,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1705</v>
+        <v>862</v>
       </c>
       <c r="C23" t="n">
-        <v>2538</v>
+        <v>2138</v>
       </c>
       <c r="D23" t="n">
-        <v>15371</v>
+        <v>19255</v>
       </c>
     </row>
     <row r="24">
@@ -7196,13 +7196,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1711</v>
+        <v>785</v>
       </c>
       <c r="C24" t="n">
-        <v>2569</v>
+        <v>2215</v>
       </c>
       <c r="D24" t="n">
-        <v>15449</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="26">
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.699999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="C27" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="D27" t="n">
-        <v>78.40000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="28">
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="D28" t="n">
-        <v>78.3</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20633 ask: 20586</t>
+          <t>Day 4 — Active bid: 22232 ask: 22455</t>
         </is>
       </c>
     </row>
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1552</v>
+        <v>617</v>
       </c>
       <c r="C33" t="n">
-        <v>1772</v>
+        <v>1820</v>
       </c>
       <c r="D33" t="n">
-        <v>17309</v>
+        <v>19795</v>
       </c>
     </row>
     <row r="34">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1601</v>
+        <v>683</v>
       </c>
       <c r="C34" t="n">
-        <v>1830</v>
+        <v>1985</v>
       </c>
       <c r="D34" t="n">
-        <v>17155</v>
+        <v>19787</v>
       </c>
     </row>
     <row r="36">
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="C37" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>83.90000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38">
@@ -7365,19 +7365,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>83.3</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21449 ask: 21248</t>
+          <t>Day 5 — Active bid: 22557 ask: 22834</t>
         </is>
       </c>
     </row>
@@ -7410,13 +7410,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1455</v>
+        <v>615</v>
       </c>
       <c r="C43" t="n">
-        <v>1550</v>
+        <v>1445</v>
       </c>
       <c r="D43" t="n">
-        <v>18444</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="44">
@@ -7426,13 +7426,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1582</v>
+        <v>570</v>
       </c>
       <c r="C44" t="n">
-        <v>1532</v>
+        <v>1821</v>
       </c>
       <c r="D44" t="n">
-        <v>18134</v>
+        <v>20443</v>
       </c>
     </row>
     <row r="46">
@@ -7464,13 +7464,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="C47" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="D47" t="n">
-        <v>86</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -7480,13 +7480,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>85.3</v>
+        <v>89.5</v>
       </c>
     </row>
   </sheetData>
@@ -7506,7 +7506,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19824 ask: 19291</t>
+          <t>Day 1 — Active bid: 21283 ask: 21119</t>
         </is>
       </c>
     </row>
@@ -7539,13 +7539,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>433</v>
       </c>
       <c r="C3" t="n">
-        <v>17942</v>
+        <v>19655</v>
       </c>
       <c r="D3" t="n">
-        <v>1711</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4">
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>188</v>
+        <v>524</v>
       </c>
       <c r="C4" t="n">
-        <v>17626</v>
+        <v>19407</v>
       </c>
       <c r="D4" t="n">
-        <v>1477</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>90.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -7609,19 +7609,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>91.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20397 ask: 20523</t>
+          <t>Day 2 — Active bid: 21587 ask: 22403</t>
         </is>
       </c>
     </row>
@@ -7654,13 +7654,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66</v>
+        <v>274</v>
       </c>
       <c r="C13" t="n">
-        <v>19209</v>
+        <v>20682</v>
       </c>
       <c r="D13" t="n">
-        <v>1122</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="C14" t="n">
-        <v>19443</v>
+        <v>21382</v>
       </c>
       <c r="D14" t="n">
-        <v>1009</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16">
@@ -7708,13 +7708,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C17" t="n">
-        <v>94.2</v>
+        <v>95.8</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -7724,19 +7724,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C18" t="n">
-        <v>94.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20983 ask: 20714</t>
+          <t>Day 3 — Active bid: 21824 ask: 22151</t>
         </is>
       </c>
     </row>
@@ -7769,13 +7769,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>125</v>
+        <v>245</v>
       </c>
       <c r="C23" t="n">
-        <v>19682</v>
+        <v>20835</v>
       </c>
       <c r="D23" t="n">
-        <v>1176</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24">
@@ -7785,13 +7785,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="C24" t="n">
-        <v>19554</v>
+        <v>21100</v>
       </c>
       <c r="D24" t="n">
-        <v>1052</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="C27" t="n">
-        <v>93.8</v>
+        <v>95.5</v>
       </c>
       <c r="D27" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="28">
@@ -7839,19 +7839,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="C28" t="n">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D28" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20416 ask: 20644</t>
+          <t>Day 4 — Active bid: 22146 ask: 22530</t>
         </is>
       </c>
     </row>
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="C33" t="n">
-        <v>19294</v>
+        <v>21329</v>
       </c>
       <c r="D33" t="n">
-        <v>1063</v>
+        <v>587</v>
       </c>
     </row>
     <row r="34">
@@ -7900,13 +7900,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>74</v>
+        <v>291</v>
       </c>
       <c r="C34" t="n">
-        <v>19528</v>
+        <v>21538</v>
       </c>
       <c r="D34" t="n">
-        <v>1042</v>
+        <v>701</v>
       </c>
     </row>
     <row r="36">
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="D37" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="38">
@@ -7954,19 +7954,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="C38" t="n">
-        <v>94.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20497 ask: 20355</t>
+          <t>Day 5 — Active bid: 22134 ask: 22340</t>
         </is>
       </c>
     </row>
@@ -7999,13 +7999,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="C43" t="n">
-        <v>19269</v>
+        <v>21163</v>
       </c>
       <c r="D43" t="n">
-        <v>1143</v>
+        <v>734</v>
       </c>
     </row>
     <row r="44">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68</v>
+        <v>286</v>
       </c>
       <c r="C44" t="n">
-        <v>19275</v>
+        <v>21393</v>
       </c>
       <c r="D44" t="n">
-        <v>1012</v>
+        <v>661</v>
       </c>
     </row>
     <row r="46">
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="C47" t="n">
-        <v>94</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="48">
@@ -8069,13 +8069,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C48" t="n">
-        <v>94.7</v>
+        <v>95.8</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8095,7 +8095,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 9967 ask: 10607</t>
+          <t>Day 1 — Active bid: 13031 ask: 12211</t>
         </is>
       </c>
     </row>
@@ -8128,13 +8128,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="C3" t="n">
-        <v>5790</v>
+        <v>5429</v>
       </c>
       <c r="D3" t="n">
-        <v>4101</v>
+        <v>7411</v>
       </c>
     </row>
     <row r="4">
@@ -8144,13 +8144,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="C4" t="n">
-        <v>6423</v>
+        <v>6964</v>
       </c>
       <c r="D4" t="n">
-        <v>4104</v>
+        <v>4892</v>
       </c>
     </row>
     <row r="6">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="C7" t="n">
-        <v>58.1</v>
+        <v>41.7</v>
       </c>
       <c r="D7" t="n">
-        <v>41.1</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="8">
@@ -8198,19 +8198,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="C8" t="n">
-        <v>60.6</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 11238 ask: 12199</t>
+          <t>Day 2 — Active bid: 14908 ask: 14101</t>
         </is>
       </c>
     </row>
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>240</v>
       </c>
       <c r="C13" t="n">
-        <v>7508</v>
+        <v>7374</v>
       </c>
       <c r="D13" t="n">
-        <v>3681</v>
+        <v>7294</v>
       </c>
     </row>
     <row r="14">
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>489</v>
       </c>
       <c r="C14" t="n">
-        <v>8273</v>
+        <v>8967</v>
       </c>
       <c r="D14" t="n">
-        <v>3745</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="16">
@@ -8297,13 +8297,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="C17" t="n">
-        <v>66.8</v>
+        <v>49.5</v>
       </c>
       <c r="D17" t="n">
-        <v>32.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="18">
@@ -8313,19 +8313,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="C18" t="n">
-        <v>67.8</v>
+        <v>63.6</v>
       </c>
       <c r="D18" t="n">
-        <v>30.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 11934 ask: 11561</t>
+          <t>Day 3 — Active bid: 14644 ask: 14076</t>
         </is>
       </c>
     </row>
@@ -8358,13 +8358,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="C23" t="n">
-        <v>7762</v>
+        <v>7154</v>
       </c>
       <c r="D23" t="n">
-        <v>4031</v>
+        <v>7174</v>
       </c>
     </row>
     <row r="24">
@@ -8374,13 +8374,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>117</v>
+        <v>474</v>
       </c>
       <c r="C24" t="n">
-        <v>7589</v>
+        <v>8880</v>
       </c>
       <c r="D24" t="n">
-        <v>3855</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="26">
@@ -8412,13 +8412,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="C27" t="n">
-        <v>65</v>
+        <v>48.9</v>
       </c>
       <c r="D27" t="n">
-        <v>33.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
@@ -8428,19 +8428,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="C28" t="n">
-        <v>65.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="D28" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 12053 ask: 11262</t>
+          <t>Day 4 — Active bid: 14887 ask: 13655</t>
         </is>
       </c>
     </row>
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="C33" t="n">
-        <v>8005</v>
+        <v>7395</v>
       </c>
       <c r="D33" t="n">
-        <v>3987</v>
+        <v>7284</v>
       </c>
     </row>
     <row r="34">
@@ -8489,13 +8489,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>60</v>
+        <v>383</v>
       </c>
       <c r="C34" t="n">
-        <v>7630</v>
+        <v>8817</v>
       </c>
       <c r="D34" t="n">
-        <v>3572</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="36">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="C37" t="n">
-        <v>66.40000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="D37" t="n">
-        <v>33.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="38">
@@ -8543,19 +8543,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="C38" t="n">
-        <v>67.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 11769 ask: 11732</t>
+          <t>Day 5 — Active bid: 14677 ask: 14392</t>
         </is>
       </c>
     </row>
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="C43" t="n">
-        <v>7828</v>
+        <v>7321</v>
       </c>
       <c r="D43" t="n">
-        <v>3904</v>
+        <v>7234</v>
       </c>
     </row>
     <row r="44">
@@ -8604,13 +8604,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93</v>
+        <v>421</v>
       </c>
       <c r="C44" t="n">
-        <v>8254</v>
+        <v>9495</v>
       </c>
       <c r="D44" t="n">
-        <v>3385</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="46">
@@ -8642,13 +8642,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C47" t="n">
-        <v>66.5</v>
+        <v>49.9</v>
       </c>
       <c r="D47" t="n">
-        <v>33.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="48">
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="C48" t="n">
-        <v>70.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="D48" t="n">
-        <v>28.9</v>
+        <v>31.1</v>
       </c>
     </row>
   </sheetData>
@@ -8684,7 +8684,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 11901 ask: 12077</t>
+          <t>Day 1 — Active bid: 15327 ask: 14727</t>
         </is>
       </c>
     </row>
@@ -8717,13 +8717,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>1048</v>
       </c>
       <c r="C3" t="n">
-        <v>7235</v>
+        <v>6960</v>
       </c>
       <c r="D3" t="n">
-        <v>4392</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="4">
@@ -8733,13 +8733,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>268</v>
+        <v>1227</v>
       </c>
       <c r="C4" t="n">
-        <v>7555</v>
+        <v>8868</v>
       </c>
       <c r="D4" t="n">
-        <v>4254</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="6">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="C7" t="n">
-        <v>60.8</v>
+        <v>45.4</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="8">
@@ -8787,19 +8787,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>62.6</v>
+        <v>60.2</v>
       </c>
       <c r="D8" t="n">
-        <v>35.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 13998 ask: 14001</t>
+          <t>Day 2 — Active bid: 17896 ask: 17356</t>
         </is>
       </c>
     </row>
@@ -8832,13 +8832,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>310</v>
+        <v>894</v>
       </c>
       <c r="C13" t="n">
-        <v>9845</v>
+        <v>9730</v>
       </c>
       <c r="D13" t="n">
-        <v>3843</v>
+        <v>7272</v>
       </c>
     </row>
     <row r="14">
@@ -8848,13 +8848,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>484</v>
+        <v>1206</v>
       </c>
       <c r="C14" t="n">
-        <v>9820</v>
+        <v>11870</v>
       </c>
       <c r="D14" t="n">
-        <v>3697</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="16">
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>70.3</v>
+        <v>54.4</v>
       </c>
       <c r="D17" t="n">
-        <v>27.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="18">
@@ -8902,19 +8902,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5</v>
+        <v>6.9</v>
       </c>
       <c r="C18" t="n">
-        <v>70.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>26.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 14075 ask: 13656</t>
+          <t>Day 3 — Active bid: 17735 ask: 17018</t>
         </is>
       </c>
     </row>
@@ -8947,13 +8947,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>444</v>
+        <v>1040</v>
       </c>
       <c r="C23" t="n">
-        <v>9534</v>
+        <v>9328</v>
       </c>
       <c r="D23" t="n">
-        <v>4097</v>
+        <v>7367</v>
       </c>
     </row>
     <row r="24">
@@ -8963,13 +8963,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>450</v>
+        <v>1171</v>
       </c>
       <c r="C24" t="n">
-        <v>9516</v>
+        <v>11568</v>
       </c>
       <c r="D24" t="n">
-        <v>3690</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="26">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="C27" t="n">
-        <v>67.7</v>
+        <v>52.6</v>
       </c>
       <c r="D27" t="n">
-        <v>29.1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="28">
@@ -9017,19 +9017,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.3</v>
+        <v>6.9</v>
       </c>
       <c r="C28" t="n">
-        <v>69.7</v>
+        <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 14540 ask: 13035</t>
+          <t>Day 4 — Active bid: 17808 ask: 16865</t>
         </is>
       </c>
     </row>
@@ -9062,13 +9062,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>349</v>
+        <v>944</v>
       </c>
       <c r="C33" t="n">
-        <v>10003</v>
+        <v>9623</v>
       </c>
       <c r="D33" t="n">
-        <v>4188</v>
+        <v>7241</v>
       </c>
     </row>
     <row r="34">
@@ -9078,13 +9078,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>309</v>
+        <v>1139</v>
       </c>
       <c r="C34" t="n">
-        <v>9378</v>
+        <v>11598</v>
       </c>
       <c r="D34" t="n">
-        <v>3348</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="36">
@@ -9116,13 +9116,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="C37" t="n">
-        <v>68.8</v>
+        <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>28.8</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="38">
@@ -9132,19 +9132,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="C38" t="n">
-        <v>71.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="D38" t="n">
-        <v>25.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 14546 ask: 13533</t>
+          <t>Day 5 — Active bid: 18072 ask: 17223</t>
         </is>
       </c>
     </row>
@@ -9177,13 +9177,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>219</v>
+        <v>829</v>
       </c>
       <c r="C43" t="n">
-        <v>10403</v>
+        <v>10079</v>
       </c>
       <c r="D43" t="n">
-        <v>3924</v>
+        <v>7164</v>
       </c>
     </row>
     <row r="44">
@@ -9193,13 +9193,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>382</v>
+        <v>1034</v>
       </c>
       <c r="C44" t="n">
-        <v>9747</v>
+        <v>12151</v>
       </c>
       <c r="D44" t="n">
-        <v>3404</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="46">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="C47" t="n">
-        <v>71.5</v>
+        <v>55.8</v>
       </c>
       <c r="D47" t="n">
-        <v>27</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="48">
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>25.2</v>
+        <v>23.4</v>
       </c>
     </row>
   </sheetData>
@@ -9273,7 +9273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 17337 ask: 17437</t>
+          <t>Day 1 — Active bid: 18163 ask: 17866</t>
         </is>
       </c>
     </row>
@@ -9306,13 +9306,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10266</v>
+        <v>15313</v>
       </c>
       <c r="C3" t="n">
-        <v>262</v>
+        <v>419</v>
       </c>
       <c r="D3" t="n">
-        <v>6809</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="4">
@@ -9322,13 +9322,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10372</v>
+        <v>15203</v>
       </c>
       <c r="C4" t="n">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="D4" t="n">
-        <v>6789</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="6">
@@ -9360,13 +9360,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.2</v>
+        <v>84.3</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="D7" t="n">
-        <v>39.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="8">
@@ -9376,19 +9376,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>38.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19706 ask: 19604</t>
+          <t>Day 2 — Active bid: 19647 ask: 19864</t>
         </is>
       </c>
     </row>
@@ -9421,13 +9421,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10061</v>
+        <v>16398</v>
       </c>
       <c r="C13" t="n">
-        <v>336</v>
+        <v>454</v>
       </c>
       <c r="D13" t="n">
-        <v>9309</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="14">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10069</v>
+        <v>16643</v>
       </c>
       <c r="C14" t="n">
-        <v>318</v>
+        <v>450</v>
       </c>
       <c r="D14" t="n">
-        <v>9217</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="16">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.1</v>
+        <v>83.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>47.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="18">
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.4</v>
+        <v>83.8</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19542 ask: 19981</t>
+          <t>Day 3 — Active bid: 19266 ask: 19770</t>
         </is>
       </c>
     </row>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9712</v>
+        <v>17366</v>
       </c>
       <c r="C23" t="n">
-        <v>514</v>
+        <v>350</v>
       </c>
       <c r="D23" t="n">
-        <v>9316</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="24">
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9951</v>
+        <v>17745</v>
       </c>
       <c r="C24" t="n">
-        <v>539</v>
+        <v>368</v>
       </c>
       <c r="D24" t="n">
-        <v>9491</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="26">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="D27" t="n">
-        <v>47.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -9606,19 +9606,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49.8</v>
+        <v>89.8</v>
       </c>
       <c r="C28" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="D28" t="n">
-        <v>47.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19466 ask: 19594</t>
+          <t>Day 4 — Active bid: 19443 ask: 19488</t>
         </is>
       </c>
     </row>
@@ -9651,13 +9651,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8464</v>
+        <v>16178</v>
       </c>
       <c r="C33" t="n">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="D33" t="n">
-        <v>10485</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="34">
@@ -9667,13 +9667,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8690</v>
+        <v>16421</v>
       </c>
       <c r="C34" t="n">
-        <v>508</v>
+        <v>464</v>
       </c>
       <c r="D34" t="n">
-        <v>10396</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="36">
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>43.5</v>
+        <v>83.2</v>
       </c>
       <c r="C37" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="D37" t="n">
-        <v>53.9</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="38">
@@ -9721,19 +9721,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>44.4</v>
+        <v>84.3</v>
       </c>
       <c r="C38" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D38" t="n">
-        <v>53.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18452 ask: 18622</t>
+          <t>Day 5 — Active bid: 18230 ask: 18960</t>
         </is>
       </c>
     </row>
@@ -9766,13 +9766,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4527</v>
+        <v>12185</v>
       </c>
       <c r="C43" t="n">
-        <v>295</v>
+        <v>788</v>
       </c>
       <c r="D43" t="n">
-        <v>13630</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="44">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4561</v>
+        <v>12747</v>
       </c>
       <c r="C44" t="n">
-        <v>356</v>
+        <v>768</v>
       </c>
       <c r="D44" t="n">
-        <v>13705</v>
+        <v>5445</v>
       </c>
     </row>
     <row r="46">
@@ -9820,13 +9820,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24.5</v>
+        <v>66.8</v>
       </c>
       <c r="C47" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="D47" t="n">
-        <v>73.90000000000001</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="48">
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.5</v>
+        <v>67.2</v>
       </c>
       <c r="C48" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="D48" t="n">
-        <v>73.59999999999999</v>
+        <v>28.7</v>
       </c>
     </row>
   </sheetData>
@@ -9862,7 +9862,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18272 ask: 18370</t>
+          <t>Day 1 — Active bid: 18357 ask: 18108</t>
         </is>
       </c>
     </row>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10743</v>
+        <v>15517</v>
       </c>
       <c r="C3" t="n">
-        <v>277</v>
+        <v>432</v>
       </c>
       <c r="D3" t="n">
-        <v>7252</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="4">
@@ -9911,13 +9911,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10924</v>
+        <v>15478</v>
       </c>
       <c r="C4" t="n">
-        <v>287</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
-        <v>7159</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="6">
@@ -9949,13 +9949,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.8</v>
+        <v>84.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="D7" t="n">
-        <v>39.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="8">
@@ -9965,19 +9965,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.5</v>
+        <v>85.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20651 ask: 20715</t>
+          <t>Day 2 — Active bid: 19725 ask: 20071</t>
         </is>
       </c>
     </row>
@@ -10010,13 +10010,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10544</v>
+        <v>16572</v>
       </c>
       <c r="C13" t="n">
-        <v>350</v>
+        <v>457</v>
       </c>
       <c r="D13" t="n">
-        <v>9757</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="14">
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10609</v>
+        <v>16873</v>
       </c>
       <c r="C14" t="n">
-        <v>339</v>
+        <v>470</v>
       </c>
       <c r="D14" t="n">
-        <v>9767</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="16">
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.1</v>
+        <v>84</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>47.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="18">
@@ -10080,19 +10080,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="D18" t="n">
-        <v>47.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20426 ask: 20850</t>
+          <t>Day 3 — Active bid: 19210 ask: 19992</t>
         </is>
       </c>
     </row>
@@ -10125,13 +10125,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10217</v>
+        <v>17347</v>
       </c>
       <c r="C23" t="n">
-        <v>541</v>
+        <v>384</v>
       </c>
       <c r="D23" t="n">
-        <v>9668</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="24">
@@ -10141,13 +10141,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10510</v>
+        <v>17957</v>
       </c>
       <c r="C24" t="n">
-        <v>565</v>
+        <v>423</v>
       </c>
       <c r="D24" t="n">
-        <v>9775</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="26">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>90.3</v>
       </c>
       <c r="C27" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>47.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="28">
@@ -10195,19 +10195,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50.4</v>
+        <v>89.8</v>
       </c>
       <c r="C28" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="D28" t="n">
-        <v>46.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20736 ask: 20973</t>
+          <t>Day 4 — Active bid: 19756 ask: 19661</t>
         </is>
       </c>
     </row>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9031</v>
+        <v>16574</v>
       </c>
       <c r="C33" t="n">
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="D33" t="n">
-        <v>11155</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="34">
@@ -10256,13 +10256,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9318</v>
+        <v>16654</v>
       </c>
       <c r="C34" t="n">
-        <v>539</v>
+        <v>483</v>
       </c>
       <c r="D34" t="n">
-        <v>11116</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="36">
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>43.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D37" t="n">
-        <v>53.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="38">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>44.4</v>
+        <v>84.7</v>
       </c>
       <c r="C38" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D38" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20661 ask: 20657</t>
+          <t>Day 5 — Active bid: 18606 ask: 19235</t>
         </is>
       </c>
     </row>
@@ -10355,13 +10355,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5239</v>
+        <v>12459</v>
       </c>
       <c r="C43" t="n">
-        <v>348</v>
+        <v>799</v>
       </c>
       <c r="D43" t="n">
-        <v>15074</v>
+        <v>5348</v>
       </c>
     </row>
     <row r="44">
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5235</v>
+        <v>13178</v>
       </c>
       <c r="C44" t="n">
-        <v>388</v>
+        <v>755</v>
       </c>
       <c r="D44" t="n">
-        <v>15034</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="46">
@@ -10409,13 +10409,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25.4</v>
+        <v>67</v>
       </c>
       <c r="C47" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="D47" t="n">
-        <v>73</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="48">
@@ -10425,13 +10425,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25.3</v>
+        <v>68.5</v>
       </c>
       <c r="C48" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="D48" t="n">
-        <v>72.8</v>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>
@@ -10451,7 +10451,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 17905 ask: 17684</t>
+          <t>Day 1 — Active bid: 20316 ask: 20270</t>
         </is>
       </c>
     </row>
@@ -10484,13 +10484,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>510</v>
+        <v>744</v>
       </c>
       <c r="C3" t="n">
-        <v>14577</v>
+        <v>15660</v>
       </c>
       <c r="D3" t="n">
-        <v>2818</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="4">
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>301</v>
+        <v>645</v>
       </c>
       <c r="C4" t="n">
-        <v>14618</v>
+        <v>16700</v>
       </c>
       <c r="D4" t="n">
-        <v>2765</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="6">
@@ -10538,13 +10538,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="C7" t="n">
-        <v>81.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>15.7</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="8">
@@ -10554,19 +10554,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="C8" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19238 ask: 19184</t>
+          <t>Day 2 — Active bid: 21036 ask: 21237</t>
         </is>
       </c>
     </row>
@@ -10599,13 +10599,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>314</v>
+        <v>473</v>
       </c>
       <c r="C13" t="n">
-        <v>16895</v>
+        <v>17533</v>
       </c>
       <c r="D13" t="n">
-        <v>2029</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="14">
@@ -10615,13 +10615,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>367</v>
+        <v>702</v>
       </c>
       <c r="C14" t="n">
-        <v>16667</v>
+        <v>17950</v>
       </c>
       <c r="D14" t="n">
-        <v>2150</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="16">
@@ -10653,13 +10653,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="C17" t="n">
-        <v>87.8</v>
+        <v>83.3</v>
       </c>
       <c r="D17" t="n">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="18">
@@ -10669,19 +10669,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="C18" t="n">
-        <v>86.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D18" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19112 ask: 19665</t>
+          <t>Day 3 — Active bid: 21089 ask: 21653</t>
         </is>
       </c>
     </row>
@@ -10714,13 +10714,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>412</v>
+        <v>541</v>
       </c>
       <c r="C23" t="n">
-        <v>16616</v>
+        <v>17744</v>
       </c>
       <c r="D23" t="n">
-        <v>2084</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="24">
@@ -10730,13 +10730,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>542</v>
+        <v>986</v>
       </c>
       <c r="C24" t="n">
-        <v>16700</v>
+        <v>18026</v>
       </c>
       <c r="D24" t="n">
-        <v>2423</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="26">
@@ -10768,13 +10768,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="C27" t="n">
-        <v>86.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>10.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="28">
@@ -10784,19 +10784,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="C28" t="n">
-        <v>84.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="D28" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19123 ask: 18928</t>
+          <t>Day 4 — Active bid: 21091 ask: 20937</t>
         </is>
       </c>
     </row>
@@ -10829,13 +10829,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>336</v>
+        <v>437</v>
       </c>
       <c r="C33" t="n">
-        <v>16674</v>
+        <v>17394</v>
       </c>
       <c r="D33" t="n">
-        <v>2113</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="34">
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
       <c r="C34" t="n">
-        <v>16687</v>
+        <v>18327</v>
       </c>
       <c r="D34" t="n">
-        <v>1892</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="36">
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="C37" t="n">
-        <v>87.2</v>
+        <v>82.5</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="38">
@@ -10899,19 +10899,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="C38" t="n">
-        <v>88.2</v>
+        <v>87.5</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 17101 ask: 16975</t>
+          <t>Day 5 — Active bid: 19681 ask: 19917</t>
         </is>
       </c>
     </row>
@@ -10944,13 +10944,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>348</v>
+        <v>575</v>
       </c>
       <c r="C43" t="n">
-        <v>13940</v>
+        <v>15096</v>
       </c>
       <c r="D43" t="n">
-        <v>2813</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="44">
@@ -10960,13 +10960,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>360</v>
+        <v>693</v>
       </c>
       <c r="C44" t="n">
-        <v>13986</v>
+        <v>16252</v>
       </c>
       <c r="D44" t="n">
-        <v>2629</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="46">
@@ -10998,13 +10998,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="C47" t="n">
-        <v>81.5</v>
+        <v>76.7</v>
       </c>
       <c r="D47" t="n">
-        <v>16.4</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="48">
@@ -11014,13 +11014,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="C48" t="n">
-        <v>82.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>
@@ -11040,7 +11040,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19462 ask: 19054</t>
+          <t>Day 1 — Active bid: 21415 ask: 21589</t>
         </is>
       </c>
     </row>
@@ -11073,13 +11073,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>603</v>
+        <v>958</v>
       </c>
       <c r="C3" t="n">
-        <v>16157</v>
+        <v>16914</v>
       </c>
       <c r="D3" t="n">
-        <v>2702</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="4">
@@ -11089,13 +11089,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>417</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>16149</v>
+        <v>18063</v>
       </c>
       <c r="D4" t="n">
-        <v>2488</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="6">
@@ -11127,13 +11127,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="8">
@@ -11143,19 +11143,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="C8" t="n">
-        <v>84.8</v>
+        <v>83.7</v>
       </c>
       <c r="D8" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20332 ask: 20256</t>
+          <t>Day 2 — Active bid: 22039 ask: 22296</t>
         </is>
       </c>
     </row>
@@ -11188,13 +11188,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>355</v>
+        <v>600</v>
       </c>
       <c r="C13" t="n">
-        <v>18058</v>
+        <v>18642</v>
       </c>
       <c r="D13" t="n">
-        <v>1919</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="14">
@@ -11204,13 +11204,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>392</v>
+        <v>870</v>
       </c>
       <c r="C14" t="n">
-        <v>17846</v>
+        <v>19085</v>
       </c>
       <c r="D14" t="n">
-        <v>2018</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="16">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="C17" t="n">
-        <v>88.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>9.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="18">
@@ -11258,19 +11258,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="C18" t="n">
-        <v>88.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20451 ask: 20783</t>
+          <t>Day 3 — Active bid: 22163 ask: 22560</t>
         </is>
       </c>
     </row>
@@ -11303,13 +11303,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>464</v>
+        <v>732</v>
       </c>
       <c r="C23" t="n">
-        <v>18127</v>
+        <v>18827</v>
       </c>
       <c r="D23" t="n">
-        <v>1860</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="24">
@@ -11319,13 +11319,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>612</v>
+        <v>1103</v>
       </c>
       <c r="C24" t="n">
-        <v>18000</v>
+        <v>19184</v>
       </c>
       <c r="D24" t="n">
-        <v>2171</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="26">
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="C27" t="n">
-        <v>88.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>9.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="28">
@@ -11373,19 +11373,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="C28" t="n">
-        <v>86.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20223 ask: 19957</t>
+          <t>Day 4 — Active bid: 21960 ask: 22053</t>
         </is>
       </c>
     </row>
@@ -11418,13 +11418,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>378</v>
+        <v>567</v>
       </c>
       <c r="C33" t="n">
-        <v>17828</v>
+        <v>18507</v>
       </c>
       <c r="D33" t="n">
-        <v>2017</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="34">
@@ -11434,13 +11434,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>406</v>
+        <v>634</v>
       </c>
       <c r="C34" t="n">
-        <v>17805</v>
+        <v>19542</v>
       </c>
       <c r="D34" t="n">
-        <v>1746</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="36">
@@ -11472,13 +11472,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="C37" t="n">
-        <v>88.2</v>
+        <v>84.3</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="38">
@@ -11488,19 +11488,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="C38" t="n">
-        <v>89.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18282 ask: 18474</t>
+          <t>Day 5 — Active bid: 20914 ask: 21509</t>
         </is>
       </c>
     </row>
@@ -11533,13 +11533,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>405</v>
+        <v>724</v>
       </c>
       <c r="C43" t="n">
-        <v>15322</v>
+        <v>16519</v>
       </c>
       <c r="D43" t="n">
-        <v>2555</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="44">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>447</v>
+        <v>899</v>
       </c>
       <c r="C44" t="n">
-        <v>15537</v>
+        <v>17826</v>
       </c>
       <c r="D44" t="n">
-        <v>2490</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="46">
@@ -11587,13 +11587,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="C47" t="n">
-        <v>83.8</v>
+        <v>79</v>
       </c>
       <c r="D47" t="n">
-        <v>14</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="48">
@@ -11603,13 +11603,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="C48" t="n">
-        <v>84.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>
@@ -11629,7 +11629,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 23119 ask: 23114</t>
+          <t>Day 1 — Active bid: 16726 ask: 15890</t>
         </is>
       </c>
     </row>
@@ -11662,13 +11662,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>15413</v>
       </c>
       <c r="D3" t="n">
-        <v>23101</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="4">
@@ -11678,13 +11678,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>14131</v>
       </c>
       <c r="D4" t="n">
-        <v>23100</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="6">
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>99.90000000000001</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8">
@@ -11732,19 +11732,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>99.90000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23314 ask: 23320</t>
+          <t>Day 2 — Active bid: 19170 ask: 17766</t>
         </is>
       </c>
     </row>
@@ -11777,13 +11777,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>18528</v>
       </c>
       <c r="D13" t="n">
-        <v>23301</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>16855</v>
       </c>
       <c r="D14" t="n">
-        <v>23314</v>
+        <v>728</v>
       </c>
     </row>
     <row r="16">
@@ -11831,13 +11831,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1</v>
+        <v>96.7</v>
       </c>
       <c r="D17" t="n">
-        <v>99.90000000000001</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -11847,19 +11847,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23334 ask: 23343</t>
+          <t>Day 3 — Active bid: 18108 ask: 17994</t>
         </is>
       </c>
     </row>
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>16934</v>
       </c>
       <c r="D23" t="n">
-        <v>23324</v>
+        <v>812</v>
       </c>
     </row>
     <row r="24">
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>16380</v>
       </c>
       <c r="D24" t="n">
-        <v>23338</v>
+        <v>994</v>
       </c>
     </row>
     <row r="26">
@@ -11946,13 +11946,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="28">
@@ -11962,19 +11962,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23355 ask: 23367</t>
+          <t>Day 4 — Active bid: 18378 ask: 18313</t>
         </is>
       </c>
     </row>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>17561</v>
       </c>
       <c r="D33" t="n">
-        <v>23351</v>
+        <v>666</v>
       </c>
     </row>
     <row r="34">
@@ -12023,13 +12023,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>17146</v>
       </c>
       <c r="D34" t="n">
-        <v>23363</v>
+        <v>862</v>
       </c>
     </row>
     <row r="36">
@@ -12061,13 +12061,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="38">
@@ -12077,19 +12077,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23343 ask: 23331</t>
+          <t>Day 5 — Active bid: 18969 ask: 16490</t>
         </is>
       </c>
     </row>
@@ -12122,13 +12122,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>18365</v>
       </c>
       <c r="D43" t="n">
-        <v>23340</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44">
@@ -12138,13 +12138,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>15458</v>
       </c>
       <c r="D44" t="n">
-        <v>23324</v>
+        <v>771</v>
       </c>
     </row>
     <row r="46">
@@ -12176,13 +12176,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="48">
@@ -12192,13 +12192,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>93.7</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>

--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -1027,7 +1027,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19195 ask: 19298</t>
+          <t>Day 1 — Active bid: 19769 ask: 19788</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="C3" t="n">
-        <v>17854</v>
+        <v>17245</v>
       </c>
       <c r="D3" t="n">
-        <v>866</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="4">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>702</v>
+        <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>17461</v>
+        <v>16532</v>
       </c>
       <c r="D4" t="n">
-        <v>1135</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="6">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>87.2</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="8">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="C8" t="n">
-        <v>90.5</v>
+        <v>83.5</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20994 ask: 21277</t>
+          <t>Day 2 — Active bid: 21383 ask: 21416</t>
         </is>
       </c>
     </row>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="C13" t="n">
-        <v>20338</v>
+        <v>17607</v>
       </c>
       <c r="D13" t="n">
-        <v>476</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="14">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="C14" t="n">
-        <v>20223</v>
+        <v>19624</v>
       </c>
       <c r="D14" t="n">
-        <v>692</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="16">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>96.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="18">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C18" t="n">
-        <v>95</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20598 ask: 20639</t>
+          <t>Day 3 — Active bid: 21085 ask: 21105</t>
         </is>
       </c>
     </row>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>487</v>
+        <v>425</v>
       </c>
       <c r="C23" t="n">
-        <v>19537</v>
+        <v>17650</v>
       </c>
       <c r="D23" t="n">
-        <v>574</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="24">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>836</v>
+        <v>767</v>
       </c>
       <c r="C24" t="n">
-        <v>18900</v>
+        <v>17366</v>
       </c>
       <c r="D24" t="n">
-        <v>903</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="26">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>94.8</v>
+        <v>83.7</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="28">
@@ -1360,19 +1360,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="C28" t="n">
-        <v>91.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="D28" t="n">
-        <v>4.4</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20756 ask: 21113</t>
+          <t>Day 4 — Active bid: 21269 ask: 21349</t>
         </is>
       </c>
     </row>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="C33" t="n">
-        <v>19909</v>
+        <v>17766</v>
       </c>
       <c r="D33" t="n">
-        <v>545</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="34">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C34" t="n">
-        <v>19864</v>
+        <v>18803</v>
       </c>
       <c r="D34" t="n">
-        <v>764</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="36">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C37" t="n">
-        <v>95.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="D37" t="n">
-        <v>2.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="38">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C38" t="n">
-        <v>94.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20604 ask: 21158</t>
+          <t>Day 5 — Active bid: 21346 ask: 21452</t>
         </is>
       </c>
     </row>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="C43" t="n">
-        <v>20047</v>
+        <v>17548</v>
       </c>
       <c r="D43" t="n">
-        <v>336</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="44">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>471</v>
+        <v>410</v>
       </c>
       <c r="C44" t="n">
-        <v>19885</v>
+        <v>18707</v>
       </c>
       <c r="D44" t="n">
-        <v>802</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="46">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C47" t="n">
-        <v>97.3</v>
+        <v>82.2</v>
       </c>
       <c r="D47" t="n">
-        <v>1.6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="C48" t="n">
-        <v>94</v>
+        <v>87.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3.8</v>
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>
@@ -2794,7 +2794,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19007 ask: 19116</t>
+          <t>Day 1 — Active bid: 19546 ask: 19545</t>
         </is>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8892</v>
+        <v>6070</v>
       </c>
       <c r="C3" t="n">
-        <v>8511</v>
+        <v>10487</v>
       </c>
       <c r="D3" t="n">
-        <v>1604</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="4">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8960</v>
+        <v>6174</v>
       </c>
       <c r="C4" t="n">
-        <v>8235</v>
+        <v>10303</v>
       </c>
       <c r="D4" t="n">
-        <v>1921</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="6">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46.8</v>
+        <v>31.1</v>
       </c>
       <c r="C7" t="n">
-        <v>44.8</v>
+        <v>53.7</v>
       </c>
       <c r="D7" t="n">
-        <v>8.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="8">
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.9</v>
+        <v>31.6</v>
       </c>
       <c r="C8" t="n">
-        <v>43.1</v>
+        <v>52.7</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19817 ask: 19046</t>
+          <t>Day 2 — Active bid: 20391 ask: 19994</t>
         </is>
       </c>
     </row>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8292</v>
+        <v>5974</v>
       </c>
       <c r="C13" t="n">
-        <v>10022</v>
+        <v>11316</v>
       </c>
       <c r="D13" t="n">
-        <v>1503</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="14">
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8142</v>
+        <v>4922</v>
       </c>
       <c r="C14" t="n">
-        <v>9548</v>
+        <v>11607</v>
       </c>
       <c r="D14" t="n">
-        <v>1356</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="16">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.8</v>
+        <v>29.3</v>
       </c>
       <c r="C17" t="n">
-        <v>50.6</v>
+        <v>55.5</v>
       </c>
       <c r="D17" t="n">
-        <v>7.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="18">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.7</v>
+        <v>24.6</v>
       </c>
       <c r="C18" t="n">
-        <v>50.1</v>
+        <v>58.1</v>
       </c>
       <c r="D18" t="n">
-        <v>7.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19823 ask: 18995</t>
+          <t>Day 3 — Active bid: 20031 ask: 19554</t>
         </is>
       </c>
     </row>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12745</v>
+        <v>10454</v>
       </c>
       <c r="C23" t="n">
-        <v>5465</v>
+        <v>7372</v>
       </c>
       <c r="D23" t="n">
-        <v>1613</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="24">
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12150</v>
+        <v>7708</v>
       </c>
       <c r="C24" t="n">
-        <v>5290</v>
+        <v>9254</v>
       </c>
       <c r="D24" t="n">
-        <v>1555</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="26">
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.3</v>
+        <v>52.2</v>
       </c>
       <c r="C27" t="n">
-        <v>27.6</v>
+        <v>36.8</v>
       </c>
       <c r="D27" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64</v>
+        <v>39.4</v>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>47.3</v>
       </c>
       <c r="D28" t="n">
-        <v>8.199999999999999</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 17969 ask: 18233</t>
+          <t>Day 4 — Active bid: 19114 ask: 19148</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3317</v>
+        <v>1963</v>
       </c>
       <c r="C33" t="n">
-        <v>12692</v>
+        <v>11588</v>
       </c>
       <c r="D33" t="n">
-        <v>1960</v>
+        <v>5563</v>
       </c>
     </row>
     <row r="34">
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3490</v>
+        <v>2434</v>
       </c>
       <c r="C34" t="n">
-        <v>12201</v>
+        <v>10862</v>
       </c>
       <c r="D34" t="n">
-        <v>2542</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="36">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.5</v>
+        <v>10.3</v>
       </c>
       <c r="C37" t="n">
-        <v>70.59999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="D37" t="n">
-        <v>10.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="38">
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.1</v>
+        <v>12.7</v>
       </c>
       <c r="C38" t="n">
-        <v>66.90000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20046 ask: 19184</t>
+          <t>Day 5 — Active bid: 20391 ask: 20050</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6562</v>
+        <v>4788</v>
       </c>
       <c r="C43" t="n">
-        <v>12066</v>
+        <v>13078</v>
       </c>
       <c r="D43" t="n">
-        <v>1418</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="44">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6212</v>
+        <v>2690</v>
       </c>
       <c r="C44" t="n">
-        <v>11665</v>
+        <v>13289</v>
       </c>
       <c r="D44" t="n">
-        <v>1307</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="46">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32.7</v>
+        <v>23.5</v>
       </c>
       <c r="C47" t="n">
-        <v>60.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>7.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="48">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32.4</v>
+        <v>13.4</v>
       </c>
       <c r="C48" t="n">
-        <v>60.8</v>
+        <v>66.3</v>
       </c>
       <c r="D48" t="n">
-        <v>6.8</v>
+        <v>20.3</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3383,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 20096 ask: 20248</t>
+          <t>Day 1 — Active bid: 20947 ask: 20998</t>
         </is>
       </c>
     </row>
@@ -3416,13 +3416,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9549</v>
+        <v>6617</v>
       </c>
       <c r="C3" t="n">
-        <v>9149</v>
+        <v>11346</v>
       </c>
       <c r="D3" t="n">
-        <v>1398</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="4">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9556</v>
+        <v>6772</v>
       </c>
       <c r="C4" t="n">
-        <v>9032</v>
+        <v>11310</v>
       </c>
       <c r="D4" t="n">
-        <v>1660</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="6">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.5</v>
+        <v>31.6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.5</v>
+        <v>54.2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="8">
@@ -3486,19 +3486,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.2</v>
+        <v>32.3</v>
       </c>
       <c r="C8" t="n">
-        <v>44.6</v>
+        <v>53.9</v>
       </c>
       <c r="D8" t="n">
-        <v>8.199999999999999</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20759 ask: 20431</t>
+          <t>Day 2 — Active bid: 21589 ask: 21483</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8823</v>
+        <v>6515</v>
       </c>
       <c r="C13" t="n">
-        <v>10740</v>
+        <v>11999</v>
       </c>
       <c r="D13" t="n">
-        <v>1196</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="14">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8699</v>
+        <v>5410</v>
       </c>
       <c r="C14" t="n">
-        <v>10527</v>
+        <v>12948</v>
       </c>
       <c r="D14" t="n">
-        <v>1205</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="16">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.5</v>
+        <v>30.2</v>
       </c>
       <c r="C17" t="n">
-        <v>51.7</v>
+        <v>55.6</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="18">
@@ -3601,19 +3601,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.6</v>
+        <v>25.2</v>
       </c>
       <c r="C18" t="n">
-        <v>51.5</v>
+        <v>60.3</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20526 ask: 19870</t>
+          <t>Day 3 — Active bid: 20977 ask: 20848</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13196</v>
+        <v>10738</v>
       </c>
       <c r="C23" t="n">
-        <v>5778</v>
+        <v>8116</v>
       </c>
       <c r="D23" t="n">
-        <v>1552</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="24">
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12794</v>
+        <v>8600</v>
       </c>
       <c r="C24" t="n">
-        <v>5679</v>
+        <v>9824</v>
       </c>
       <c r="D24" t="n">
-        <v>1397</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="26">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.3</v>
+        <v>51.2</v>
       </c>
       <c r="C27" t="n">
-        <v>28.1</v>
+        <v>38.7</v>
       </c>
       <c r="D27" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="28">
@@ -3716,19 +3716,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64.40000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="C28" t="n">
-        <v>28.6</v>
+        <v>47.1</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 20254 ask: 20743</t>
+          <t>Day 4 — Active bid: 21553 ask: 21614</t>
         </is>
       </c>
     </row>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3888</v>
+        <v>2315</v>
       </c>
       <c r="C33" t="n">
-        <v>14764</v>
+        <v>12437</v>
       </c>
       <c r="D33" t="n">
-        <v>1602</v>
+        <v>6801</v>
       </c>
     </row>
     <row r="34">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4102</v>
+        <v>2953</v>
       </c>
       <c r="C34" t="n">
-        <v>14736</v>
+        <v>14134</v>
       </c>
       <c r="D34" t="n">
-        <v>1905</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="36">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.2</v>
+        <v>10.7</v>
       </c>
       <c r="C37" t="n">
-        <v>72.90000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="D37" t="n">
-        <v>7.9</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="38">
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.8</v>
+        <v>13.7</v>
       </c>
       <c r="C38" t="n">
-        <v>71</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>9.199999999999999</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20990 ask: 20611</t>
+          <t>Day 5 — Active bid: 21536 ask: 21506</t>
         </is>
       </c>
     </row>
@@ -3876,13 +3876,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6885</v>
+        <v>4649</v>
       </c>
       <c r="C43" t="n">
-        <v>12892</v>
+        <v>14131</v>
       </c>
       <c r="D43" t="n">
-        <v>1213</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="44">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6602</v>
+        <v>3254</v>
       </c>
       <c r="C44" t="n">
-        <v>12779</v>
+        <v>14512</v>
       </c>
       <c r="D44" t="n">
-        <v>1230</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="46">
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32.8</v>
+        <v>21.6</v>
       </c>
       <c r="C47" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>5.8</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="48">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>15.1</v>
       </c>
       <c r="C48" t="n">
-        <v>62</v>
+        <v>67.5</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
@@ -5150,7 +5150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 21626 ask: 21811</t>
+          <t>Day 1 — Active bid: 21529 ask: 21529</t>
         </is>
       </c>
     </row>
@@ -5183,13 +5183,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="C3" t="n">
-        <v>2542</v>
+        <v>2549</v>
       </c>
       <c r="D3" t="n">
-        <v>18810</v>
+        <v>18676</v>
       </c>
     </row>
     <row r="4">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="C4" t="n">
-        <v>2588</v>
+        <v>2353</v>
       </c>
       <c r="D4" t="n">
-        <v>18816</v>
+        <v>18729</v>
       </c>
     </row>
     <row r="6">
@@ -5237,13 +5237,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C7" t="n">
         <v>11.8</v>
       </c>
       <c r="D7" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="8">
@@ -5253,19 +5253,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="C8" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="D8" t="n">
-        <v>86.3</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 22706 ask: 22874</t>
+          <t>Day 2 — Active bid: 22635 ask: 22659</t>
         </is>
       </c>
     </row>
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C13" t="n">
-        <v>1211</v>
+        <v>1422</v>
       </c>
       <c r="D13" t="n">
-        <v>21370</v>
+        <v>21103</v>
       </c>
     </row>
     <row r="14">
@@ -5314,13 +5314,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" t="n">
-        <v>1188</v>
+        <v>1555</v>
       </c>
       <c r="D14" t="n">
-        <v>21531</v>
+        <v>20948</v>
       </c>
     </row>
     <row r="16">
@@ -5352,13 +5352,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="D17" t="n">
-        <v>94.09999999999999</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="18">
@@ -5371,16 +5371,16 @@
         <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="D18" t="n">
-        <v>94.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 22623 ask: 22729</t>
+          <t>Day 3 — Active bid: 22511 ask: 22531</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C23" t="n">
-        <v>1917</v>
+        <v>2526</v>
       </c>
       <c r="D23" t="n">
-        <v>20356</v>
+        <v>19628</v>
       </c>
     </row>
     <row r="24">
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C24" t="n">
-        <v>1982</v>
+        <v>2200</v>
       </c>
       <c r="D24" t="n">
-        <v>20399</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="26">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C27" t="n">
-        <v>8.5</v>
+        <v>11.2</v>
       </c>
       <c r="D27" t="n">
-        <v>90</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="28">
@@ -5486,16 +5486,16 @@
         <v>1.5</v>
       </c>
       <c r="C28" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>89.7</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 22703 ask: 22714</t>
+          <t>Day 4 — Active bid: 22620 ask: 22609</t>
         </is>
       </c>
     </row>
@@ -5528,13 +5528,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="C33" t="n">
-        <v>1713</v>
+        <v>1646</v>
       </c>
       <c r="D33" t="n">
-        <v>20627</v>
+        <v>20571</v>
       </c>
     </row>
     <row r="34">
@@ -5544,13 +5544,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="C34" t="n">
-        <v>1651</v>
+        <v>2517</v>
       </c>
       <c r="D34" t="n">
-        <v>20697</v>
+        <v>19796</v>
       </c>
     </row>
     <row r="36">
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="C37" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="D37" t="n">
         <v>90.90000000000001</v>
@@ -5598,19 +5598,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="C38" t="n">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="D38" t="n">
-        <v>91.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 22791 ask: 22768</t>
+          <t>Day 5 — Active bid: 22620 ask: 22580</t>
         </is>
       </c>
     </row>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C43" t="n">
-        <v>1322</v>
+        <v>1782</v>
       </c>
       <c r="D43" t="n">
-        <v>21101</v>
+        <v>20473</v>
       </c>
     </row>
     <row r="44">
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C44" t="n">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="D44" t="n">
-        <v>21012</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="46">
@@ -5700,10 +5700,10 @@
         <v>1.6</v>
       </c>
       <c r="C47" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="D47" t="n">
-        <v>92.59999999999999</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="48">
@@ -5716,10 +5716,10 @@
         <v>1.5</v>
       </c>
       <c r="C48" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D48" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
     </row>
   </sheetData>
@@ -5739,7 +5739,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 22728 ask: 22859</t>
+          <t>Day 1 — Active bid: 22675 ask: 22690</t>
         </is>
       </c>
     </row>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C3" t="n">
-        <v>2965</v>
+        <v>3040</v>
       </c>
       <c r="D3" t="n">
-        <v>19355</v>
+        <v>19221</v>
       </c>
     </row>
     <row r="4">
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C4" t="n">
-        <v>3011</v>
+        <v>2970</v>
       </c>
       <c r="D4" t="n">
-        <v>19351</v>
+        <v>19221</v>
       </c>
     </row>
     <row r="6">
@@ -5829,10 +5829,10 @@
         <v>1.8</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="D7" t="n">
-        <v>85.2</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="8">
@@ -5845,7 +5845,7 @@
         <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D8" t="n">
         <v>84.7</v>
@@ -5854,7 +5854,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23248 ask: 23263</t>
+          <t>Day 2 — Active bid: 23204 ask: 23202</t>
         </is>
       </c>
     </row>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="C13" t="n">
-        <v>1366</v>
+        <v>1218</v>
       </c>
       <c r="D13" t="n">
-        <v>21730</v>
+        <v>21873</v>
       </c>
     </row>
     <row r="14">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C14" t="n">
-        <v>1318</v>
+        <v>1114</v>
       </c>
       <c r="D14" t="n">
-        <v>21765</v>
+        <v>21880</v>
       </c>
     </row>
     <row r="16">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="D17" t="n">
-        <v>93.5</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="18">
@@ -5957,19 +5957,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="D18" t="n">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23148 ask: 23253</t>
+          <t>Day 3 — Active bid: 23153 ask: 23159</t>
         </is>
       </c>
     </row>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C23" t="n">
-        <v>2052</v>
+        <v>1966</v>
       </c>
       <c r="D23" t="n">
-        <v>20711</v>
+        <v>20820</v>
       </c>
     </row>
     <row r="24">
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C24" t="n">
-        <v>2087</v>
+        <v>2337</v>
       </c>
       <c r="D24" t="n">
-        <v>20777</v>
+        <v>20444</v>
       </c>
     </row>
     <row r="26">
@@ -6056,13 +6056,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C27" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="D27" t="n">
-        <v>89.5</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D28" t="n">
-        <v>89.40000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23172 ask: 23156</t>
+          <t>Day 4 — Active bid: 23130 ask: 23126</t>
         </is>
       </c>
     </row>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C33" t="n">
-        <v>1891</v>
+        <v>1605</v>
       </c>
       <c r="D33" t="n">
-        <v>20877</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="34">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="C34" t="n">
-        <v>1888</v>
+        <v>2095</v>
       </c>
       <c r="D34" t="n">
-        <v>20848</v>
+        <v>20669</v>
       </c>
     </row>
     <row r="36">
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C37" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D37" t="n">
-        <v>90.09999999999999</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="38">
@@ -6187,19 +6187,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C38" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D38" t="n">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23227 ask: 23199</t>
+          <t>Day 5 — Active bid: 23248 ask: 23230</t>
         </is>
       </c>
     </row>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C43" t="n">
-        <v>1490</v>
+        <v>1419</v>
       </c>
       <c r="D43" t="n">
-        <v>21308</v>
+        <v>21412</v>
       </c>
     </row>
     <row r="44">
@@ -6248,13 +6248,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="C44" t="n">
-        <v>1531</v>
+        <v>1007</v>
       </c>
       <c r="D44" t="n">
-        <v>21288</v>
+        <v>21885</v>
       </c>
     </row>
     <row r="46">
@@ -6289,10 +6289,10 @@
         <v>1.8</v>
       </c>
       <c r="C47" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="D47" t="n">
-        <v>91.7</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C48" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="D48" t="n">
-        <v>91.8</v>
+        <v>94.2</v>
       </c>
     </row>
   </sheetData>
@@ -9273,7 +9273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18163 ask: 17866</t>
+          <t>Day 1 — Active bid: 18318 ask: 17934</t>
         </is>
       </c>
     </row>
@@ -9306,13 +9306,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15313</v>
+        <v>15477</v>
       </c>
       <c r="C3" t="n">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="D3" t="n">
-        <v>2431</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="4">
@@ -9322,13 +9322,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15203</v>
+        <v>15258</v>
       </c>
       <c r="C4" t="n">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="D4" t="n">
-        <v>2304</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="6">
@@ -9360,13 +9360,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="D7" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="8">
@@ -9379,16 +9379,16 @@
         <v>85.09999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19647 ask: 19864</t>
+          <t>Day 2 — Active bid: 19568 ask: 19830</t>
         </is>
       </c>
     </row>
@@ -9421,13 +9421,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16398</v>
+        <v>16399</v>
       </c>
       <c r="C13" t="n">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="D13" t="n">
-        <v>2795</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="14">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16643</v>
+        <v>16602</v>
       </c>
       <c r="C14" t="n">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="D14" t="n">
-        <v>2771</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="16">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="D17" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D18" t="n">
         <v>13.9</v>
@@ -9503,7 +9503,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19266 ask: 19770</t>
+          <t>Day 3 — Active bid: 19273 ask: 19863</t>
         </is>
       </c>
     </row>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17366</v>
+        <v>17352</v>
       </c>
       <c r="C23" t="n">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="D23" t="n">
-        <v>1550</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="24">
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17745</v>
+        <v>17876</v>
       </c>
       <c r="C24" t="n">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D24" t="n">
-        <v>1657</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="26">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="C27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="28">
@@ -9606,19 +9606,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="C28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="D28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19443 ask: 19488</t>
+          <t>Day 4 — Active bid: 19564 ask: 19429</t>
         </is>
       </c>
     </row>
@@ -9651,13 +9651,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16178</v>
+        <v>16320</v>
       </c>
       <c r="C33" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D33" t="n">
-        <v>2771</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="34">
@@ -9667,13 +9667,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16421</v>
+        <v>16388</v>
       </c>
       <c r="C34" t="n">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D34" t="n">
-        <v>2603</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="36">
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="C37" t="n">
         <v>2.5</v>
       </c>
       <c r="D37" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="38">
@@ -9727,13 +9727,13 @@
         <v>2.4</v>
       </c>
       <c r="D38" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18230 ask: 18960</t>
+          <t>Day 5 — Active bid: 18147 ask: 18951</t>
         </is>
       </c>
     </row>
@@ -9766,13 +9766,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12185</v>
+        <v>12050</v>
       </c>
       <c r="C43" t="n">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="D43" t="n">
-        <v>5257</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="44">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12747</v>
+        <v>12833</v>
       </c>
       <c r="C44" t="n">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D44" t="n">
-        <v>5445</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="46">
@@ -9820,13 +9820,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D47" t="n">
-        <v>28.8</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="48">
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>67.2</v>
+        <v>67.7</v>
       </c>
       <c r="C48" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
     </row>
   </sheetData>
@@ -9862,7 +9862,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18357 ask: 18108</t>
+          <t>Day 1 — Active bid: 18382 ask: 18126</t>
         </is>
       </c>
     </row>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15517</v>
+        <v>15509</v>
       </c>
       <c r="C3" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D3" t="n">
-        <v>2408</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="4">
@@ -9911,13 +9911,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15478</v>
+        <v>15461</v>
       </c>
       <c r="C4" t="n">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D4" t="n">
-        <v>2249</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="6">
@@ -9949,13 +9949,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D7" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="8">
@@ -9965,19 +9965,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="C8" t="n">
         <v>2.1</v>
       </c>
       <c r="D8" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19725 ask: 20071</t>
+          <t>Day 2 — Active bid: 19650 ask: 19943</t>
         </is>
       </c>
     </row>
@@ -10010,13 +10010,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16572</v>
+        <v>16484</v>
       </c>
       <c r="C13" t="n">
         <v>457</v>
       </c>
       <c r="D13" t="n">
-        <v>2696</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="14">
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16873</v>
+        <v>16815</v>
       </c>
       <c r="C14" t="n">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D14" t="n">
-        <v>2728</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="16">
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="18">
@@ -10080,19 +10080,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D18" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19210 ask: 19992</t>
+          <t>Day 3 — Active bid: 19259 ask: 19742</t>
         </is>
       </c>
     </row>
@@ -10125,13 +10125,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17347</v>
+        <v>17377</v>
       </c>
       <c r="C23" t="n">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D23" t="n">
-        <v>1479</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="24">
@@ -10141,13 +10141,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17957</v>
+        <v>17776</v>
       </c>
       <c r="C24" t="n">
-        <v>423</v>
+        <v>335</v>
       </c>
       <c r="D24" t="n">
-        <v>1612</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="26">
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
@@ -10195,19 +10195,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="C28" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="D28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19756 ask: 19661</t>
+          <t>Day 4 — Active bid: 19718 ask: 19628</t>
         </is>
       </c>
     </row>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16574</v>
+        <v>16589</v>
       </c>
       <c r="C33" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D33" t="n">
-        <v>2672</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="34">
@@ -10256,13 +10256,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16654</v>
+        <v>16622</v>
       </c>
       <c r="C34" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D34" t="n">
-        <v>2524</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="36">
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C37" t="n">
         <v>2.6</v>
       </c>
       <c r="D37" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="38">
@@ -10322,7 +10322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18606 ask: 19235</t>
+          <t>Day 5 — Active bid: 18634 ask: 19236</t>
         </is>
       </c>
     </row>
@@ -10355,13 +10355,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12459</v>
+        <v>12553</v>
       </c>
       <c r="C43" t="n">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="D43" t="n">
-        <v>5348</v>
+        <v>5303</v>
       </c>
     </row>
     <row r="44">
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13178</v>
+        <v>13186</v>
       </c>
       <c r="C44" t="n">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D44" t="n">
-        <v>5302</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="46">
@@ -10409,13 +10409,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>67</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D47" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="48">
@@ -11629,7 +11629,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 16726 ask: 15890</t>
+          <t>Day 1 — Active bid: 17255 ask: 16473</t>
         </is>
       </c>
     </row>
@@ -11662,13 +11662,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="C3" t="n">
-        <v>15413</v>
+        <v>14843</v>
       </c>
       <c r="D3" t="n">
-        <v>1019</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="4">
@@ -11678,13 +11678,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="C4" t="n">
-        <v>14131</v>
+        <v>13440</v>
       </c>
       <c r="D4" t="n">
-        <v>1337</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="6">
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="C7" t="n">
-        <v>92.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="8">
@@ -11732,19 +11732,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="C8" t="n">
-        <v>88.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>8.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19170 ask: 17766</t>
+          <t>Day 2 — Active bid: 19675 ask: 19036</t>
         </is>
       </c>
     </row>
@@ -11777,13 +11777,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C13" t="n">
-        <v>18528</v>
+        <v>17430</v>
       </c>
       <c r="D13" t="n">
-        <v>533</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="14">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C14" t="n">
-        <v>16855</v>
+        <v>15211</v>
       </c>
       <c r="D14" t="n">
-        <v>728</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="16">
@@ -11831,13 +11831,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C17" t="n">
-        <v>96.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -11847,19 +11847,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C18" t="n">
-        <v>94.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 18108 ask: 17994</t>
+          <t>Day 3 — Active bid: 18777 ask: 18891</t>
         </is>
       </c>
     </row>
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="C23" t="n">
-        <v>16934</v>
+        <v>15381</v>
       </c>
       <c r="D23" t="n">
-        <v>812</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="24">
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>620</v>
+        <v>587</v>
       </c>
       <c r="C24" t="n">
-        <v>16380</v>
+        <v>15508</v>
       </c>
       <c r="D24" t="n">
-        <v>994</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="26">
@@ -11946,13 +11946,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="C27" t="n">
-        <v>93.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>4.5</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="28">
@@ -11962,19 +11962,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="C28" t="n">
-        <v>91</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>5.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 18378 ask: 18313</t>
+          <t>Day 4 — Active bid: 19220 ask: 18790</t>
         </is>
       </c>
     </row>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="C33" t="n">
-        <v>17561</v>
+        <v>16061</v>
       </c>
       <c r="D33" t="n">
-        <v>666</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="34">
@@ -12023,13 +12023,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C34" t="n">
-        <v>17146</v>
+        <v>16123</v>
       </c>
       <c r="D34" t="n">
-        <v>862</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="36">
@@ -12061,13 +12061,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C37" t="n">
-        <v>95.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>3.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="38">
@@ -12080,16 +12080,16 @@
         <v>1.7</v>
       </c>
       <c r="C38" t="n">
-        <v>93.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D38" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18969 ask: 16490</t>
+          <t>Day 5 — Active bid: 19962 ask: 18785</t>
         </is>
       </c>
     </row>
@@ -12122,13 +12122,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="C43" t="n">
-        <v>18365</v>
+        <v>17264</v>
       </c>
       <c r="D43" t="n">
-        <v>440</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="44">
@@ -12138,13 +12138,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="C44" t="n">
-        <v>15458</v>
+        <v>14782</v>
       </c>
       <c r="D44" t="n">
-        <v>771</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="46">
@@ -12176,13 +12176,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C47" t="n">
-        <v>96.8</v>
+        <v>86.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="48">
@@ -12192,13 +12192,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="C48" t="n">
-        <v>93.7</v>
+        <v>78.7</v>
       </c>
       <c r="D48" t="n">
-        <v>4.7</v>
+        <v>20.1</v>
       </c>
     </row>
   </sheetData>

--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -1079,10 +1079,10 @@
         <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>16532</v>
+        <v>16534</v>
       </c>
       <c r="D4" t="n">
-        <v>2622</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="6">
@@ -1133,10 +1133,10 @@
         <v>3.2</v>
       </c>
       <c r="C8" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="11">
@@ -1293,10 +1293,10 @@
         <v>425</v>
       </c>
       <c r="C23" t="n">
-        <v>17650</v>
+        <v>17652</v>
       </c>
       <c r="D23" t="n">
-        <v>3010</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="24">
@@ -2794,7 +2794,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19546 ask: 19545</t>
+          <t>Day 1 — Active bid: 19374 ask: 19279</t>
         </is>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6070</v>
+        <v>7013</v>
       </c>
       <c r="C3" t="n">
-        <v>10487</v>
+        <v>10025</v>
       </c>
       <c r="D3" t="n">
-        <v>2989</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="4">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6174</v>
+        <v>7160</v>
       </c>
       <c r="C4" t="n">
-        <v>10303</v>
+        <v>9706</v>
       </c>
       <c r="D4" t="n">
-        <v>3068</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="6">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.1</v>
+        <v>36.2</v>
       </c>
       <c r="C7" t="n">
-        <v>53.7</v>
+        <v>51.7</v>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="8">
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.6</v>
+        <v>37.1</v>
       </c>
       <c r="C8" t="n">
-        <v>52.7</v>
+        <v>50.3</v>
       </c>
       <c r="D8" t="n">
-        <v>15.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20391 ask: 19994</t>
+          <t>Day 2 — Active bid: 20111 ask: 19635</t>
         </is>
       </c>
     </row>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5974</v>
+        <v>7027</v>
       </c>
       <c r="C13" t="n">
-        <v>11316</v>
+        <v>10853</v>
       </c>
       <c r="D13" t="n">
-        <v>3101</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="14">
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4922</v>
+        <v>5619</v>
       </c>
       <c r="C14" t="n">
-        <v>11607</v>
+        <v>11313</v>
       </c>
       <c r="D14" t="n">
-        <v>3465</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="16">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.3</v>
+        <v>34.9</v>
       </c>
       <c r="C17" t="n">
-        <v>55.5</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>15.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="C18" t="n">
-        <v>58.1</v>
+        <v>57.6</v>
       </c>
       <c r="D18" t="n">
-        <v>17.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20031 ask: 19554</t>
+          <t>Day 3 — Active bid: 19910 ask: 19255</t>
         </is>
       </c>
     </row>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10454</v>
+        <v>11370</v>
       </c>
       <c r="C23" t="n">
-        <v>7372</v>
+        <v>6642</v>
       </c>
       <c r="D23" t="n">
-        <v>2205</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="24">
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7708</v>
+        <v>9086</v>
       </c>
       <c r="C24" t="n">
-        <v>9254</v>
+        <v>8002</v>
       </c>
       <c r="D24" t="n">
-        <v>2592</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="26">
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52.2</v>
+        <v>57.1</v>
       </c>
       <c r="C27" t="n">
-        <v>36.8</v>
+        <v>33.4</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="28">
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.4</v>
+        <v>47.2</v>
       </c>
       <c r="C28" t="n">
-        <v>47.3</v>
+        <v>41.6</v>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19114 ask: 19148</t>
+          <t>Day 4 — Active bid: 18603 ask: 18605</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1963</v>
+        <v>2217</v>
       </c>
       <c r="C33" t="n">
-        <v>11588</v>
+        <v>12396</v>
       </c>
       <c r="D33" t="n">
-        <v>5563</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="34">
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2434</v>
+        <v>2725</v>
       </c>
       <c r="C34" t="n">
-        <v>10862</v>
+        <v>11793</v>
       </c>
       <c r="D34" t="n">
-        <v>5852</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="36">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.3</v>
+        <v>11.9</v>
       </c>
       <c r="C37" t="n">
-        <v>60.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>29.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="38">
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12.7</v>
+        <v>14.6</v>
       </c>
       <c r="C38" t="n">
-        <v>56.7</v>
+        <v>63.4</v>
       </c>
       <c r="D38" t="n">
-        <v>30.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20391 ask: 20050</t>
+          <t>Day 5 — Active bid: 20189 ask: 19791</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4788</v>
+        <v>5454</v>
       </c>
       <c r="C43" t="n">
-        <v>13078</v>
+        <v>12834</v>
       </c>
       <c r="D43" t="n">
-        <v>2525</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="44">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2690</v>
+        <v>3309</v>
       </c>
       <c r="C44" t="n">
-        <v>13289</v>
+        <v>13367</v>
       </c>
       <c r="D44" t="n">
-        <v>4071</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="46">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.5</v>
+        <v>27</v>
       </c>
       <c r="C47" t="n">
-        <v>64.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="D47" t="n">
-        <v>12.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="48">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="C48" t="n">
-        <v>66.3</v>
+        <v>67.5</v>
       </c>
       <c r="D48" t="n">
-        <v>20.3</v>
+        <v>15.7</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3383,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 20947 ask: 20998</t>
+          <t>Day 1 — Active bid: 20605 ask: 20709</t>
         </is>
       </c>
     </row>
@@ -3416,13 +3416,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6617</v>
+        <v>7301</v>
       </c>
       <c r="C3" t="n">
-        <v>11346</v>
+        <v>11067</v>
       </c>
       <c r="D3" t="n">
-        <v>2984</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6772</v>
+        <v>7828</v>
       </c>
       <c r="C4" t="n">
-        <v>11310</v>
+        <v>10648</v>
       </c>
       <c r="D4" t="n">
-        <v>2916</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="6">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.6</v>
+        <v>35.4</v>
       </c>
       <c r="C7" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="D7" t="n">
-        <v>14.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="8">
@@ -3486,19 +3486,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.3</v>
+        <v>37.8</v>
       </c>
       <c r="C8" t="n">
-        <v>53.9</v>
+        <v>51.4</v>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 21589 ask: 21483</t>
+          <t>Day 2 — Active bid: 21211 ask: 21135</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6515</v>
+        <v>7323</v>
       </c>
       <c r="C13" t="n">
-        <v>11999</v>
+        <v>11628</v>
       </c>
       <c r="D13" t="n">
-        <v>3075</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="14">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5410</v>
+        <v>6477</v>
       </c>
       <c r="C14" t="n">
-        <v>12948</v>
+        <v>12393</v>
       </c>
       <c r="D14" t="n">
-        <v>3125</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="16">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.2</v>
+        <v>34.5</v>
       </c>
       <c r="C17" t="n">
-        <v>55.6</v>
+        <v>54.8</v>
       </c>
       <c r="D17" t="n">
-        <v>14.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="18">
@@ -3601,19 +3601,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.2</v>
+        <v>30.6</v>
       </c>
       <c r="C18" t="n">
-        <v>60.3</v>
+        <v>58.6</v>
       </c>
       <c r="D18" t="n">
-        <v>14.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20977 ask: 20848</t>
+          <t>Day 3 — Active bid: 20789 ask: 20484</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10738</v>
+        <v>11737</v>
       </c>
       <c r="C23" t="n">
-        <v>8116</v>
+        <v>7219</v>
       </c>
       <c r="D23" t="n">
-        <v>2123</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="24">
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8600</v>
+        <v>9637</v>
       </c>
       <c r="C24" t="n">
-        <v>9824</v>
+        <v>8894</v>
       </c>
       <c r="D24" t="n">
-        <v>2424</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="26">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51.2</v>
+        <v>56.5</v>
       </c>
       <c r="C27" t="n">
-        <v>38.7</v>
+        <v>34.7</v>
       </c>
       <c r="D27" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3716,19 +3716,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41.3</v>
+        <v>47</v>
       </c>
       <c r="C28" t="n">
-        <v>47.1</v>
+        <v>43.4</v>
       </c>
       <c r="D28" t="n">
-        <v>11.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 21553 ask: 21614</t>
+          <t>Day 4 — Active bid: 21050 ask: 21141</t>
         </is>
       </c>
     </row>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2315</v>
+        <v>2678</v>
       </c>
       <c r="C33" t="n">
-        <v>12437</v>
+        <v>13612</v>
       </c>
       <c r="D33" t="n">
-        <v>6801</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="34">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2953</v>
+        <v>3359</v>
       </c>
       <c r="C34" t="n">
-        <v>14134</v>
+        <v>14729</v>
       </c>
       <c r="D34" t="n">
-        <v>4527</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="36">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.7</v>
+        <v>12.7</v>
       </c>
       <c r="C37" t="n">
-        <v>57.7</v>
+        <v>64.7</v>
       </c>
       <c r="D37" t="n">
-        <v>31.6</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="38">
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13.7</v>
+        <v>15.9</v>
       </c>
       <c r="C38" t="n">
-        <v>65.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="D38" t="n">
-        <v>20.9</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21536 ask: 21506</t>
+          <t>Day 5 — Active bid: 21283 ask: 21228</t>
         </is>
       </c>
     </row>
@@ -3876,13 +3876,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4649</v>
+        <v>5657</v>
       </c>
       <c r="C43" t="n">
-        <v>14131</v>
+        <v>13752</v>
       </c>
       <c r="D43" t="n">
-        <v>2756</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="44">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3254</v>
+        <v>3994</v>
       </c>
       <c r="C44" t="n">
-        <v>14512</v>
+        <v>14380</v>
       </c>
       <c r="D44" t="n">
-        <v>3740</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="46">
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.6</v>
+        <v>26.6</v>
       </c>
       <c r="C47" t="n">
-        <v>65.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>12.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.1</v>
+        <v>18.8</v>
       </c>
       <c r="C48" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>13.4</v>
       </c>
     </row>
   </sheetData>
@@ -5890,10 +5890,10 @@
         <v>113</v>
       </c>
       <c r="C13" t="n">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D13" t="n">
-        <v>21873</v>
+        <v>21871</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>0.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D17" t="n">
         <v>94.3</v>
@@ -9670,10 +9670,10 @@
         <v>16388</v>
       </c>
       <c r="C34" t="n">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D34" t="n">
-        <v>2566</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="36">
@@ -9862,7 +9862,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18382 ask: 18126</t>
+          <t>Day 1 — Active bid: 18374 ask: 18126</t>
         </is>
       </c>
     </row>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15509</v>
+        <v>15499</v>
       </c>
       <c r="C3" t="n">
         <v>427</v>
       </c>
       <c r="D3" t="n">
-        <v>2446</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="4">
@@ -9911,13 +9911,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15461</v>
+        <v>15468</v>
       </c>
       <c r="C4" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D4" t="n">
-        <v>2276</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="6">
@@ -9968,10 +9968,10 @@
         <v>85.3</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D8" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
@@ -10322,7 +10322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18634 ask: 19236</t>
+          <t>Day 5 — Active bid: 18640 ask: 19230</t>
         </is>
       </c>
     </row>
@@ -10355,13 +10355,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12553</v>
+        <v>12556</v>
       </c>
       <c r="C43" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D43" t="n">
-        <v>5303</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="44">
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13186</v>
+        <v>13184</v>
       </c>
       <c r="C44" t="n">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="D44" t="n">
-        <v>5300</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="46">
@@ -10425,7 +10425,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C48" t="n">
         <v>3.9</v>
@@ -12141,10 +12141,10 @@
         <v>222</v>
       </c>
       <c r="C44" t="n">
-        <v>14782</v>
+        <v>14784</v>
       </c>
       <c r="D44" t="n">
-        <v>3781</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="46">

--- a/sheets/quote_position.xlsx
+++ b/sheets/quote_position.xlsx
@@ -438,7 +438,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 15393 ask: 15945</t>
+          <t>Day 1 — Active bid: 16600 ask: 16655</t>
         </is>
       </c>
     </row>
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>1417</v>
+        <v>1138</v>
       </c>
       <c r="D3" t="n">
-        <v>13724</v>
+        <v>15272</v>
       </c>
     </row>
     <row r="4">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="C4" t="n">
-        <v>1611</v>
+        <v>1385</v>
       </c>
       <c r="D4" t="n">
-        <v>13938</v>
+        <v>14966</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="C7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D7" t="n">
-        <v>89.2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="C8" t="n">
-        <v>10.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>87.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 18456 ask: 18962</t>
+          <t>Day 2 — Active bid: 19629 ask: 19720</t>
         </is>
       </c>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="C13" t="n">
-        <v>1312</v>
+        <v>1138</v>
       </c>
       <c r="D13" t="n">
-        <v>16948</v>
+        <v>18383</v>
       </c>
     </row>
     <row r="14">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="C14" t="n">
-        <v>1492</v>
+        <v>1251</v>
       </c>
       <c r="D14" t="n">
-        <v>17231</v>
+        <v>18307</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="D17" t="n">
-        <v>91.8</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="18">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C18" t="n">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="D18" t="n">
-        <v>90.90000000000001</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 17837 ask: 18574</t>
+          <t>Day 3 — Active bid: 18951 ask: 19111</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="C23" t="n">
-        <v>1501</v>
+        <v>967</v>
       </c>
       <c r="D23" t="n">
-        <v>16088</v>
+        <v>17824</v>
       </c>
     </row>
     <row r="24">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="C24" t="n">
-        <v>1603</v>
+        <v>1394</v>
       </c>
       <c r="D24" t="n">
-        <v>16624</v>
+        <v>17453</v>
       </c>
     </row>
     <row r="26">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="C27" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="D27" t="n">
-        <v>90.2</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="C28" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="D28" t="n">
-        <v>89.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 18446 ask: 18619</t>
+          <t>Day 4 — Active bid: 19587 ask: 19626</t>
         </is>
       </c>
     </row>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C33" t="n">
-        <v>1414</v>
+        <v>1046</v>
       </c>
       <c r="D33" t="n">
-        <v>16874</v>
+        <v>18425</v>
       </c>
     </row>
     <row r="34">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>261</v>
+        <v>165</v>
       </c>
       <c r="C34" t="n">
-        <v>1448</v>
+        <v>1245</v>
       </c>
       <c r="D34" t="n">
-        <v>16910</v>
+        <v>18216</v>
       </c>
     </row>
     <row r="36">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C37" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="D37" t="n">
-        <v>91.5</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="C38" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="D38" t="n">
-        <v>90.8</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18546 ask: 19214</t>
+          <t>Day 5 — Active bid: 19970 ask: 20015</t>
         </is>
       </c>
     </row>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="C43" t="n">
-        <v>1056</v>
+        <v>842</v>
       </c>
       <c r="D43" t="n">
-        <v>17360</v>
+        <v>19055</v>
       </c>
     </row>
     <row r="44">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="C44" t="n">
-        <v>1428</v>
+        <v>1289</v>
       </c>
       <c r="D44" t="n">
-        <v>17517</v>
+        <v>18534</v>
       </c>
     </row>
     <row r="46">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="C47" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="D47" t="n">
-        <v>93.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="D48" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1027,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19769 ask: 19788</t>
+          <t>Day 1 — Active bid: 19997 ask: 19951</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C3" t="n">
-        <v>17245</v>
+        <v>16382</v>
       </c>
       <c r="D3" t="n">
-        <v>2115</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="4">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>634</v>
+        <v>551</v>
       </c>
       <c r="C4" t="n">
-        <v>16534</v>
+        <v>15804</v>
       </c>
       <c r="D4" t="n">
-        <v>2620</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="6">
@@ -1117,10 +1117,10 @@
         <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>87.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>10.7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="C8" t="n">
-        <v>83.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 21383 ask: 21416</t>
+          <t>Day 2 — Active bid: 21567 ask: 21571</t>
         </is>
       </c>
     </row>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C13" t="n">
-        <v>17607</v>
+        <v>15977</v>
       </c>
       <c r="D13" t="n">
-        <v>3646</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="14">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>377</v>
+        <v>313</v>
       </c>
       <c r="C14" t="n">
-        <v>19624</v>
+        <v>18273</v>
       </c>
       <c r="D14" t="n">
-        <v>1415</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
         <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>82.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>17.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="18">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="C18" t="n">
-        <v>91.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="D18" t="n">
-        <v>6.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 21085 ask: 21105</t>
+          <t>Day 3 — Active bid: 21208 ask: 21213</t>
         </is>
       </c>
     </row>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="C23" t="n">
-        <v>17652</v>
+        <v>16553</v>
       </c>
       <c r="D23" t="n">
-        <v>3008</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="24">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>767</v>
+        <v>730</v>
       </c>
       <c r="C24" t="n">
-        <v>17366</v>
+        <v>16430</v>
       </c>
       <c r="D24" t="n">
-        <v>2972</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="26">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C27" t="n">
-        <v>83.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1360,19 +1360,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="C28" t="n">
-        <v>82.3</v>
+        <v>77.5</v>
       </c>
       <c r="D28" t="n">
-        <v>14.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 21269 ask: 21349</t>
+          <t>Day 4 — Active bid: 21494 ask: 21488</t>
         </is>
       </c>
     </row>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="C33" t="n">
-        <v>17766</v>
+        <v>16983</v>
       </c>
       <c r="D33" t="n">
-        <v>3244</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="34">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>477</v>
+        <v>418</v>
       </c>
       <c r="C34" t="n">
-        <v>18803</v>
+        <v>17851</v>
       </c>
       <c r="D34" t="n">
-        <v>2069</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="36">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C37" t="n">
-        <v>83.5</v>
+        <v>79</v>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="38">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="C38" t="n">
-        <v>88.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>9.699999999999999</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21346 ask: 21452</t>
+          <t>Day 5 — Active bid: 21557 ask: 21608</t>
         </is>
       </c>
     </row>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C43" t="n">
-        <v>17548</v>
+        <v>16250</v>
       </c>
       <c r="D43" t="n">
-        <v>3627</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="44">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C44" t="n">
-        <v>18707</v>
+        <v>18276</v>
       </c>
       <c r="D44" t="n">
-        <v>2335</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="46">
@@ -1577,10 +1577,10 @@
         <v>0.8</v>
       </c>
       <c r="C47" t="n">
-        <v>82.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="48">
@@ -1593,10 +1593,10 @@
         <v>1.9</v>
       </c>
       <c r="C48" t="n">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>10.9</v>
+        <v>13.5</v>
       </c>
     </row>
   </sheetData>
@@ -2794,7 +2794,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 19374 ask: 19279</t>
+          <t>Day 1 — Active bid: 20202 ask: 20104</t>
         </is>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7013</v>
+        <v>4201</v>
       </c>
       <c r="C3" t="n">
-        <v>10025</v>
+        <v>9964</v>
       </c>
       <c r="D3" t="n">
-        <v>2336</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="4">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7160</v>
+        <v>4398</v>
       </c>
       <c r="C4" t="n">
-        <v>9706</v>
+        <v>10572</v>
       </c>
       <c r="D4" t="n">
-        <v>2413</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="6">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36.2</v>
+        <v>20.8</v>
       </c>
       <c r="C7" t="n">
-        <v>51.7</v>
+        <v>49.3</v>
       </c>
       <c r="D7" t="n">
-        <v>12.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="8">
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.1</v>
+        <v>21.9</v>
       </c>
       <c r="C8" t="n">
-        <v>50.3</v>
+        <v>52.6</v>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 20111 ask: 19635</t>
+          <t>Day 2 — Active bid: 20992 ask: 20738</t>
         </is>
       </c>
     </row>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7027</v>
+        <v>4624</v>
       </c>
       <c r="C13" t="n">
-        <v>10853</v>
+        <v>10959</v>
       </c>
       <c r="D13" t="n">
-        <v>2231</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="14">
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5619</v>
+        <v>2904</v>
       </c>
       <c r="C14" t="n">
-        <v>11313</v>
+        <v>10675</v>
       </c>
       <c r="D14" t="n">
-        <v>2703</v>
+        <v>7159</v>
       </c>
     </row>
     <row r="16">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.9</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="18">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.6</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>57.6</v>
+        <v>51.5</v>
       </c>
       <c r="D18" t="n">
-        <v>13.8</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19910 ask: 19255</t>
+          <t>Day 3 — Active bid: 20322 ask: 20020</t>
         </is>
       </c>
     </row>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11370</v>
+        <v>8908</v>
       </c>
       <c r="C23" t="n">
-        <v>6642</v>
+        <v>7793</v>
       </c>
       <c r="D23" t="n">
-        <v>1898</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="24">
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9086</v>
+        <v>4552</v>
       </c>
       <c r="C24" t="n">
-        <v>8002</v>
+        <v>10089</v>
       </c>
       <c r="D24" t="n">
-        <v>2167</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="26">
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="C27" t="n">
-        <v>33.4</v>
+        <v>38.3</v>
       </c>
       <c r="D27" t="n">
-        <v>9.5</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="28">
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>47.2</v>
+        <v>22.7</v>
       </c>
       <c r="C28" t="n">
-        <v>41.6</v>
+        <v>50.4</v>
       </c>
       <c r="D28" t="n">
-        <v>11.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 18603 ask: 18605</t>
+          <t>Day 4 — Active bid: 20375 ask: 20322</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2217</v>
+        <v>1546</v>
       </c>
       <c r="C33" t="n">
-        <v>12396</v>
+        <v>8693</v>
       </c>
       <c r="D33" t="n">
-        <v>3990</v>
+        <v>10136</v>
       </c>
     </row>
     <row r="34">
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2725</v>
+        <v>1589</v>
       </c>
       <c r="C34" t="n">
-        <v>11793</v>
+        <v>8773</v>
       </c>
       <c r="D34" t="n">
-        <v>4087</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="36">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11.9</v>
+        <v>7.6</v>
       </c>
       <c r="C37" t="n">
-        <v>66.59999999999999</v>
+        <v>42.7</v>
       </c>
       <c r="D37" t="n">
-        <v>21.4</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="38">
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.6</v>
+        <v>7.8</v>
       </c>
       <c r="C38" t="n">
-        <v>63.4</v>
+        <v>43.2</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 20189 ask: 19791</t>
+          <t>Day 5 — Active bid: 20807 ask: 20775</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5454</v>
+        <v>3643</v>
       </c>
       <c r="C43" t="n">
-        <v>12834</v>
+        <v>11802</v>
       </c>
       <c r="D43" t="n">
-        <v>1901</v>
+        <v>5362</v>
       </c>
     </row>
     <row r="44">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3309</v>
+        <v>1798</v>
       </c>
       <c r="C44" t="n">
-        <v>13367</v>
+        <v>10562</v>
       </c>
       <c r="D44" t="n">
-        <v>3115</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="46">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="C47" t="n">
-        <v>63.6</v>
+        <v>56.7</v>
       </c>
       <c r="D47" t="n">
-        <v>9.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="48">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>67.5</v>
+        <v>50.8</v>
       </c>
       <c r="D48" t="n">
-        <v>15.7</v>
+        <v>40.5</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3383,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 20605 ask: 20709</t>
+          <t>Day 1 — Active bid: 21697 ask: 21642</t>
         </is>
       </c>
     </row>
@@ -3416,13 +3416,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7301</v>
+        <v>4428</v>
       </c>
       <c r="C3" t="n">
-        <v>11067</v>
+        <v>11372</v>
       </c>
       <c r="D3" t="n">
-        <v>2237</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="4">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7828</v>
+        <v>5046</v>
       </c>
       <c r="C4" t="n">
-        <v>10648</v>
+        <v>11879</v>
       </c>
       <c r="D4" t="n">
-        <v>2233</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="6">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.4</v>
+        <v>20.4</v>
       </c>
       <c r="C7" t="n">
-        <v>53.7</v>
+        <v>52.4</v>
       </c>
       <c r="D7" t="n">
-        <v>10.9</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="8">
@@ -3486,19 +3486,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.8</v>
+        <v>23.3</v>
       </c>
       <c r="C8" t="n">
-        <v>51.4</v>
+        <v>54.9</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 21211 ask: 21135</t>
+          <t>Day 2 — Active bid: 22235 ask: 22179</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7323</v>
+        <v>4431</v>
       </c>
       <c r="C13" t="n">
-        <v>11628</v>
+        <v>12356</v>
       </c>
       <c r="D13" t="n">
-        <v>2260</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="14">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6477</v>
+        <v>2733</v>
       </c>
       <c r="C14" t="n">
-        <v>12393</v>
+        <v>13471</v>
       </c>
       <c r="D14" t="n">
-        <v>2265</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="16">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.5</v>
+        <v>19.9</v>
       </c>
       <c r="C17" t="n">
-        <v>54.8</v>
+        <v>55.6</v>
       </c>
       <c r="D17" t="n">
-        <v>10.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="18">
@@ -3601,19 +3601,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.6</v>
+        <v>12.3</v>
       </c>
       <c r="C18" t="n">
-        <v>58.6</v>
+        <v>60.7</v>
       </c>
       <c r="D18" t="n">
-        <v>10.7</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 20789 ask: 20484</t>
+          <t>Day 3 — Active bid: 21511 ask: 21428</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11737</v>
+        <v>8251</v>
       </c>
       <c r="C23" t="n">
-        <v>7219</v>
+        <v>9665</v>
       </c>
       <c r="D23" t="n">
-        <v>1833</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="24">
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9637</v>
+        <v>5162</v>
       </c>
       <c r="C24" t="n">
-        <v>8894</v>
+        <v>11546</v>
       </c>
       <c r="D24" t="n">
-        <v>1953</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="26">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>56.5</v>
+        <v>38.4</v>
       </c>
       <c r="C27" t="n">
-        <v>34.7</v>
+        <v>44.9</v>
       </c>
       <c r="D27" t="n">
-        <v>8.800000000000001</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="28">
@@ -3716,19 +3716,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>24.1</v>
       </c>
       <c r="C28" t="n">
-        <v>43.4</v>
+        <v>53.9</v>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 21050 ask: 21141</t>
+          <t>Day 4 — Active bid: 22303 ask: 22316</t>
         </is>
       </c>
     </row>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2678</v>
+        <v>1458</v>
       </c>
       <c r="C33" t="n">
-        <v>13612</v>
+        <v>9795</v>
       </c>
       <c r="D33" t="n">
-        <v>4760</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="34">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3359</v>
+        <v>2087</v>
       </c>
       <c r="C34" t="n">
-        <v>14729</v>
+        <v>11859</v>
       </c>
       <c r="D34" t="n">
-        <v>3053</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="36">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12.7</v>
+        <v>6.5</v>
       </c>
       <c r="C37" t="n">
-        <v>64.7</v>
+        <v>43.9</v>
       </c>
       <c r="D37" t="n">
-        <v>22.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="38">
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.9</v>
+        <v>9.4</v>
       </c>
       <c r="C38" t="n">
-        <v>69.7</v>
+        <v>53.1</v>
       </c>
       <c r="D38" t="n">
-        <v>14.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 21283 ask: 21228</t>
+          <t>Day 5 — Active bid: 22142 ask: 22173</t>
         </is>
       </c>
     </row>
@@ -3876,13 +3876,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5657</v>
+        <v>2761</v>
       </c>
       <c r="C43" t="n">
-        <v>13752</v>
+        <v>13780</v>
       </c>
       <c r="D43" t="n">
-        <v>1874</v>
+        <v>5601</v>
       </c>
     </row>
     <row r="44">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3994</v>
+        <v>1907</v>
       </c>
       <c r="C44" t="n">
-        <v>14380</v>
+        <v>12997</v>
       </c>
       <c r="D44" t="n">
-        <v>2854</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="46">
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26.6</v>
+        <v>12.5</v>
       </c>
       <c r="C47" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="D47" t="n">
-        <v>8.800000000000001</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="48">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.8</v>
+        <v>8.6</v>
       </c>
       <c r="C48" t="n">
-        <v>67.7</v>
+        <v>58.6</v>
       </c>
       <c r="D48" t="n">
-        <v>13.4</v>
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -5150,7 +5150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 21529 ask: 21529</t>
+          <t>Day 1 — Active bid: 21919 ask: 21941</t>
         </is>
       </c>
     </row>
@@ -5183,13 +5183,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="C3" t="n">
-        <v>2549</v>
+        <v>1735</v>
       </c>
       <c r="D3" t="n">
-        <v>18676</v>
+        <v>19978</v>
       </c>
     </row>
     <row r="4">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>447</v>
+        <v>340</v>
       </c>
       <c r="C4" t="n">
-        <v>2353</v>
+        <v>1997</v>
       </c>
       <c r="D4" t="n">
-        <v>18729</v>
+        <v>19604</v>
       </c>
     </row>
     <row r="6">
@@ -5237,13 +5237,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="C7" t="n">
-        <v>11.8</v>
+        <v>7.9</v>
       </c>
       <c r="D7" t="n">
-        <v>86.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5253,19 +5253,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="C8" t="n">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
       <c r="D8" t="n">
-        <v>87</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 22635 ask: 22659</t>
+          <t>Day 2 — Active bid: 22884 ask: 22922</t>
         </is>
       </c>
     </row>
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>1422</v>
+        <v>871</v>
       </c>
       <c r="D13" t="n">
-        <v>21103</v>
+        <v>21912</v>
       </c>
     </row>
     <row r="14">
@@ -5314,13 +5314,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C14" t="n">
-        <v>1555</v>
+        <v>972</v>
       </c>
       <c r="D14" t="n">
-        <v>20948</v>
+        <v>21798</v>
       </c>
     </row>
     <row r="16">
@@ -5352,13 +5352,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C17" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="D17" t="n">
-        <v>93.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="18">
@@ -5371,16 +5371,16 @@
         <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="D18" t="n">
-        <v>92.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 22511 ask: 22531</t>
+          <t>Day 3 — Active bid: 22722 ask: 22742</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="C23" t="n">
-        <v>2526</v>
+        <v>1433</v>
       </c>
       <c r="D23" t="n">
-        <v>19628</v>
+        <v>20978</v>
       </c>
     </row>
     <row r="24">
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C24" t="n">
-        <v>2200</v>
+        <v>1559</v>
       </c>
       <c r="D24" t="n">
-        <v>19992</v>
+        <v>20855</v>
       </c>
     </row>
     <row r="26">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C27" t="n">
-        <v>11.2</v>
+        <v>6.3</v>
       </c>
       <c r="D27" t="n">
-        <v>87.2</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="28">
@@ -5483,19 +5483,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C28" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="D28" t="n">
-        <v>88.7</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 22620 ask: 22609</t>
+          <t>Day 4 — Active bid: 22858 ask: 22864</t>
         </is>
       </c>
     </row>
@@ -5528,13 +5528,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>403</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>1646</v>
+        <v>1007</v>
       </c>
       <c r="D33" t="n">
-        <v>20571</v>
+        <v>21530</v>
       </c>
     </row>
     <row r="34">
@@ -5544,13 +5544,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="C34" t="n">
-        <v>2517</v>
+        <v>1068</v>
       </c>
       <c r="D34" t="n">
-        <v>19796</v>
+        <v>21560</v>
       </c>
     </row>
     <row r="36">
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="C37" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="D37" t="n">
-        <v>90.90000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="38">
@@ -5598,19 +5598,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>11.1</v>
+        <v>4.7</v>
       </c>
       <c r="D38" t="n">
-        <v>87.59999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 22620 ask: 22580</t>
+          <t>Day 5 — Active bid: 22872 ask: 22816</t>
         </is>
       </c>
     </row>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="C43" t="n">
-        <v>1782</v>
+        <v>788</v>
       </c>
       <c r="D43" t="n">
-        <v>20473</v>
+        <v>21753</v>
       </c>
     </row>
     <row r="44">
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="C44" t="n">
-        <v>1426</v>
+        <v>1176</v>
       </c>
       <c r="D44" t="n">
-        <v>20826</v>
+        <v>21372</v>
       </c>
     </row>
     <row r="46">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C47" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="D47" t="n">
-        <v>90.5</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C48" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="D48" t="n">
-        <v>92.2</v>
+        <v>93.7</v>
       </c>
     </row>
   </sheetData>
@@ -5739,7 +5739,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 22675 ask: 22690</t>
+          <t>Day 1 — Active bid: 22970 ask: 23002</t>
         </is>
       </c>
     </row>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="C3" t="n">
-        <v>3040</v>
+        <v>1621</v>
       </c>
       <c r="D3" t="n">
-        <v>19221</v>
+        <v>21032</v>
       </c>
     </row>
     <row r="4">
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>499</v>
+        <v>402</v>
       </c>
       <c r="C4" t="n">
-        <v>2970</v>
+        <v>2397</v>
       </c>
       <c r="D4" t="n">
-        <v>19221</v>
+        <v>20203</v>
       </c>
     </row>
     <row r="6">
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="C7" t="n">
-        <v>13.4</v>
+        <v>7.1</v>
       </c>
       <c r="D7" t="n">
-        <v>84.8</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5842,19 +5842,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.1</v>
+        <v>10.4</v>
       </c>
       <c r="D8" t="n">
-        <v>84.7</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 23204 ask: 23202</t>
+          <t>Day 2 — Active bid: 23303 ask: 23298</t>
         </is>
       </c>
     </row>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" t="n">
-        <v>1220</v>
+        <v>1156</v>
       </c>
       <c r="D13" t="n">
-        <v>21871</v>
+        <v>22035</v>
       </c>
     </row>
     <row r="14">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="C14" t="n">
-        <v>1114</v>
+        <v>656</v>
       </c>
       <c r="D14" t="n">
-        <v>21880</v>
+        <v>22473</v>
       </c>
     </row>
     <row r="16">
@@ -5944,10 +5944,10 @@
         <v>0.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -5957,19 +5957,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="D18" t="n">
-        <v>94.3</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 23153 ask: 23159</t>
+          <t>Day 3 — Active bid: 23258 ask: 23270</t>
         </is>
       </c>
     </row>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="C23" t="n">
-        <v>1966</v>
+        <v>1708</v>
       </c>
       <c r="D23" t="n">
-        <v>20820</v>
+        <v>21213</v>
       </c>
     </row>
     <row r="24">
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="C24" t="n">
-        <v>2337</v>
+        <v>1302</v>
       </c>
       <c r="D24" t="n">
-        <v>20444</v>
+        <v>21614</v>
       </c>
     </row>
     <row r="26">
@@ -6056,13 +6056,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C27" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="D27" t="n">
-        <v>89.90000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="28">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.1</v>
+        <v>5.6</v>
       </c>
       <c r="D28" t="n">
-        <v>88.3</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 23130 ask: 23126</t>
+          <t>Day 4 — Active bid: 23255 ask: 23247</t>
         </is>
       </c>
     </row>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>413</v>
+        <v>323</v>
       </c>
       <c r="C33" t="n">
-        <v>1605</v>
+        <v>1155</v>
       </c>
       <c r="D33" t="n">
-        <v>21112</v>
+        <v>21777</v>
       </c>
     </row>
     <row r="34">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C34" t="n">
-        <v>2095</v>
+        <v>1552</v>
       </c>
       <c r="D34" t="n">
-        <v>20669</v>
+        <v>21351</v>
       </c>
     </row>
     <row r="36">
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="C37" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>91.3</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -6187,19 +6187,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C38" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="D38" t="n">
-        <v>89.40000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 23248 ask: 23230</t>
+          <t>Day 5 — Active bid: 23260 ask: 23223</t>
         </is>
       </c>
     </row>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C43" t="n">
-        <v>1419</v>
+        <v>1219</v>
       </c>
       <c r="D43" t="n">
-        <v>21412</v>
+        <v>21631</v>
       </c>
     </row>
     <row r="44">
@@ -6248,13 +6248,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="C44" t="n">
-        <v>1007</v>
+        <v>944</v>
       </c>
       <c r="D44" t="n">
-        <v>21885</v>
+        <v>21977</v>
       </c>
     </row>
     <row r="46">
@@ -6289,10 +6289,10 @@
         <v>1.8</v>
       </c>
       <c r="C47" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="D47" t="n">
-        <v>92.09999999999999</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48">
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="C48" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="D48" t="n">
-        <v>94.2</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6917,7 +6917,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 20617 ask: 20729</t>
+          <t>Day 1 — Active bid: 21715 ask: 21752</t>
         </is>
       </c>
     </row>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1039</v>
+        <v>880</v>
       </c>
       <c r="C3" t="n">
-        <v>2052</v>
+        <v>1295</v>
       </c>
       <c r="D3" t="n">
-        <v>17526</v>
+        <v>19540</v>
       </c>
     </row>
     <row r="4">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1142</v>
+        <v>941</v>
       </c>
       <c r="C4" t="n">
-        <v>2236</v>
+        <v>1485</v>
       </c>
       <c r="D4" t="n">
-        <v>17351</v>
+        <v>19326</v>
       </c>
     </row>
     <row r="6">
@@ -7004,13 +7004,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -7020,19 +7020,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="C8" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="D8" t="n">
-        <v>83.7</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 22397 ask: 22565</t>
+          <t>Day 2 — Active bid: 22984 ask: 22991</t>
         </is>
       </c>
     </row>
@@ -7065,13 +7065,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>667</v>
+        <v>409</v>
       </c>
       <c r="C13" t="n">
-        <v>1738</v>
+        <v>1020</v>
       </c>
       <c r="D13" t="n">
-        <v>19992</v>
+        <v>21555</v>
       </c>
     </row>
     <row r="14">
@@ -7081,13 +7081,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>604</v>
+        <v>323</v>
       </c>
       <c r="C14" t="n">
-        <v>2023</v>
+        <v>1048</v>
       </c>
       <c r="D14" t="n">
-        <v>19938</v>
+        <v>21620</v>
       </c>
     </row>
     <row r="16">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="C17" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="D17" t="n">
-        <v>89.3</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="18">
@@ -7135,19 +7135,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="D18" t="n">
-        <v>88.40000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 22255 ask: 22355</t>
+          <t>Day 3 — Active bid: 22736 ask: 22729</t>
         </is>
       </c>
     </row>
@@ -7180,13 +7180,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>862</v>
+        <v>573</v>
       </c>
       <c r="C23" t="n">
-        <v>2138</v>
+        <v>1180</v>
       </c>
       <c r="D23" t="n">
-        <v>19255</v>
+        <v>20983</v>
       </c>
     </row>
     <row r="24">
@@ -7196,13 +7196,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>785</v>
+        <v>569</v>
       </c>
       <c r="C24" t="n">
-        <v>2215</v>
+        <v>1476</v>
       </c>
       <c r="D24" t="n">
-        <v>19355</v>
+        <v>20684</v>
       </c>
     </row>
     <row r="26">
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="D27" t="n">
-        <v>86.5</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="28">
@@ -7250,19 +7250,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
       <c r="D28" t="n">
-        <v>86.59999999999999</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 22232 ask: 22455</t>
+          <t>Day 4 — Active bid: 22904 ask: 22918</t>
         </is>
       </c>
     </row>
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>617</v>
+        <v>373</v>
       </c>
       <c r="C33" t="n">
-        <v>1820</v>
+        <v>1079</v>
       </c>
       <c r="D33" t="n">
-        <v>19795</v>
+        <v>21452</v>
       </c>
     </row>
     <row r="34">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>683</v>
+        <v>355</v>
       </c>
       <c r="C34" t="n">
-        <v>1985</v>
+        <v>1055</v>
       </c>
       <c r="D34" t="n">
-        <v>19787</v>
+        <v>21508</v>
       </c>
     </row>
     <row r="36">
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="C37" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="D37" t="n">
-        <v>89</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="38">
@@ -7365,19 +7365,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="C38" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="D38" t="n">
-        <v>88.09999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 22557 ask: 22834</t>
+          <t>Day 5 — Active bid: 23054 ask: 23053</t>
         </is>
       </c>
     </row>
@@ -7410,13 +7410,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>615</v>
+        <v>291</v>
       </c>
       <c r="C43" t="n">
-        <v>1445</v>
+        <v>753</v>
       </c>
       <c r="D43" t="n">
-        <v>20497</v>
+        <v>22010</v>
       </c>
     </row>
     <row r="44">
@@ -7426,13 +7426,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>570</v>
+        <v>324</v>
       </c>
       <c r="C44" t="n">
-        <v>1821</v>
+        <v>1066</v>
       </c>
       <c r="D44" t="n">
-        <v>20443</v>
+        <v>21663</v>
       </c>
     </row>
     <row r="46">
@@ -7464,13 +7464,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="C47" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="D47" t="n">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="48">
@@ -7480,13 +7480,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="D48" t="n">
-        <v>89.5</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -9273,7 +9273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18318 ask: 17934</t>
+          <t>Day 1 — Active bid: 22303 ask: 22333</t>
         </is>
       </c>
     </row>
@@ -9306,13 +9306,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15477</v>
+        <v>1693</v>
       </c>
       <c r="C3" t="n">
-        <v>400</v>
+        <v>121</v>
       </c>
       <c r="D3" t="n">
-        <v>2441</v>
+        <v>20489</v>
       </c>
     </row>
     <row r="4">
@@ -9322,13 +9322,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15258</v>
+        <v>2238</v>
       </c>
       <c r="C4" t="n">
-        <v>376</v>
+        <v>181</v>
       </c>
       <c r="D4" t="n">
-        <v>2300</v>
+        <v>19914</v>
       </c>
     </row>
     <row r="6">
@@ -9360,13 +9360,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.5</v>
+        <v>7.6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -9376,19 +9376,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.09999999999999</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>12.8</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19568 ask: 19830</t>
+          <t>Day 2 — Active bid: 23123 ask: 23112</t>
         </is>
       </c>
     </row>
@@ -9421,13 +9421,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16399</v>
+        <v>1047</v>
       </c>
       <c r="C13" t="n">
-        <v>424</v>
+        <v>199</v>
       </c>
       <c r="D13" t="n">
-        <v>2745</v>
+        <v>21877</v>
       </c>
     </row>
     <row r="14">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16602</v>
+        <v>856</v>
       </c>
       <c r="C14" t="n">
-        <v>472</v>
+        <v>157</v>
       </c>
       <c r="D14" t="n">
-        <v>2756</v>
+        <v>22099</v>
       </c>
     </row>
     <row r="16">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.8</v>
+        <v>4.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.7</v>
+        <v>3.7</v>
       </c>
       <c r="C18" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19273 ask: 19863</t>
+          <t>Day 3 — Active bid: 22296 ask: 22300</t>
         </is>
       </c>
     </row>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17352</v>
+        <v>2774</v>
       </c>
       <c r="C23" t="n">
-        <v>364</v>
+        <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>1557</v>
+        <v>19378</v>
       </c>
     </row>
     <row r="24">
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17876</v>
+        <v>3300</v>
       </c>
       <c r="C24" t="n">
-        <v>355</v>
+        <v>132</v>
       </c>
       <c r="D24" t="n">
-        <v>1632</v>
+        <v>18868</v>
       </c>
     </row>
     <row r="26">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90</v>
+        <v>12.4</v>
       </c>
       <c r="C27" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>8.1</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -9606,19 +9606,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>14.8</v>
       </c>
       <c r="C28" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="D28" t="n">
-        <v>8.199999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19564 ask: 19429</t>
+          <t>Day 4 — Active bid: 22950 ask: 22983</t>
         </is>
       </c>
     </row>
@@ -9651,13 +9651,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16320</v>
+        <v>1582</v>
       </c>
       <c r="C33" t="n">
-        <v>495</v>
+        <v>205</v>
       </c>
       <c r="D33" t="n">
-        <v>2749</v>
+        <v>21163</v>
       </c>
     </row>
     <row r="34">
@@ -9667,13 +9667,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16388</v>
+        <v>1625</v>
       </c>
       <c r="C34" t="n">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="D34" t="n">
-        <v>2570</v>
+        <v>21170</v>
       </c>
     </row>
     <row r="36">
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>83.40000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="C37" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="D37" t="n">
-        <v>14.1</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="38">
@@ -9721,19 +9721,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>84.3</v>
+        <v>7.1</v>
       </c>
       <c r="C38" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18147 ask: 18951</t>
+          <t>Day 5 — Active bid: 22677 ask: 22743</t>
         </is>
       </c>
     </row>
@@ -9766,13 +9766,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12050</v>
+        <v>883</v>
       </c>
       <c r="C43" t="n">
-        <v>770</v>
+        <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>5327</v>
+        <v>21716</v>
       </c>
     </row>
     <row r="44">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12833</v>
+        <v>1041</v>
       </c>
       <c r="C44" t="n">
-        <v>763</v>
+        <v>94</v>
       </c>
       <c r="D44" t="n">
-        <v>5355</v>
+        <v>21608</v>
       </c>
     </row>
     <row r="46">
@@ -9820,13 +9820,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.40000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="C47" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="D47" t="n">
-        <v>29.4</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="48">
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>67.7</v>
+        <v>4.6</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="D48" t="n">
-        <v>28.3</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -9862,7 +9862,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 18374 ask: 18126</t>
+          <t>Day 1 — Active bid: 23068 ask: 23077</t>
         </is>
       </c>
     </row>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15499</v>
+        <v>1718</v>
       </c>
       <c r="C3" t="n">
-        <v>427</v>
+        <v>158</v>
       </c>
       <c r="D3" t="n">
-        <v>2448</v>
+        <v>21192</v>
       </c>
     </row>
     <row r="4">
@@ -9911,13 +9911,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15468</v>
+        <v>1876</v>
       </c>
       <c r="C4" t="n">
-        <v>391</v>
+        <v>157</v>
       </c>
       <c r="D4" t="n">
-        <v>2267</v>
+        <v>21044</v>
       </c>
     </row>
     <row r="6">
@@ -9949,13 +9949,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -9965,19 +9965,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.3</v>
+        <v>8.1</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19650 ask: 19943</t>
+          <t>Day 2 — Active bid: 23273 ask: 23279</t>
         </is>
       </c>
     </row>
@@ -10010,13 +10010,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16484</v>
+        <v>1080</v>
       </c>
       <c r="C13" t="n">
-        <v>457</v>
+        <v>172</v>
       </c>
       <c r="D13" t="n">
-        <v>2709</v>
+        <v>22021</v>
       </c>
     </row>
     <row r="14">
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16815</v>
+        <v>898</v>
       </c>
       <c r="C14" t="n">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="D14" t="n">
-        <v>2647</v>
+        <v>22209</v>
       </c>
     </row>
     <row r="16">
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.90000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="D17" t="n">
-        <v>13.8</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -10080,19 +10080,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.3</v>
+        <v>3.9</v>
       </c>
       <c r="C18" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 19259 ask: 19742</t>
+          <t>Day 3 — Active bid: 22431 ask: 22452</t>
         </is>
       </c>
     </row>
@@ -10125,13 +10125,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17377</v>
+        <v>2910</v>
       </c>
       <c r="C23" t="n">
-        <v>391</v>
+        <v>143</v>
       </c>
       <c r="D23" t="n">
-        <v>1491</v>
+        <v>19378</v>
       </c>
     </row>
     <row r="24">
@@ -10141,13 +10141,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17776</v>
+        <v>3295</v>
       </c>
       <c r="C24" t="n">
-        <v>335</v>
+        <v>155</v>
       </c>
       <c r="D24" t="n">
-        <v>1631</v>
+        <v>19002</v>
       </c>
     </row>
     <row r="26">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90.2</v>
+        <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>7.7</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -10195,19 +10195,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>14.7</v>
       </c>
       <c r="C28" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>8.300000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19718 ask: 19628</t>
+          <t>Day 4 — Active bid: 23129 ask: 23132</t>
         </is>
       </c>
     </row>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16589</v>
+        <v>1700</v>
       </c>
       <c r="C33" t="n">
-        <v>515</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>2614</v>
+        <v>21222</v>
       </c>
     </row>
     <row r="34">
@@ -10256,13 +10256,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16622</v>
+        <v>1547</v>
       </c>
       <c r="C34" t="n">
-        <v>484</v>
+        <v>222</v>
       </c>
       <c r="D34" t="n">
-        <v>2522</v>
+        <v>21363</v>
       </c>
     </row>
     <row r="36">
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>84.09999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="C37" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="D37" t="n">
-        <v>13.3</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="38">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>84.7</v>
+        <v>6.7</v>
       </c>
       <c r="C38" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>12.8</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 18640 ask: 19230</t>
+          <t>Day 5 — Active bid: 22918 ask: 22911</t>
         </is>
       </c>
     </row>
@@ -10355,13 +10355,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12556</v>
+        <v>950</v>
       </c>
       <c r="C43" t="n">
-        <v>776</v>
+        <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>5308</v>
+        <v>21889</v>
       </c>
     </row>
     <row r="44">
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13184</v>
+        <v>1184</v>
       </c>
       <c r="C44" t="n">
-        <v>742</v>
+        <v>109</v>
       </c>
       <c r="D44" t="n">
-        <v>5304</v>
+        <v>21618</v>
       </c>
     </row>
     <row r="46">
@@ -10409,13 +10409,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>67.40000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="C47" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="D47" t="n">
-        <v>28.5</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="48">
@@ -10425,13 +10425,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.59999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="C48" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="D48" t="n">
-        <v>27.6</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11629,7 +11629,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Day 1 — Active bid: 17255 ask: 16473</t>
+          <t>Day 1 — Active bid: 17683 ask: 16865</t>
         </is>
       </c>
     </row>
@@ -11662,13 +11662,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="C3" t="n">
-        <v>14843</v>
+        <v>14231</v>
       </c>
       <c r="D3" t="n">
-        <v>2170</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="4">
@@ -11678,13 +11678,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="C4" t="n">
-        <v>13440</v>
+        <v>13012</v>
       </c>
       <c r="D4" t="n">
-        <v>2655</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="6">
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>80.5</v>
       </c>
       <c r="D7" t="n">
-        <v>12.6</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="8">
@@ -11732,19 +11732,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="C8" t="n">
-        <v>81.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Day 2 — Active bid: 19675 ask: 19036</t>
+          <t>Day 2 — Active bid: 19824 ask: 19436</t>
         </is>
       </c>
     </row>
@@ -11777,13 +11777,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>17430</v>
+        <v>16124</v>
       </c>
       <c r="D13" t="n">
-        <v>2171</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="14">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C14" t="n">
-        <v>15211</v>
+        <v>14216</v>
       </c>
       <c r="D14" t="n">
-        <v>3663</v>
+        <v>5053</v>
       </c>
     </row>
     <row r="16">
@@ -11831,13 +11831,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C17" t="n">
-        <v>88.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="18">
@@ -11850,16 +11850,16 @@
         <v>0.9</v>
       </c>
       <c r="C18" t="n">
-        <v>79.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>19.2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Day 3 — Active bid: 18777 ask: 18891</t>
+          <t>Day 3 — Active bid: 19099 ask: 19178</t>
         </is>
       </c>
     </row>
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C23" t="n">
-        <v>15381</v>
+        <v>14618</v>
       </c>
       <c r="D23" t="n">
-        <v>3057</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="24">
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C24" t="n">
-        <v>15508</v>
+        <v>14722</v>
       </c>
       <c r="D24" t="n">
-        <v>2796</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="26">
@@ -11946,13 +11946,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C27" t="n">
-        <v>81.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="D27" t="n">
-        <v>16.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="28">
@@ -11962,19 +11962,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="C28" t="n">
-        <v>82.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D28" t="n">
-        <v>14.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4 — Active bid: 19220 ask: 18790</t>
+          <t>Day 4 — Active bid: 19605 ask: 19065</t>
         </is>
       </c>
     </row>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C33" t="n">
-        <v>16061</v>
+        <v>14816</v>
       </c>
       <c r="D33" t="n">
-        <v>3055</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="34">
@@ -12023,13 +12023,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="C34" t="n">
-        <v>16123</v>
+        <v>15573</v>
       </c>
       <c r="D34" t="n">
-        <v>2348</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="36">
@@ -12064,10 +12064,10 @@
         <v>0.5</v>
       </c>
       <c r="C37" t="n">
-        <v>83.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>15.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -12077,19 +12077,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C38" t="n">
-        <v>85.8</v>
+        <v>81.7</v>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Day 5 — Active bid: 19962 ask: 18785</t>
+          <t>Day 5 — Active bid: 20168 ask: 19380</t>
         </is>
       </c>
     </row>
@@ -12122,13 +12122,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C43" t="n">
-        <v>17264</v>
+        <v>15829</v>
       </c>
       <c r="D43" t="n">
-        <v>2612</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="44">
@@ -12138,13 +12138,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C44" t="n">
-        <v>14784</v>
+        <v>14316</v>
       </c>
       <c r="D44" t="n">
-        <v>3779</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="46">
@@ -12176,13 +12176,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C47" t="n">
-        <v>86.5</v>
+        <v>78.5</v>
       </c>
       <c r="D47" t="n">
-        <v>13.1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -12192,13 +12192,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C48" t="n">
-        <v>78.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
